--- a/coordinate_descent/results/mixed_archive.xlsx
+++ b/coordinate_descent/results/mixed_archive.xlsx
@@ -95,10 +95,10 @@
     <t xml:space="preserve">RS_1000</t>
   </si>
   <si>
-    <t xml:space="preserve">0.741281653522539, 0.831313368583707, 0.657739343667182, -0.0619987904527004, 0.781107391973205, 0.76915872750249, 0.482047392055718, 0.594272823238446, -0.0936775815733499, 0.104448187787296, 0.167331615317842, 0.445258453679007, -0.181903723379909, -0.0354803765226668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.1519325256348, -93.9881256103516, -92.1989095052083, -94.1661580403646, -0.793946717182795, -0.88074277639389, -0.965406173467636, -0.991366996367772, -0.984745079278946, -0.936007455984751, -0.976467496156692, -0.824072905381521, -0.893589689334234, -0.983076431353887</t>
+    <t xml:space="preserve">0.77318750583852, 0.819057867210521, 0.510590876506628, 0.0245478158180241, 0.802677470975575, 0.737879111154754, 0.301961919897346, 0.467694955507199, 0.0192016325075679, -0.0170503184218026, 0.0847702443258851, 0.438405186424431, -0.145713970987529, -0.0932913342481249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.3905881245931, -94.153030649821, -91.8658871968587, -94.2163210550944, -0.795162864526113, -0.881291387478511, -0.964886065324148, -0.991288969914118, -0.98478217124939, -0.933152802785238, -0.976770397027334, -0.823861120144526, -0.897522787253062, -0.982794735829035</t>
   </si>
   <si>
     <t xml:space="preserve"/>
@@ -107,127 +107,127 @@
     <t xml:space="preserve">unitcube</t>
   </si>
   <si>
-    <t xml:space="preserve">0.696011347020728, 0.820819772167353, 0.637454762322076, -0.0132244740774355, 0.808583493410995, 0.780282597698358, 0.482283904927755, 0.59997902692222, -0.0896293786150903, 0.0439381273647732, 0.185234138508065, 0.440022156004305, -0.181321343667361, -0.0177754301405168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-86.8425486246745, -93.8509536743164, -92.0731755574544, -94.21189549764, -0.794929061333338, -0.880972580115, -0.965408704678218, -0.991401159763336, -0.984801544745763, -0.931722557544708, -0.976973285277685, -0.823880817492803, -0.893625301122665, -0.983248112599055</t>
+    <t xml:space="preserve">0.702520878846441, 0.806430819314816, 0.499022584630942, 0.00572309335579209, 0.819512406331218, 0.67252834637671, 0.366232214425496, 0.417466005513427, 0.00271469943157121, 0.0053017904866502, 0.0692482228273861, 0.422046156659577, -0.228634858336721, -0.0139222800882006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-86.9140622456868, -94.010658009847, -91.8078689575195, -94.1980702718099, -0.795726795991262, -0.880239214499791, -0.965444334348043, -0.99105239311854, -0.984526364008586, -0.934609274069468, -0.97637655933698, -0.823262161016464, -0.892576773961385, -0.983544115225474</t>
   </si>
   <si>
     <t xml:space="preserve">standardize</t>
   </si>
   <si>
-    <t xml:space="preserve">0.756726548552141, 0.833531669053842, 0.619645370412307, 0.0924723309278151, 0.792685165267001, 0.71786576416979, 0.45878985979835, 0.627013722432621, -0.0910784415529645, 0.24778449725215, 0.198510467201069, 0.0898921868942393, -0.268751049276106, -0.0207898401760952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.2574851989746, -94.0171231587728, -91.9627840677897, -94.3110112508138, -0.794360653559367, -0.879683134953181, -0.965157266457876, -0.991563018163045, -0.98478133281072, -0.946157528956731, -0.977348373333613, -0.811036680142085, -0.888279084364573, -0.983218882481257</t>
+    <t xml:space="preserve">0.759557135046681, 0.807863066027003, 0.555017981187357, 0.0976105075343085, 0.809190780038359, 0.742631817762801, 0.528711954550144, 0.46101902257025, 0.013359394447896, 0.208105803710226, 0.0793296867186495, 0.0971597195805707, -0.162027309288634, -0.044471711537049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.2986745198568, -94.0268068949381, -92.0887016296387, -94.2871561686198, -0.795381045341492, -0.881367907921473, -0.966855676968892, -0.991257526477178, -0.984691524505615, -0.947824054956436, -0.976632354656855, -0.811366975307465, -0.896549739440282, -0.983255676428477</t>
   </si>
   <si>
     <t xml:space="preserve">log</t>
   </si>
   <si>
-    <t xml:space="preserve">0.877645991842286, 0.895297863690054, 0.81496452210697, 0.0195740549395006, 0.906602983476825, 0.924026767149256, 0.787813238000437, 0.793847255596463, -0.0100133909767764, 0.31947095937398, 0.26570969757513, 0.221624385859794, 0.103577128645122, 0.151466932975016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.0838663736979, -94.8245287577311, -93.173469543457, -94.2426518758138, -0.79843352039655, -0.883942135175069, -0.968678543965022, -0.992561860879262, -0.985912050803502, -0.951233861843745, -0.979246912399928, -0.815869132677714, -0.91104648510615, -0.984889221191406</t>
+    <t xml:space="preserve">0.890761753229116, 0.891549354195447, 0.822424638159059, 0.0556570697698735, 0.898970696218368, 0.8975248386734, 0.649327690074545, 0.702973713461394, 0.085591399832215, 0.229814181053887, 0.207530190909301, 0.206778448793713, 0.256195466803186, 0.179106500255594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.1834259033203, -94.9703875223796, -93.4298212687174, -94.2464818318685, -0.798388465245565, -0.883861746390661, -0.967903377612432, -0.992397125562032, -0.985812258720398, -0.949238580465317, -0.979885164896647, -0.815380485852559, -0.921495630343755, -0.985366636514664</t>
   </si>
   <si>
     <t xml:space="preserve">lhs</t>
   </si>
   <si>
-    <t xml:space="preserve">0.831526132386552, 0.820312195106008, 0.629413689169148, -0.0554832358372963, 0.803484662969432, 0.681367632830721, 0.470986609547126, 0.583872565986396, -0.0845409213920713, 0.0480149374829996, 0.153842697150727, 0.445612609619625, -0.119221224068974, -0.0471774020875794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.7686765034993, -93.8443186442057, -92.0233329772949, -94.1722679138184, -0.794746764500936, -0.878929134209951, -0.965287798643112, -0.991304729382197, -0.98487251996994, -0.932011248668035, -0.976086401939392, -0.82408589720726, -0.897422645489375, -0.982963007688522</t>
+    <t xml:space="preserve">0.769726878549336, 0.797823151904967, 0.503091011769293, 0.00478480822727565, 0.798691039232641, 0.670078445450044, 0.273714747359374, 0.433138797901869, 0.0535977706683576, 0.0274061273841392, 0.0673946636351, 0.400274417723789, -0.171283706710656, -0.07641292909107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.3672520955404, -93.9136047363281, -91.8282732645671, -94.1971605936686, -0.79502932826678, -0.880199770132701, -0.96464070280393, -0.991126211484273, -0.985315853357315, -0.936049600442251, -0.976329529285431, -0.82246502439181, -0.895997619628906, -0.982954096794128</t>
   </si>
   <si>
     <t xml:space="preserve">sobol</t>
   </si>
   <si>
-    <t xml:space="preserve">0.668529592779839, 0.843891357731092, 0.581737254840174, -0.0431832789579227, 0.804476221082725, 0.784951172457297, 0.48265204074035, 0.55398526641286, -0.0702126759461928, 0.0810659339296544, 0.162391775748, 0.487529800497382, -0.16310131298293, 0.0000651564974467992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-86.6547342936198, -94.1525446573893, -91.7278106689453, -94.1838020324707, -0.794782215356827, -0.881069026390711, -0.965412644545237, -0.991125792264938, -0.985072374343872, -0.934351688623428, -0.976327933867772, -0.82562358379364, -0.894739433129628, -0.983421109120051</t>
+    <t xml:space="preserve">0.795816163796916, 0.791832887167807, 0.545556389471079, 0.0831280752642355, 0.798250171708793, 0.673746077820035, 0.315949754136685, 0.440466885035741, 0.0336279550527902, 0.0249172169806141, 0.0827953905880021, 0.477648060490191, -0.200462721608209, -0.0855605453259365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.5431798299154, -93.8460632324219, -92.0412490844727, -94.2731152852376, -0.795014560222626, -0.88025882045428, -0.965007567405701, -0.991160726547241, -0.985006006558736, -0.935887422164281, -0.976720289389292, -0.82529793381691, -0.894257167975108, -0.982867727677027</t>
   </si>
   <si>
     <t xml:space="preserve">0.05</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85493918663287, 0.846104619394829, 0.668548301334627, -0.0389482362576502, 0.846286708503306, 0.847921198866677, 0.512530448247568, 0.585177078151609, -0.0780283285892981, 0.182250328031942, 0.231169076846216, -0.168718232797069, -0.383281751269477, 0.022753140676304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.9286847432454, -94.1814763387044, -92.2659088134766, -94.1877733866374, -0.796277052164078, -0.882369899749756, -0.965732409556707, -0.991312539577484, -0.984963359435399, -0.94151685833931, -0.978271057208379, -0.801549837986628, -0.881275675694148, -0.983641109863917</t>
+    <t xml:space="preserve">0.852599739633629, 0.781033972508578, 0.6531527559432, 0.0911734046398155, 0.84248123065681, 0.807680741123093, 0.269498543210278, 0.545203861461594, 0.0612618025399527, 0.109638870921905, 0.127698255504091, 0.483670001969814, -0.329110893733611, -0.0437764497754179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.9260882059733, -93.7243031819661, -92.5808751424154, -94.2809153238932, -0.796496198574702, -0.882415221134822, -0.964604079723358, -0.991654034455617, -0.985434766610463, -0.941407914956411, -0.977859602371852, -0.825518417358398, -0.886583642164866, -0.983262240886688</t>
   </si>
   <si>
     <t xml:space="preserve">0.10</t>
   </si>
   <si>
-    <t xml:space="preserve">0.837433930326317, 0.833653300781996, 0.684571777334452, -0.0110546113312117, 0.870643983735177, 0.825976021896891, 0.458259655118174, 0.60412784683814, -0.0663154615570961, 0.18243477673374, 0.213517047770052, 0.525192353957925, -0.314809571029129, 0.052877161356728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.8090512593587, -94.0187131245931, -92.3652303059896, -94.2139302571615, -0.797147889931997, -0.881916542847951, -0.965151592095693, -0.991425999005636, -0.985126733779907, -0.941529919703802, -0.977772345145543, -0.827005193630854, -0.88546266357104, -0.983933216333389</t>
+    <t xml:space="preserve">0.845903106584389, 0.817357260319097, 0.591808209051831, 0.013700484277844, 0.854061343041551, 0.692328945937917, 0.318646953687821, 0.57599431368792, 0.0400528290753707, 0.144099335171523, 0.151718334175624, 0.504587719521966, -0.374699444634805, 0.0566834035925335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.8809308369954, -94.1338559468587, -92.2732149759928, -94.2058044433594, -0.7968841056029, -0.880558011929194, -0.96503099600474, -0.991799056529999, -0.985105693340302, -0.943653370936712, -0.97846905986468, -0.826284285386403, -0.883864404757818, -0.984210753440857</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674162020949168, 0.682090167708985, 0.46133737608667, -0.0411438629034927, 0.663948212914193, 0.505325731739918, 0.40367029363053, 0.516928957349343, -0.0557662036018174, 0.0949863397414886, 0.146468873363699, 0.221884789860788, -0.0118037489540561, 0.0997822584593842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-86.6932271321615, -92.0374849955241, -90.9815121968587, -94.1857144673665, -0.789757963021596, -0.875292352835337, -0.964567365248998, -0.990903933842977, -0.985273877779643, -0.935337434212367, -0.975878073771795, -0.81587868531545, -0.903991089264552, -0.98438804546992</t>
+    <t xml:space="preserve">0.583483046448721, 0.711822037278699, 0.349768866910608, -0.0465315452142653, 0.66178082484279, 0.449897224601468, 0.249809809919665, 0.379608159098697, 0.0493209665969203, -0.0187334057013078, 0.0812809706319847, 0.251093302568735, 0.0397885422607235, -0.00411012491772302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-86.111355082194, -92.9439239501953, -91.0593195597331, -94.147408803304, -0.790443152189255, -0.876654766003291, -0.964433058102926, -0.990874083836873, -0.985249495506287, -0.933043132225672, -0.976681864261627, -0.817003001769384, -0.908587525288264, -0.983636758724848</t>
   </si>
   <si>
     <t xml:space="preserve">4</t>
   </si>
   <si>
-    <t xml:space="preserve">0.721689950235104, 0.786491765481421, 0.568859820145559, -0.00686404525765926, 0.771451495369993, 0.583728993192798, 0.437968744285575, 0.543322181983282, -0.119439650082567, 0.110302035170052, 0.162970542328205, 0.379473405483144, -0.101153221652507, -0.0270124905826004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.0180399576823, -93.402219136556, -91.6479899088542, -94.2178599039714, -0.793601493040721, -0.876912055412928, -0.964934434493383, -0.991061951716741, -0.98438574274381, -0.936421984434128, -0.976344285408656, -0.82165965239207, -0.898527481158574, -0.983158542712529</t>
+    <t xml:space="preserve">0.732244801412657, 0.685955774431925, 0.406849204414663, 0.154160220382859, 0.742423401269515, 0.561657403080322, 0.224198765674347, 0.376323765452351, 0.0841019005969441, 0.00831694961491698, 0.117886395951427, 0.379952529043939, 0.000809086632464821, 0.0407851828439748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.1144994099935, -92.652276357015, -91.3455935160319, -94.3419817606608, -0.793144492308299, -0.878454148769379, -0.964210593700409, -0.990858614444733, -0.985789148012797, -0.934805742899577, -0.977610647678375, -0.821720971663793, -0.906262503067652, -0.984060647090276</t>
   </si>
   <si>
     <t xml:space="preserve">10</t>
   </si>
   <si>
-    <t xml:space="preserve">0.71853752454559, 0.713619535720876, 0.518419275895183, -0.000832038358370448, 0.679057984782471, 0.586153155180597, 0.36275950743687, 0.391941692188905, -0.0866964968800182, 0.16629700236349, 0.142047813995821, 0.271922328549033, -0.131407074418897, 0.0242562478011664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-86.9964958190918, -92.4496358235677, -91.3353342692057, -94.2235163370768, -0.790298177798589, -0.876962135235469, -0.964129529396693, -0.990155627330144, -0.984842453400294, -0.94038715561231, -0.975753168265025, -0.817714258035024, -0.896677496035894, -0.983655685186386</t>
+    <t xml:space="preserve">0.745567958138634, 0.721854508228844, 0.356911191985304, 0.075347417315717, 0.728883673370126, 0.397138528551452, 0.314973300194702, 0.208513016719436, 0.0283779568455183, 0.0833280507218438, 0.11516059664073, 0.282851686906574, -0.316683336382811, -0.0566133302975057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.2043413798014, -93.0570421854655, -91.0951403299967, -94.2655718485514, -0.792690942684809, -0.875805330276489, -0.964999085664749, -0.990068231026332, -0.984924548864365, -0.939693492650986, -0.977541486422221, -0.818165783087413, -0.887324913342794, -0.98314103881518</t>
   </si>
   <si>
     <t xml:space="preserve">jack</t>
   </si>
   <si>
-    <t xml:space="preserve">0.759777459547906, 0.823535844453954, 0.581970376993228, 0.0518315420643206, 0.87389234656398, 0.891418874340959, 0.606650504334916, 0.587566747981603, -0.0317416431744126, 0.139159194492822, 0.201416747451379, 0.0685261685981519, -0.19308879948713, -0.0923917085694008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.2783355712891, -93.8864580790202, -91.7292556762695, -94.2729008992513, -0.79726402759552, -0.883268501361211, -0.966739702224731, -0.991326846679052, -0.985608979066213, -0.938465446233749, -0.977430482705434, -0.810252890984217, -0.892905735969543, -0.982524573802948</t>
+    <t xml:space="preserve">0.782397629662081, 0.73565067543289, 0.559118455562523, 0.128412333426162, 0.848731905332992, 0.806960443349001, 0.554855485274022, 0.513170688495189, 0.0337466591269921, 0.137861706811306, 0.0800219034927519, 0.114262775726861, -0.214225321866751, -0.147568888046217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.4526947021484, -93.2125968933105, -92.1092666625977, -94.3170188903809, -0.796705581744512, -0.88240362405777, -0.967082766691844, -0.991503159205119, -0.98500784834226, -0.943246924877167, -0.976649918158849, -0.81199317574501, -0.89343626499176, -0.982282263040543</t>
   </si>
   <si>
     <t xml:space="preserve">law_of_total_variance</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806514817107774, 0.766748885460771, 0.641025322268192, 0.0571364645963413, 0.907383704203925, 0.869858489567994, 0.554093408475353, 0.718059446065194, -0.0490752733569658, 0.256007559310469, 0.272417904632916, 0.108676100209603, -0.211703148414782, -0.396636900255539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.597745513916, -93.1441408793132, -92.0953076680501, -94.2778755187988, -0.798461433251699, -0.882823093732198, -0.966177225112915, -0.992108114560445, -0.985367204745611, -0.946739828586578, -0.979436435302099, -0.811725747585297, -0.891767491896947, -0.979574370384216</t>
+    <t xml:space="preserve">0.741915406913629, 0.765748020618129, 0.476081732420882, 0.01860175842551, 0.884118508132292, 0.854997283303825, 0.417292361152053, 0.612601424530922, 0.0663120398456576, 0.201588631441994, 0.165585926261987, 0.164595935231551, -0.22192177094907, -0.345835699797573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.179711151123, -93.5519508361816, -91.6928141276042, -94.2105562845866, -0.797890951236089, -0.883177036046982, -0.965887856483459, -0.991971474885941, -0.985513124863307, -0.947399393717448, -0.97882091999054, -0.813836042086283, -0.892977192004522, -0.980410285790761</t>
   </si>
   <si>
     <t xml:space="preserve">PI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.749933883346001, 0.889630509968841, 0.768610344157551, 0.031377175354536, 0.877364550455401, 0.903212019442529, 0.524895950116192, 0.701881968695044, -0.0587623296054797, 0.0483351274107316, 0.201394454741061, 0.582431568937351, 0.19566398744056, 0.204317662922442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.2110631306966, -94.7504453023275, -92.8861432393392, -94.2537200927734, -0.797388168176015, -0.883512131373088, -0.96586474776268, -0.992011258999507, -0.985232086976369, -0.932033922274907, -0.977429852883021, -0.829104952017466, -0.91667748093605, -0.985401703914006</t>
+    <t xml:space="preserve">0.794693998988451, 0.853758160112869, 0.760448780985481, 0.0530030108013874, 0.847566183509546, 0.821694278081324, 0.46585704933868, 0.568797416693281, 0.0366032400193994, -0.0110559188742184, 0.104204621784175, 0.570155756613127, -0.0628730929463292, 0.181229110845663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.5356127421061, -94.544283803304, -93.1189949035645, -94.2439086914062, -0.796666532754898, -0.882640844583511, -0.966309702396393, -0.991765159368515, -0.985052170356115, -0.933543399969737, -0.977263502279917, -0.828684951861699, -0.902464028199514, -0.985386677583059</t>
   </si>
   <si>
     <t xml:space="preserve">Mean</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571595749585731, 0.341906505744956, 0.615237548273761, 0.0990502613001982, 0.912489592196368, 0.902180168535315, 0.641716415125747, 0.650320386993129, -0.129669552969846, 0.0322448821096701, 0.16372603313879, 0.518333893173043, -0.0403832762926805, 0.329874233617158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-85.9922742207845, -87.59061571757, -91.9354621887207, -94.3171796162923, -0.798643982410431, -0.883490814765294, -0.967114984989166, -0.991702556610107, -0.984243053197861, -0.930894523859024, -0.97636562983195, -0.826753598451614, -0.902243487040202, -0.986619200309118</t>
+    <t xml:space="preserve">0.556537551903656, 0.298271557901213, 0.57189855893413, 0.218928387623726, 0.878364098567371, 0.89008431198357, 0.433169515972503, 0.580236690633878, 0.0146767919833596, -0.0786815174977704, 0.0692367902879031, 0.430455809087309, 0.0214118831543048, 0.336123078166256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-85.9296536763509, -88.2810546875, -92.1733624776204, -94.4047752380371, -0.797698191801707, -0.88374195098877, -0.966025769710541, -0.991819037993749, -0.98471196492513, -0.92913689215978, -0.976376269261042, -0.823570066690445, -0.907491405804952, -0.986849141120911</t>
   </si>
   <si>
     <t xml:space="preserve">CB</t>
@@ -236,1033 +236,1033 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830015878044239, 0.789501469833444, 0.787917182801246, 0.00228241030774352, 0.904372074971638, 0.91466403534586, 0.565565953582202, 0.72355193674098, -0.0953890227606671, -0.0133073537682901, 0.199150907935687, 0.618914505271931, -0.0160987830882857, 0.177082042070155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.7583552042643, -93.4415618896484, -93.0058166503906, -94.2264368693034, -0.798353759447734, -0.88374871412913, -0.966300006707509, -0.992140998442968, -0.984721207618713, -0.927668833732605, -0.977366467316945, -0.830443288882573, -0.903728453318278, -0.985137605667114</t>
+    <t xml:space="preserve">0.76060802136454, 0.708242412921149, 0.787563177298953, 0.166502460211374, 0.909607863373177, 0.899047496585756, 0.53117493324474, 0.65088658802295, 0.0759547290576453, -0.10432506687726, 0.102647682177894, 0.644437492504654, 0.141502490198114, 0.171630963305812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.3057609558105, -92.9035629272461, -93.2549812316895, -94.3539477030436, -0.798744785785675, -0.883886261781057, -0.966877071062724, -0.99215179681778, -0.985662738482157, -0.927465949455897, -0.977223998308182, -0.831404656171799, -0.914654495318731, -0.985296054681142</t>
   </si>
   <si>
     <t xml:space="preserve">3</t>
   </si>
   <si>
-    <t xml:space="preserve">0.671964384120441, 0.685643304412659, 0.373743798999958, 0.000727355566240877, 0.711966788832685, 0.620572581560356, 0.369016145437956, 0.401356015672741, -0.164584092727487, 0.0944716004833248, 0.10575253896039, 0.188809582173973, -0.306710711000701, -0.331430408455522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-86.6782081604004, -92.0839314778646, -90.4385635375977, -94.2249786376953, -0.791474755605062, -0.87767319281896, -0.964196489254634, -0.990211991469065, -0.983756055434545, -0.935300983985265, -0.974727739890417, -0.81466535727183, -0.885957898696264, -0.98020666440328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444999297993149, 0.51168619823458, 0.197394234259778, -0.12222095662714, -0.0922404673187903, -0.426536524002142, 0.134930036559234, 0.199946107154504, -0.22410976925955, 0.0829351394304801, 0.0644199552809756, 0.0736997483375069, -0.162240382652457, -0.380897508214835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-85.1270955403646, -89.8099700927734, -89.3454610188802, -94.1096855163574, -0.762722194194794, -0.856041371822357, -0.961691250403722, -0.9890061378479, -0.982925774653753, -0.934484052658081, -0.973559995492299, -0.810442678133647, -0.894792077938716, -0.979726992050807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818204747620446, 0.733628849925318, 0.727768467114758, 0.0853110516281504, 0.914527723977069, 0.92471344954999, 0.590619238595624, 0.696335386062284, -0.0569701237778606, 0.0477522650238845, 0.196350605964398, 0.67004446257499, 0.19656111343047, 0.204155796151915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.6776362101237, -92.7111968994141, -92.6329849243164, -94.3042958577474, -0.79871685107549, -0.883956321080526, -0.966568132241567, -0.991978051265081, -0.985257085164388, -0.931992648045222, -0.977287352085114, -0.832318935791651, -0.91673233906428, -0.985400134325027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590631019876231, 0.653536419150249, 0.423420193285421, 0.00387977208442704, 0.703562357157528, 0.653833399693388, 0.41821249363465, 0.351559225549196, -0.183805222466694, 0.0897781750442295, 0.106150080573743, 0.281536478928447, -0.269579682940974, -0.313904335099554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-86.1223640441895, -91.6642313639323, -90.7464825948079, -94.227934773763, -0.791174274682999, -0.87836031516393, -0.964722998936971, -0.989913854996363, -0.983487953742345, -0.934968628485997, -0.974738971392314, -0.818066942691803, -0.88822841445605, -0.980376611153285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347519292350302, 0.49322037354014, 0.195909547291707, -0.0817778717933969, -0.283801903771575, -0.220356286221531, 0.194879923305951, 0.132918871688235, -0.161801060025219, 0.00694412607200502, -0.00490861571058101, 0.0693797932777764, -0.31635714666563, -0.218222633195438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-84.4609029134115, -89.5685854593913, -89.3362581888835, -94.1476104736328, -0.755873360236486, -0.860300769408544, -0.962332846721013, -0.988604841629664, -0.983794873952866, -0.929102901617686, -0.971601297458013, -0.810284205277761, -0.885368031263351, -0.981304417053858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.737904540985203, 0.806795840132641, 0.599960539090668, -0.00136277469061461, 0.036246858903606, -0.158879938294758, 0.234800474288123, 0.407419292643139, -0.190714801252744, 0.118865348126863, 0.114658582218797, 0.183604318503549, -0.200035604312045, -0.17476488851588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.1288528442383, -93.6676333109538, -91.8407676696777, -94.2230186462402, -0.76731595993042, -0.861570785442988, -0.962760084867477, -0.990248292684555, -0.983391577005386, -0.937028378248215, -0.974979356924693, -0.814474407831828, -0.89248094757398, -0.981725817918777</t>
+    <t xml:space="preserve">0.642436166057461, 0.604159691042506, 0.20953107134267, -0.0367208652893611, 0.757324462601881, 0.578279906209489, 0.156780899655076, 0.305586548581563, -0.102026599956751, 0.0396955398507168, -0.0215776653908833, 0.327422562595942, -0.280341623090403, -0.353359635719851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-86.5088933308919, -91.7300081888835, -90.3559875488281, -94.1569203694661, -0.793643643458684, -0.878721777598063, -0.963624984025955, -0.990525444348653, -0.98290122350057, -0.936850382884343, -0.974072049061457, -0.819797672828039, -0.889492601156235, -0.980339246988297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405789578428455, 0.379222976611501, -0.013440976215634, -0.00488002698655794, -0.344875841788289, -0.822789594689685, 0.0397562456226118, -0.132317277656883, -0.00278884145845891, -0.109582919452548, -0.123195322744519, 0.0777946843165086, -0.22674637885433, -0.30748940430753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-84.9131156921387, -89.1937990824381, -89.2377199808757, -94.1877904256185, -0.756722478071849, -0.856164008378983, -0.962608476479848, -0.98846293091774, -0.984440972407659, -0.927123345931371, -0.971493721008301, -0.810657956202825, -0.892689416805903, -0.980772340297699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799454421610313, 0.775521559406764, 0.727203778693748, 0.0935777438872034, 0.902790282764942, 0.909204596035351, 0.465209282282299, 0.576025951181302, 0.0533925035368105, -0.0575059749918668, 0.106087153850488, 0.608854027895423, -0.0420829640563971, 0.155913502198074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.5677136739095, -93.6621495564779, -92.9522618611654, -94.2832463582357, -0.79851641257604, -0.884049795071284, -0.966304075717926, -0.991799205541611, -0.985312668482463, -0.930516697963079, -0.977311267455419, -0.830101825793584, -0.903704104820887, -0.985147655010223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604847359752309, 0.602645591994594, 0.287828048725383, 0.028958569084972, 0.714071936199058, 0.54088451875605, 0.199722914896817, 0.234444793628698, -0.0411796854431443, 0.00659760822255997, 0.00768478076851528, 0.290432496875691, -0.278275137886978, -0.211176080301872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-86.2554209391276, -91.7129364013672, -90.7486689249674, -94.2205973307292, -0.792194783687592, -0.878119697173437, -0.96399798989296, -0.990190368890762, -0.983845309416453, -0.934693710009257, -0.974814520279566, -0.818443342049917, -0.889615861574809, -0.981681702534358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494988462124324, 0.4158953266286, 0.0733961841172501, -0.0316524992695018, -0.376677852946098, -0.696875324316035, -0.020958420765919, -0.0858143807170579, -0.101924670676208, -0.0519650415219444, -0.135335426793158, 0.111263444813381, -0.308508063902318, -0.30421342515949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-85.5146100362142, -89.6072875976563, -89.6732327779134, -94.1618342081706, -0.755657184123993, -0.85819127758344, -0.962081092596054, -0.988681958119075, -0.982902805010478, -0.930877747138341, -0.971185692151388, -0.811883360147476, -0.887812546888987, -0.980803271134694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813417915633649, 0.809585641553038, 0.5011666056231, 0.0360711218553183, -0.17635887197701, -0.322838893809222, -0.0226000253434797, 0.320848053556032, -0.0155746916254924, -0.016490712254285, 0.0445351443311, 0.170498873731484, -0.198387542637346, -0.242618367578389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.661873626709, -94.0462292989095, -91.8186218261719, -94.2274930318197, -0.762367407480876, -0.864213411013285, -0.962066833178202, -0.990597325563431, -0.984242590268453, -0.93318926692009, -0.975749518473943, -0.814052168528239, -0.894380946954091, -0.981384833653768</t>
   </si>
   <si>
     <t xml:space="preserve">RS</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786611052888601, 0.872686054618872, 0.697964443989304, -0.0054760490652955, 0.859124115701376, 0.8442297520057, 0.565732663597187, 0.635546313832263, -0.0859268825034011, 0.154707092150783, 0.198523688114442, 0.697587710057687, -0.174399232470071, 0.148402938435047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.4617202758789, -94.5289479573568, -92.4482447306315, -94.2191614786784, -0.79673602382342, -0.882293639580409, -0.96630179087321, -0.991614103317261, -0.984853188196818, -0.939566439390182, -0.977348746856054, -0.833329329888026, -0.894048579533895, -0.984859510262807</t>
+    <t xml:space="preserve">0.807017672879474, 0.829573535346734, 0.556754160524909, 0.023974142467155, 0.825180694593217, 0.691143422430008, 0.493652935011463, 0.527564060651248, 0.0848156616644692, -0.023899784484706, 0.0988255336529193, 0.52854780007282, -0.21410171048375, 0.0754127538026511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.6187149047852, -94.2715970357259, -92.0974090576172, -94.2157648722331, -0.795916670560837, -0.880538924535116, -0.966551144917806, -0.991570951541265, -0.985800222555796, -0.932706489165624, -0.977127019564311, -0.827161544561386, -0.893443638086319, -0.984387590487798</t>
   </si>
   <si>
     <t xml:space="preserve">LS</t>
   </si>
   <si>
-    <t xml:space="preserve">0.815036134653888, 1.03250228565317, 0.866018601851323, 0.127416043587111, 0.796945369721469, 0.826591343185389, 0.692737291192446, 0.835205700429479, 0.0419147116851968, 0.166978261707624, 0.240956420564294, 0.517940416661561, -0.0142872780607441, 0.113414923747377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.6559814453125, -96.6180603027344, -93.4899281819661, -94.3437792460124, -0.794512967268626, -0.88192925453186, -0.967661021153132, -0.992809476455053, -0.986636358499527, -0.94043539762497, -0.9785475730896, -0.826739164193471, -0.90383922457695, -0.984520238637924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889381767700522, 0.889124800573187, 0.849151914572094, 0.00929344539275869, 0.901923215958108, 0.928422592428016, 0.746633265256968, 0.773064992979678, -0.00927554117650416, 0.28871589193068, 0.271477813303128, 0.212859039869643, 0.22226815453571, 0.207397844139472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.1640703837077, -94.7438346862793, -93.3853800455729, -94.2330113728841, -0.798266206185023, -0.884032946825027, -0.968237827221552, -0.992437436183294, -0.985922342538834, -0.949056003491084, -0.979409875472387, -0.815547585487366, -0.918304292360942, -0.985431571801504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759495875351571, 0.822811481988446, 0.60482077903663, -0.0162977005041381, 0.810001616568147, 0.735968597263651, 0.452224678317415, 0.560556941408468, -0.108185019113582, 0.073826869501505, 0.161337196934306, 0.431086420873736, -0.120962774648784, -0.079114535492638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.2764111836751, -93.8769892374674, -91.8708938598633, -94.2090136210124, -0.794979763031006, -0.880057114362717, -0.965087004502614, -0.991165137290955, -0.984542725483576, -0.933839068810145, -0.976298139492671, -0.823553019762039, -0.897316151857376, -0.982653319835663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.719577417550293, 0.792966612246261, 0.614402665716122, 0.104897310520089, 0.801151892332225, 0.753783196862409, 0.580459395622343, 0.627028987647476, -0.0813782806361842, 0.296034751325047, 0.182321036829042, 0.0709866831083613, -0.207890062410225, -0.0109950565069344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.0036026000977, -93.4868581136068, -91.9302871704102, -94.3226626078288, -0.794663361708323, -0.880425139268239, -0.966459399461746, -0.991563109556834, -0.984916633367538, -0.949574273824692, -0.976890983184179, -0.810343152284622, -0.892000657320023, -0.983313860495885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.879332259564889, 0.904863327532027, 0.839889186151771, 0.0591810334307071, 0.883130124955881, 0.930820979782291, 0.758944372877936, 0.776172791612923, 0.025685862014398, 0.305361924322387, 0.275449361616249, 0.21179668036892, -0.0324012236212389, 0.181986810112001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.0953905741374, -94.9495681762695, -93.327965037028, -94.2797927856445, -0.797594302892685, -0.884082494179408, -0.968369583288828, -0.992456042766571, -0.98640999396642, -0.950234758853912, -0.979522081216176, -0.81550861398379, -0.90273157954216, -0.985185166200002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.893409162229527, 0.884403283340722, 0.831691016074514, 0.0211925702337669, 0.901313710303983, 0.924953884564255, 0.759575568925761, 0.777699976803545, -0.0413663098066035, 0.302315855299067, 0.275851403966069, 0.12787147134434, 0.293230914563265, 0.0998822470467463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.1915941874186, -94.6821151733398, -93.2771486918132, -94.2441696166992, -0.798244414726893, -0.883961288134257, -0.968376338481903, -0.99246518611908, -0.985474731524785, -0.950019057591756, -0.979533439874649, -0.812429908911387, -0.922643576065699, -0.984389015038808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870235642471355, 0.91620389088459, 0.87304246318787, 0.015836391101436, 0.916413257059172, 0.931561519626218, 0.788605945978146, 0.776298563709234, 0.0258025220503906, 0.209509567904646, 0.3269303324673, 0.480319891800183, -0.0676840636197549, 0.303787661941011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.0332229614258, -95.0978116353353, -93.5334655761719, -94.2391469319661, -0.798784263928731, -0.8840977927049, -0.968687027692795, -0.992456795771917, -0.986411621173223, -0.94344716668129, -0.980976541837057, -0.825359096129735, -0.900574078162511, -0.986366244157155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92054428546885, 0.903993150958633, 0.880108173274173, 0.0929599466280663, 0.91293449575827, 0.927391222390835, 0.763584963350706, 0.806910629135951, -0.000286735839371639, 0.275367574501815, 0.333126369779808, 0.330085251980402, 0.146213633475277, 0.291396043525323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.3770395914714, -94.9381932576497, -93.5772623697917, -94.3114685058594, -0.7986598889033, -0.884011640151342, -0.968419247865677, -0.992640072107315, -0.986047720909119, -0.948110769192378, -0.981151594718297, -0.819847901662191, -0.913653653860092, -0.986246085166931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.719112563608096, 0.837650708462016, 0.759443498607994, 0.0242416599545052, 0.846526831947095, 0.814491306831618, 0.662375647416847, 0.651219043554674, -0.0488093340563685, 0.275486846091615, 0.246337894900076, 0.19704745841253, 0.542171111178478, 0.250414655540302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.0004257202148, -94.0709671020508, -92.8293225606283, -94.2470288594564, -0.796285637219747, -0.881679284572601, -0.967336084445318, -0.991707936922709, -0.985370914141337, -0.948119215170542, -0.978699612617493, -0.814967554807663, -0.937865956624349, -0.985848697026571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828477826239967, 0.880226171202456, 0.779027154422869, 0.0122647010167406, 0.853364265041375, 0.905938937200288, 0.700786897261139, 0.733561603604217, -0.0505458450438435, 0.271270535069016, 0.217842255515959, 0.185963715237168, 0.325457755685213, 0.217278683560057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.7478439331055, -94.627512105306, -92.9507118225098, -94.2357976277669, -0.796530093749364, -0.883568465709686, -0.967747169733048, -0.992200926939646, -0.985346692800522, -0.947820645570755, -0.977894542614619, -0.814560959736506, -0.92461420694987, -0.985527384281158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75062238219635, 0.869057316364398, 0.775379666627935, 0.0445631391820296, 0.862159196008247, 0.870080940043194, 0.695284538537202, 0.761965522516722, -0.051966704456535, 0.288453892846808, 0.246251466695086, 0.197111205398631, 0.199820152411018, 0.286515657946381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.2157684326172, -94.4815132141113, -92.9281028747559, -94.2660850524902, -0.796844536066055, -0.88282768925031, -0.967688282330831, -0.992370982964834, -0.985326874256134, -0.949037450551987, -0.978697170813878, -0.81496989329656, -0.916931625207265, -0.986198761065801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.837327131509946, 0.892166138512859, 0.832713684639638, 0.0495114351034625, 0.912822741940761, 0.888227243787628, 0.712210803143121, 0.771949304885188, -0.0299631117832433, 0.302869369748268, 0.267965902701821, 0.172085774304899, 0.284300171708439, 0.396503513840711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.8083213806152, -94.7835909525553, -93.283487701416, -94.2707252502441, -0.798655893405279, -0.883202566703161, -0.967869430780411, -0.992430756489436, -0.985633786519369, -0.95005825360616, -0.979310655593872, -0.814051862557729, -0.922097472349803, -0.987265290816625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875987521581645, 0.923431971113749, 0.898803691945936, 0.0250967502230705, 0.926236756603016, 0.939492028136659, 0.782501166320335, 0.832732071917773, -0.0136866864689541, 0.301760545182551, 0.357726340454698, 0.233457765428198, 0.118686996930288, 0.199204312130727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.0725321451823, -95.1922968546549, -93.6931465148926, -94.2478307088216, -0.799135480324427, -0.884261626005173, -0.968621693054835, -0.992794666687647, -0.985860814650854, -0.949979734420776, -0.981846602757772, -0.816303227345149, -0.911970434586207, -0.985352120796839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.898244320489187, 0.89634149971454, 0.852011579138775, 0.0207461767729118, 0.903592298956073, 0.911079053109199, 0.773199007388506, 0.795636936112117, -0.0498540040245574, 0.282119788629755, 0.28526413169718, 0.236796331033272, 0.376372766684763, 0.177446754540466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.2246383666992, -94.8381711324056, -93.4031056722005, -94.2437510172526, -0.798325880368551, -0.883674653371175, -0.96852213939031, -0.992572575807571, -0.985356342792511, -0.948588913679123, -0.979799371957779, -0.81642569899559, -0.927727595965068, -0.985141142209371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795679388762468, 0.927502626307605, 0.84704696348754, 0.182939688066991, 0.907905629541593, 0.934780944467196, 0.706712899920702, 0.77626836513202, -0.0463415256027464, 0.200656423020611, 0.241409236847395, 0.452468633179037, 0.0264393046391406, 0.348833749918273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.5236946105957, -95.2455083211263, -93.3723325093587, -94.3958457946777, -0.798480093479156, -0.884164301554362, -0.96781059106191, -0.992456614971161, -0.985405335823695, -0.942820249001185, -0.97856036623319, -0.824337402979533, -0.906329603989919, -0.986803046862284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850229209982366, 0.918266747095616, 0.89610502198126, 0.101066625444433, 0.916674997725742, 0.945250831424272, 0.71608281960471, 0.793691616775433, -0.0167348038195523, 0.287485270618005, 0.264020303947397, 0.318629100753702, 0.0881399723190911, 0.298391966326755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.8964960734049, -95.1247772216797, -93.6764188130697, -94.3190704345703, -0.798793621857961, -0.884380594889323, -0.96791086991628, -0.992560929059982, -0.985818298657735, -0.948968859513601, -0.979199182987213, -0.819427645206451, -0.910102522373199, -0.986313923199971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.874172797582347, 0.917333789718198, 0.862425886684745, 0.00221867855603737, 0.907800822132431, 0.902396752396168, 0.729987140308747, 0.818557324366274, -0.0299588385218518, 0.308453305888054, 0.253630564782658, 0.206937990159885, 0.313403366410772, 0.253113118031366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.0601300557454, -95.1125816345215, -93.4676587422689, -94.2263771057129, -0.798476346333822, -0.883495289087296, -0.968059676885605, -0.992709801594416, -0.985633846124013, -0.950453668832779, -0.978905647993088, -0.815330378214518, -0.923877096176147, -0.985874863465627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826991908631422, 0.847870828038533, 0.741430729980049, 0.0761426289483375, 0.887374825026917, 0.892929094752546, 0.729491094473509, 0.729261790802207, -0.0263573338210553, 0.268290204303731, 0.278284403647151, 0.13521542744222, 0.221311276465274, 0.0933879063393231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.7376889546712, -94.2045641581217, -92.7176704406738, -94.2956982930501, -0.797746062278748, -0.883299700419108, -0.968054368098577, -0.992175183693568, -0.98568408091863, -0.947609599431356, -0.979602177937826, -0.812699313958486, -0.918245780467987, -0.984326040744781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855613693721913, 0.91492132983556, 0.902424019081717, 0.154560345832898, 0.933218841704743, 0.933607910119612, 0.762488724332353, 0.815967879333145, -0.00152954269407644, 0.290524802290013, 0.260459166540967, 0.284448096792291, 0.199827170599921, 0.296733139270753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.9332944234212, -95.0810460408529, -93.7155871073405, -94.3692334493001, -0.79938510855039, -0.884140068292618, -0.968407515684764, -0.99269429842631, -0.986030385891597, -0.949184097846349, -0.979098572333654, -0.818173752228419, -0.916932054360708, -0.986297837893168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867602363223375, 0.906612279722937, 0.867537793523847, 0.0437937477795654, 0.903279043725193, 0.957076579513772, 0.756376704484578, 0.814028865193915, -0.0374354790945578, 0.318139949035593, 0.248721808424051, 0.258182659541584, 0.0321228679530015, 0.222072193808982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.0152267456055, -94.9724304199219, -93.4993448893229, -94.2653635660807, -0.798314680655797, -0.884624898433685, -0.968342103560766, -0.992682689428329, -0.985529559850693, -0.951139609018962, -0.978766963879267, -0.817210233211517, -0.906677146752675, -0.985573865969976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878194610291681, 0.900600224952551, 0.804605807753078, 0.0471910569436619, 0.867302650177038, 0.894927590591095, 0.756082270092866, 0.743352911524508, -0.0630420008891204, 0.295494844667202, 0.198009549296963, 0.129771153194343, 0.139016838162285, 0.175135133141516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.0876157124837, -94.8938410441081, -93.1092610677083, -94.2685493469238, -0.797028428316116, -0.883340986569722, -0.968338952461879, -0.992259548107783, -0.985172392924627, -0.949536041418711, -0.977334221204122, -0.812499596675237, -0.913213578859965, -0.985118726889292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.861205746728956, 0.90252442644084, 0.832924692600417, 0.00538194303196494, 0.909210665170835, 0.91423327197431, 0.733527964491125, 0.815943322248375, -0.0134092093625948, 0.279197340078008, 0.262312626077768, 0.190187426971238, 0.2538635211144, 0.157122435000717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.971511332194, -94.918994140625, -93.2847956339518, -94.2293434143066, -0.798526751995087, -0.883739815155665, -0.968097571531932, -0.99269415140152, -0.985864684979121, -0.948381966352463, -0.97915093700091, -0.8147159020106, -0.920236309369405, -0.984944061438243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922618191961536, 0.974723596177838, 0.924094491522919, 0.013403736579058, 0.931130529070132, 0.947818004158553, 0.859720948227248, 0.882978522174577, -0.0291274042971029, 0.318050137612647, 0.319956160013844, 0.269109932841975, 0.153963468572208, 0.40208955658133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.3912129720052, -95.8627792358398, -93.8499114990234, -94.2368657430013, -0.799310445785522, -0.884433629115423, -0.969448115428289, -0.993095495303472, -0.985645443201065, -0.951133249203364, -0.980779504776001, -0.817611088355382, -0.914127546548843, -0.987319457530975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980662790477435, 1.16720845184094, 0.991810035559949, 0.367488399465204, 0.96179886635727, 1.00268210067109, 0.967382387291119, 0.985201369754401, 0.103054683928938, 0.599433281784588, 0.460256281779862, 0.136787004583816, 0.422634296050147, 0.422707695043801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.7878982543945, -98.3789347330729, -94.2696461995443, -94.5689038594564, -0.800406920909882, -0.885567045211792, -0.97060033082962, -0.993707509835561, -0.987489155928294, -0.971058831612269, -0.984743318955104, -0.812756965557734, -0.930556430419286, -0.987519387404124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962819015413901, 1.16763488271896, 0.961695757291692, 0.419509509590958, 0.964569483005496, 0.987007468873274, 0.980215716818706, 1.0139358137538, 0.0493205585608505, 0.674892749561141, 0.464385426193374, 0.288693418592167, 0.442948866222955, 0.449462837950644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.6659512837728, -98.3845090230306, -94.0829828898112, -94.617685953776, -0.800505977869034, -0.885243229071299, -0.970737675825755, -0.993879544734955, -0.986739657322566, -0.976402342319489, -0.984859977165858, -0.818329487244288, -0.931798640886943, -0.987778826554616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825685613979886, 1.02158502094762, 0.843574583990603, 0.141470115232435, 0.756257922031397, 0.745407595053573, 0.727732656542641, 0.768767834997652, -0.0341057538182626, 0.0984323936587562, 0.22083496397126, 0.548166995222707, 0.123510702136981, 0.124736787215013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.7287615458171, -96.475350189209, -93.3508089701335, -94.3569582621256, -0.793058282136917, -0.880252110958099, -0.9680355489254, -0.992411708831787, -0.985576003789902, -0.93558145960172, -0.977979093790054, -0.827847993373871, -0.912265398104986, -0.984630024433136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70946219279107, 0.996301730108223, 0.875969208838717, 0.405984275885266, 0.727459280015332, 0.782088457003477, 0.942899963409183, 0.677592025186306, -0.0723936061183974, 0.523891802514977, 0.355553750572704, 0.0827472167155879, 0.0225822249874728, 0.116017905333291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-86.9344736735026, -96.144847869873, -93.5516070048014, -94.6050028483073, -0.792028653621674, -0.881009886662165, -0.970338314771652, -0.991865833600362, -0.98504195412, -0.965709513425827, -0.981785221894582, -0.810774574677149, -0.906093748410543, -0.984545479218165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.989129964372738, 1.16389157484723, 0.991743036532153, 0.338814806377517, 0.953491239828857, 0.939702649209153, 0.969441942865976, 1.00950093698557, 0.126610182697593, 0.583574873968004, 0.3340587957928, 0.362537992282979, 0.275192934399332, 0.470629684275779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.8457641601562, -98.3355766296387, -94.2692309061686, -94.5420155843099, -0.800109901030858, -0.884265977144241, -0.970622372627258, -0.993852992852529, -0.987817714611689, -0.969935850302378, -0.981177937984467, -0.821038395166397, -0.921540576219559, -0.987984077135722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.970034894187496, 1.16216022929643, 1.00057816919761, 0.389296862499431, 0.943750152473659, 1.0102783083377, 0.958095265676906, 1.00554260040283, 0.0276457221306087, 0.612016139906725, 0.386726835887328, 0.152218162225836, 0.443066973244552, 0.46761486445091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.7152656555176, -98.312944539388, -94.3239954630534, -94.5893544514974, -0.799761631091436, -0.885723972320557, -0.970500938097636, -0.993829294045766, -0.986437330643336, -0.971949861447016, -0.98266593615214, -0.813323040803274, -0.931805862983068, -0.987954843044281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.984828428073625, 1.16840379679315, 1.01078544851685, 0.338914065190814, 0.9792754740493, 0.996946379144847, 1.00712564644221, 1.04106674648829, 0.283381756507007, 0.487396070844237, 0.488434056650912, 0.769155915162451, 0.0808842372159531, 0.412116076095391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.8163668314616, -98.3945602416992, -94.3872652689616, -94.5421086629232, -0.801031756401062, -0.8854485531648, -0.971025671561559, -0.994041979312897, -0.990004408359528, -0.96312514146169, -0.985539408524831, -0.835954731702805, -0.909658843278885, -0.987416682640711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934095231871957, 1.16600925482824, 0.998712043183971, 0.353107804292004, 0.986907242831039, 0.983568190255256, 0.998262540055412, 1.03005554878949, 0.170890287005061, 0.660091540875027, 0.522069677729688, 0.465612969245784, 0.161765095303917, 0.521201166178357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.4696487426758, -98.3632588704427, -94.3124282836914, -94.5554186503092, -0.801304612557093, -0.885172178347906, -0.970930816729863, -0.993976054588954, -0.988435345888138, -0.975354224443436, -0.986489695310593, -0.824819588661194, -0.914604606231054, -0.988474458456039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832967283801337, 1.04580531818584, 0.876683591613969, 0.203772377302831, 0.874232276002917, 0.825581804647502, 0.888143706260659, 0.950124228982234, 0.000807788845049442, 0.466874848104782, 0.339870371757322, 0.427708426376667, 0.643877600056226, 0.411924909390445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.7785255432129, -96.7919570922852, -93.5560351053874, -94.4153813680013, -0.79727618098259, -0.881908398866653, -0.969752301772436, -0.993497500816981, -0.986062987645467, -0.96167197227478, -0.981342128912608, -0.823429101705551, -0.94408518075943, -0.987414828936259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.940114256871699, 1.12653431168407, 0.942296646257606, 0.359540372030716, 0.895866170163329, 0.931774448874851, 0.898985055319683, 1.00975779081814, 0.0295592885817495, 0.615780307511394, 0.360838951342473, 0.149362654708295, 0.599824200866288, 0.385206647519915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.5107836405436, -97.847243754069, -93.9627375284831, -94.5614507039388, -0.798049650589625, -0.884102191527685, -0.969868328173955, -0.993854530652364, -0.986464021603266, -0.972216413418452, -0.981934541463852, -0.813218289613724, -0.941391370693843, -0.987155747413635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.693207933909176, 1.0083779591947, 0.823238348159277, -0.011438086637203, 0.748742575053576, 0.803458417245146, 0.688689839358732, 0.800911399697452, 0.0627229307052204, 0.398778626373986, 0.319214382384686, 0.34959399614961, 0.323981011770056, 0.358937309819321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-86.8233896891276, -96.3027079264323, -93.2247548421224, -94.2135706583659, -0.792789588371913, -0.881451360384623, -0.967617704470952, -0.992604154348373, -0.986926597356796, -0.95684987505277, -0.980758547782898, -0.820563558737437, -0.924523905913035, -0.986901019016902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863733417948761, 1.09200304071539, 0.964009541843169, 0.639006544030502, 0.949538900192391, 0.955505769478591, 0.954107034884158, 0.978124283406045, 0.046412034415707, 0.533815978779252, 0.372678771538051, 0.219448593444679, 0.205753088872267, 0.599064819855603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.9887858072917, -97.3958521525065, -94.0973248799642, -94.8235163370768, -0.799968594312668, -0.884592447678248, -0.970458255211512, -0.993665138880412, -0.98669908841451, -0.966412274042765, -0.982269044717153, -0.815789316097895, -0.917294416824977, -0.989229486385981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94056712850767, 1.18480596762768, 1.07052232327191, 0.788230779452867, 1.01004678489379, 1.01981790413759, 1.07077712671761, 1.07690847541325, 0.136771998286707, 0.646246244460015, 0.56090934567379, 0.378390085843406, 0.250808789410826, 0.532809882150734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.5138786315918, -98.6089688618978, -94.7575441996257, -94.9634493509928, -0.802131913105647, -0.885921047131221, -0.97170688311259, -0.994256565968196, -0.987959454456965, -0.974373797575633, -0.987587008873622, -0.821619911988576, -0.920049516359965, -0.988587025801341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.963826347803858, 1.15443916314414, 1.00812025755198, 0.453966962544714, 0.950075385201956, 0.989342189035767, 0.943422742253499, 1.02860900375561, 0.0551079789054723, 0.559059497921318, 0.358734224127541, 0.259554763318861, 0.488459514358874, 0.461714923112242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.6728355407715, -98.212015024821, -94.3707450866699, -94.6499979654948, -0.799987775087357, -0.885291461149851, -0.970343909660975, -0.993967394034068, -0.986820381879806, -0.968199843168259, -0.981875077883403, -0.817260567347209, -0.934581559896469, -0.987897632519404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939853362620276, 1.21594693899515, 1.08600061673569, 0.836312182527728, 1.01558579533958, 1.01958343191168, 0.98787026841982, 1.01160355440576, -0.0203834568377096, 0.45480692564192, 0.321120092658919, 0.403615315264855, 0.0962604392716911, 0.344404337455721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.5090006510417, -99.016042582194, -94.8534863789876, -95.0085370381673, -0.802329947551092, -0.885916203260422, -0.970819596449534, -0.993865581353505, -0.985767406225204, -0.960817406574885, -0.980812388658524, -0.822545272111893, -0.910599078734716, -0.986760095755259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.951598478723428, 1.22362814215784, 1.08684604353714, 0.754793034526334, 1.01534911731433, 1.0199378331227, 1.07605318309381, 1.10007410266259, -0.00124508592744643, 0.602179839111576, 0.402919501163691, 0.437933128815807, 0.276121089881847, 0.481697273487421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.5892684936523, -99.1164510091146, -94.858726755778, -94.932093556722, -0.802321485678355, -0.885923524697622, -0.971763348579407, -0.994395260016123, -0.986034353574117, -0.971253323554993, -0.983123417695363, -0.823804183801015, -0.921597331762314, -0.988091397285461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953653518665628, 1.19824779106704, 1.0379384764298, 0.504057949790235, 1.00020283512377, 1.00900381041409, 0.97326736220757, 0.988223882295933, 0.0490322558589665, 0.562058458734976, 0.419429468361056, 0.404889171775535, 0.207076244921925, 0.461819829171119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.6033129374186, -98.7846799214681, -94.5555732727051, -94.6969701131185, -0.801779965559641, -0.885697642962138, -0.970663313070933, -0.993725605805715, -0.986735635995865, -0.968412208557129, -0.983589863777161, -0.822592002153397, -0.917375326156616, -0.987898649772008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912973961146148, 1.08013671001584, 0.920099289851332, 0.29529551192869, 0.872654996737685, 0.920823980411268, 0.880287357570132, 0.955489288299212, 0.0342650040261249, 0.612633204144423, 0.441790322643032, 0.242803550203425, 0.339970265623178, 0.416354731642287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.3253028869629, -97.2407358805338, -93.8251472473144, -94.5012059529622, -0.797219789028168, -0.883875970045725, -0.969668221473694, -0.99352962176005, -0.986529658238093, -0.971993557612101, -0.984221611420314, -0.816646067301432, -0.925501628716787, -0.987457784016927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9527672745504, 1.21580250618168, 1.08344804814149, 0.78679559464436, 1.01559863230221, 1.0196107453293, 1.07869622372111, 1.09447210066286, -0.00999985898237245, 0.608012643518008, 0.339074374318521, 0.260304453872468, 0.153758446479696, 0.40346849755056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.5972562154134, -99.0141545613607, -94.8376642862956, -94.9621035257975, -0.802330406506856, -0.885916767517726, -0.971791634956996, -0.994361720482508, -0.985912239551544, -0.97166636188825, -0.981319640080134, -0.817288068930308, -0.914115009705226, -0.98733282883962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980017755396256, 1.1805182741166, 1.05370224401202, 0.568514887465989, 0.985001815235426, 1.01320026697903, 0.981873905965518, 1.00587047066975, 0.0122803561450034, 0.581072330994457, 0.327583923791284, 0.290101160021826, 0.453808863719152, 0.456096711912168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.7834899902344, -98.5529202779134, -94.653284962972, -94.7574137369792, -0.801236488421758, -0.885784335931142, -0.970755422115326, -0.993831257025401, -0.986223010222117, -0.969758637746175, -0.980995007356008, -0.818381128708522, -0.9324627161026, -0.987843153874079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.912205456213847, 1.08317289242001, 0.858848310918814, 0.218961958924222, 0.862290344197865, 0.907946473395377, 0.854772928150014, 0.937544364530708, 0.128048989808134, 0.587108101921852, 0.412335745095166, 0.246063095542805, 0.446955082388827, 0.328557170831082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.3200508117676, -97.2804247538249, -93.4454831441244, -94.429625193278, -0.796849224964778, -0.883609938621521, -0.969395160675049, -0.993422184387843, -0.987837783495585, -0.970186048746109, -0.983389449119568, -0.816765640179316, -0.932043615976969, -0.986606429020564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934604107765293, 1.16852342467166, 0.973708399881051, 0.448459454401964, 0.957684647620649, 0.994960482101047, 0.922467033465814, 1.00910835548176, 0.0901958706335629, 0.659301812002274, 0.456789097247205, 0.244686388117426, 0.235675299721342, 0.425141843441207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.4731264750163, -98.396124013265, -94.1574432373047, -94.6448333740234, -0.800259826580683, -0.885407527287801, -0.9701196372509, -0.993850642442703, -0.987309797604879, -0.975298301378886, -0.984645362695058, -0.816715137163798, -0.919124122460683, -0.987542990843455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86652492317835, 0.900568669184307, 0.814136122002726, 0.0611569889323885, 0.906840939641211, 0.925694424408182, 0.826715706886648, 0.793715842007708, -0.048840528864522, 0.270770890639202, 0.285672925151704, 0.213871084204617, 0.219997283051129, 0.225528766491162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.0078633626302, -94.8934285481771, -93.1683347066243, -94.281645711263, -0.798442027966181, -0.883976586659749, -0.969094886382421, -0.992561074097951, -0.98537047902743, -0.947785264253616, -0.979810921351115, -0.815584711233775, -0.918165431420008, -0.985607383648554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93599859516763, 0.944928141757072, 0.932476303760873, -0.00221732256129507, 0.942607329372173, 0.955906815082381, 0.868453545548861, 0.869127994512522, -0.0134335669525314, 0.324765961420199, 0.306436088311487, 0.265779816285188, 0.186923125585519, 0.296876155733827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.4826566060384, -95.4732940673828, -93.9018661499023, -94.2222173055013, -0.799720772107442, -0.884600732723872, -0.969541573524475, -0.993012571334839, -0.985864345232646, -0.951608816782633, -0.980397530396779, -0.817488926649094, -0.916142988204956, -0.98629922469457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.944682939060265, 1.19743269117669, 1.06931076093828, 0.738686258078326, 1.01543608634685, 1.01963257682859, 1.04035013558647, 1.06661441096019, 0.157456862494567, 0.641787378063668, 0.466300137940542, 0.393595664728325, 0.29564803080829, 0.490071112784855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.5420066833496, -98.7740249633789, -94.7500343322754, -94.9169896443685, -0.802324595053991, -0.885917218526204, -0.97138124704361, -0.994194934765498, -0.988247972726822, -0.974058051904043, -0.984914072354635, -0.822177712122599, -0.92279137969017, -0.988172596693039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8139608901246, 0.954540919796561, 0.850488284647647, 0.547797186582166, 1.0110307853148, 1.01640555424117, 0.831589468605322, 0.871283376479724, 0.18218309244247, 0.484861570603983, 0.47728425561511, 0.0504324775350017, -0.220723698094284, -0.322618094615116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.6486330668131, -95.5989519755046, -93.3936635335287, -94.7379859924316, -0.802167093753815, -0.885850552717845, -0.969147046407064, -0.993025475740433, -0.988592861096064, -0.962945665915807, -0.985224399964015, -0.809589143594106, -0.891215896606445, -0.980292115608851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793800064503513, 0.976931916309435, 0.788147843263138, 0.613884572305698, 0.995514843057569, 1.01215447084099, 0.87634386743842, 0.71863952422974, 0.584804937725053, 0.62525026411741, 0.697744041007331, 0.00242655583536445, -0.00315844493959769, -0.292829281575939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.5108510335287, -95.8916463216146, -93.0072463989258, -94.7999585469564, -0.801612357298533, -0.885762731234233, -0.96962601741155, -0.992111587524414, -0.994208743174871, -0.972887009382248, -0.991452916463216, -0.807828098535538, -0.904519738753637, -0.980580971638362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.968358785376694, 1.21601954449891, 1.08045746263317, 0.883140646484024, 1.01419706938256, 1.01898099793994, 1.05745313508579, 1.07612563537313, 0.157009309584829, 0.657066262312316, 0.491886754438062, 0.229043462662621, 0.158162717424548, 0.531645260981469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.7038108825684, -99.0169916788737, -94.819127146403, -95.052449798584, -0.802280296881994, -0.885903757810593, -0.97156428694725, -0.994251879056295, -0.988241730133692, -0.975139995416005, -0.985636955499649, -0.816141293446223, -0.914384325345357, -0.988575732707977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962736888240476, 1.19908927173528, 1.07952074811779, 0.787433725758203, 1.01500963244552, 1.01909544500673, 1.03989233280591, 1.06561387568212, 0.172372396497692, 0.706922319937075, 0.538628238816111, 0.183795342819584, 0.175675828035005, 0.505949218501066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.6653900146484, -98.7956797281901, -94.8133209228516, -94.9627019246419, -0.802309348185857, -0.885906122128169, -0.971376347541809, -0.994188944498698, -0.988456018765767, -0.978670452038447, -0.986957514286041, -0.814481415351232, -0.915455230077108, -0.98832656343778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99950038992732, 1.21427057285315, 1.07617329944733, 0.819612565189439, 1.01523080608734, 1.01980694030094, 1.12762617005645, 1.08324984477603, 0.402523987596716, 0.670141301621998, 0.603826399562021, 0.83841709680085, -0.160081737207105, 0.38739246360608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9166371663411, -98.9941291809082, -94.7925717671712, -94.9928771972656, -0.802317255735397, -0.88592082063357, -0.972315293550491, -0.994294532140096, -0.991666237513224, -0.976065878073374, -0.988799518346786, -0.838495502869288, -0.894924076398214, -0.987176942825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976184682616063, 1.21179790020681, 1.07999146449618, 0.849747920582095, 1.01418684426947, 1.01645575707214, 1.0957698911688, 1.07970068232195, 0.191074040093734, 0.736340064149092, 0.596881200599582, 0.498997379603493, 0.156394653686655, 0.4760102176862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.7572942097982, -98.9618064880371, -94.8162386576335, -95.0211362202962, -0.802279931306839, -0.885851589838664, -0.971974360942841, -0.994273283084234, -0.988716874519984, -0.980753610531489, -0.988603299856186, -0.826044259468714, -0.914276210467021, -0.988036251068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85344526841613, 1.15709589813534, 1.04100832839354, 0.572192616337572, 0.970828697068851, 0.958849547308945, 0.981588753868614, 1.01032061265284, 0.154549050559661, 0.459979120878319, 0.38673365731604, 0.316560762901391, 0.53571678176659, 0.55238346770665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.9184750874837, -98.2467437744141, -94.5746017456055, -94.7608624776204, -0.800729761521021, -0.8846615254879, -0.970752370357513, -0.993857900301615, -0.988207413752874, -0.961183665196101, -0.982666128873825, -0.819351770480474, -0.937471282482147, -0.988776826858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886284974147062, 1.18714339015019, 1.04579623564752, 0.678668575907228, 1.01145612779079, 1.00976281566712, 1.04780548914072, 1.06947862986073, 0.0337704452410795, 0.649311448563138, 0.445149419176447, 0.34343539819768, 0.390899313000535, 0.554128555408733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.142906443278, -98.6395235697428, -94.6042795817057, -94.8607088724772, -0.802182300885518, -0.885713322957357, -0.971461035807927, -0.9942120830218, -0.986522759993871, -0.974590853850047, -0.984316513935725, -0.820337637265523, -0.928615876038869, -0.988793748617172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.841307229420272, 1.13685763924489, 1.02466803274115, 0.25030062402877, 0.976615444221976, 0.992029290755168, 0.93133013985261, 0.987759952505306, 0.0991220014702886, 0.524076475675189, 0.355743414420434, 0.254141252272436, 0.291892097555035, 0.467438450160485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.8355219523112, -97.9821899414062, -94.4733164469401, -94.4590126037598, -0.80093665321668, -0.885346972942352, -0.970214492082596, -0.993722828229268, -0.987434301773707, -0.965722590684891, -0.981790580352147, -0.817061978578568, -0.9225617090861, -0.987953132390976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857160378740608, 1.11380459415411, 0.986155859186015, 0.693563635476067, 0.942623333897007, 0.94302411467018, 0.92821852898275, 0.948247934964902, 0.104578386499119, 0.452507994507278, 0.403973376737315, 0.41131228993147, 0.175863694554642, 0.546925689014584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.9438646952311, -97.6808413187663, -94.2345987955729, -94.8746765136719, -0.799721344312032, -0.884334594011307, -0.97018119096756, -0.993486267328262, -0.987510408957799, -0.960654612382253, -0.98315319220225, -0.82282762726148, -0.915466717878977, -0.988723903894424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965796506874926, 1.15935390595626, 0.998977987885853, 0.425453105634707, 0.954234449950875, 0.956223419909165, 0.95546150734442, 1.02385521673788, 0.158276189145379, 0.547429185194071, 0.389903511945768, 0.247424367206897, 0.332748191833486, 0.444541678337102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.6862998962402, -98.2762603759766, -94.3140767415365, -94.6232594807943, -0.800136472781499, -0.884607273340225, -0.970472751061122, -0.993938932816188, -0.988259400924047, -0.967376265923182, -0.9827556848526, -0.816815576950709, -0.925060007969538, -0.987731107076009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947554115462624, 1.20842828111217, 1.07493958189324, 0.713288748227029, 1.01422663329649, 1.01755839204755, 1.05729904899175, 1.07317214815095, 0.124443781614122, 0.71127156645543, 0.519941884240355, 0.302980434278908, 0.168492646708821, 0.451508301204127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.5616287231445, -98.9177589416504, -94.7849245707194, -94.8931734720866, -0.802281353871028, -0.885874368747075, -0.971562637885412, -0.994234196345011, -0.98778749704361, -0.978978435198466, -0.986429580052694, -0.818853590885798, -0.915015987555186, -0.987798660993576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918493487709601, 1.21846163411955, 1.09063130398079, 0.871652659241222, 1.00061122836339, 1.01975779538402, 1.0299047692245, 1.04779107363247, -0.0679582456780567, 0.567169489053528, 0.263825084503091, 0.423888319179909, 0.0946503822589778, 0.376302745772635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.3630241394043, -99.0489145914714, -94.8821896870931, -95.0416770935059, -0.80179456671079, -0.885919805367788, -0.971269458532333, -0.9940822382768, -0.985103819767634, -0.968774135907491, -0.97919366757075, -0.82328896522522, -0.910500625769297, -0.987069408098857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965217932659964, 1.21993337413924, 1.08931659678746, 0.785131246728661, 1.01565998298074, 1.02010421415257, 1.06063083589477, 1.06625269173861, -0.000479887254266668, 0.54323206536588, 0.493984941520315, 0.205995650473264, 0.2391508303346, 0.516012823946108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.6823458353678, -99.0681531270345, -94.8740404764811, -94.9605428059896, -0.802332599957784, -0.885926961898804, -0.971598295370738, -0.994192769130071, -0.986045026779175, -0.967079055309296, -0.9856962343057, -0.81529580950737, -0.919336646795273, -0.988424148162206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.960041129824309, 1.20914846078472, 1.06966442390191, 0.801139306761257, 1.01106490607261, 1.01859370521897, 1.04356830720088, 1.03299941228926, 0.277830362633234, 0.607316457689337, 0.511663412423229, 0.267823402758867, 0.0896909595751984, 0.556096773380571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.6469668070475, -98.9271731058757, -94.7522265116374, -94.9755541483561, -0.802168313662211, -0.885895756880442, -0.971415688594182, -0.993993679682414, -0.9899269759655, -0.971617062886556, -0.986195693413417, -0.817563893397649, -0.910197363297145, -0.988812834024429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980909395270499, 1.16398493867695, 1.01041652306802, 0.78841682192805, 0.99300357751144, 1.00659349748312, 1.01943749664676, 0.981420242405002, 0.281105675047814, 0.666982947277019, 0.488114504361672, 0.391286366518193, 0.388037776441507, 0.292027733719706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.7895835876465, -98.3367970784505, -94.3849784851074, -94.9636238098145, -0.801522572835286, -0.885647849241893, -0.971157435576121, -0.993684871991475, -0.989972660938899, -0.975842225551605, -0.985530380407969, -0.822092998027802, -0.928440896670024, -0.986252210537593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.942647063365601, 1.21938507807485, 1.08789439574672, 0.814702779517963, 1.01574267302572, 1.01965700502604, 1.0907058424063, 1.07780314974483, 0.0364623150336664, 0.648684900957444, 0.412235533384742, 0.250470140792551, 0.212074560069215, 0.509037595503939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.5280932108561, -99.0609858194987, -94.8652249654134, -94.9882731119792, -0.802335556348165, -0.885917723178864, -0.971920164426168, -0.994261922438939, -0.986560306946437, -0.974546486139298, -0.983386617898941, -0.816927307844162, -0.917680966854096, -0.988356510798136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983725534930902, 1.19454977408833, 1.06732052466188, 0.787897475951432, 1.01517223397215, 1.01939281503237, 1.04966918829487, 1.00803481265437, 0.372259041117184, 0.650953530206182, 0.477652401793405, 0.329045802399067, 0.357026901530358, 0.533110667491425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.808829498291, -98.7363395690918, -94.7376978556315, -94.9631368001302, -0.802315161625544, -0.885912265380224, -0.971480981508891, -0.993844215075175, -0.991244093577067, -0.974707134564718, -0.985234800974528, -0.819809770584106, -0.926544620593389, -0.988589942455292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996270265307986, 1.17912174655069, 1.0297786266783, 0.776939140245105, 0.990468138464255, 1.01231161916631, 0.915661254903125, 0.971395310326929, 0.23328560100359, 0.684232351943162, 0.574050089680689, 0.403702892899965, 0.31679666074572, 0.277651300865828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.8945620218913, -98.5346649169922, -94.5049944559733, -94.9528607686361, -0.801431924104691, -0.885765977700551, -0.970046800374985, -0.993624852101008, -0.989305653174718, -0.97706370751063, -0.987958266337713, -0.822548484802246, -0.92408459186554, -0.98611280520757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961307719131919, 1.19217184656613, 1.0746150489417, 0.787802013923344, 1.01404124755049, 1.01786364834166, 1.05904003620837, 1.07455099527546, 0.086492947195736, 0.69164697090845, 0.508980199924123, 0.353886925086939, 0.258619416319973, 0.454516359505672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.6556228637695, -98.7052553812663, -94.7829129536947, -94.963047281901, -0.802274725834529, -0.885880674918493, -0.971581270297368, -0.994242451588313, -0.987258148193359, -0.977588758865992, -0.98611988623937, -0.820721040169398, -0.920527126391729, -0.987827829519908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862021473855672, 0.906339717261096, 0.892320910326826, -0.0496969351807299, 0.921112085522397, 0.93783514236637, 0.759951687511904, 0.802586591101666, 0.00314654480464979, 0.334009158913358, 0.290654818477921, 0.0992201528432754, 0.180151840466427, 0.261707628862811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.977086130778, -94.9688674926758, -93.6529630025228, -94.177693939209, -0.798952259620031, -0.8842273970445, -0.968380363782247, -0.992614183823268, -0.986095609267553, -0.952263355255127, -0.979951671759288, -0.811378866434097, -0.915728932619095, -0.985958202679952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926362588233222, 0.994688183679942, 0.976446867186183, 0.0960513433839855, 0.942267010934366, 0.967264099590097, 0.862007363087533, 0.914331282374322, 0.0675230852263555, 0.338986636475513, 0.325452965721622, 0.29104745342976, 0.392006432300098, 0.354446633857542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.4168027242025, -96.123755645752, -94.1744176228841, -94.3143674214681, -0.799708604812622, -0.884835358460744, -0.969472585121791, -0.993283206224442, -0.986993551254272, -0.952615825335185, -0.980934802691142, -0.818415842453639, -0.928683574994405, -0.98685747385025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997302901947118, 1.21010530871911, 1.09045677007739, 0.801729164463171, 1.01412649387374, 1.0051704107207, 1.08100064623336, 1.08354884387571, 0.431909354439824, 0.753296241954499, 0.585513395141105, 0.677327217233369, 0.044171636177994, 0.420813648933903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9016192118327, -98.9396809895833, -94.8811078389486, -94.9761072794596, -0.802277773618698, -0.885618450244268, -0.971816297372182, -0.994296322266261, -0.992076112826665, -0.981954328219096, -0.988282132148743, -0.832586095730464, -0.907413913806279, -0.987501021226247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854240789355638, 0.947423401485363, 0.767190153497929, 0.444127322479949, 1.01005034145487, 1.01085362123983, 0.705123028463776, 0.755784769762423, 0.503264415598036, 0.704128766629632, 0.654567561856115, 0.584112983706654, -0.429993679406082, -0.245891606224536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.9239117940267, -95.5059120178223, -92.8773401896159, -94.6407709757487, -0.802132040262222, -0.885735857486725, -0.967793575922648, -0.992333978414536, -0.993071393171946, -0.978472632169723, -0.990233077605565, -0.829166632890701, -0.8784192999204, -0.98103611667951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838195551014356, 0.976083626443361, 0.907128926315347, 0.761148581765117, 0.98740404995612, 1.00511934232367, 0.984603457580552, 0.780434773230283, 0.384707193992825, 0.652413491903476, 0.598334024266703, 0.701532440716652, 0.0980534565701298, 0.297381835720768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.8142562866211, -95.8805575052897, -93.7447504679362, -94.9380533854167, -0.801322374741236, -0.885617395242055, -0.97078463435173, -0.992481559514999, -0.991417723894119, -0.97481051882108, -0.9886443456014, -0.833474038044612, -0.910708719491959, -0.986304128170013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.995282580923273, 1.2120694510164, 1.06759213125343, 0.848905034265983, 1.01389876282244, 1.01660213390883, 1.12060244321137, 1.08301854358572, 0.361322625679824, 0.70814357011096, 0.665151746901083, 0.51077789845955, 0.0175851445215652, 0.532743496285357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.8878120422363, -98.9653561909993, -94.7393814086914, -95.0203458150228, -0.802269631624222, -0.885854613780975, -0.972240124146144, -0.994293147325516, -0.991091549396515, -0.978756932417552, -0.990532106161118, -0.826476414998372, -0.90578818321228, -0.988586382071177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01482888541072, 1.20787918739889, 1.0808466560059, 0.840724589336996, 1.01516789941334, 1.01940906843933, 1.11681638079983, 1.07813666150419, 0.396086604194432, 0.690085946810201, 0.767680070774076, 0.648622713056559, 0.024967694399201, 0.402711411832684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-89.0213943481445, -98.9105812072754, -94.8215395609538, -95.0126747131348, -0.802315006653468, -0.885912601153056, -0.972199604908625, -0.994263919194539, -0.991576447089513, -0.977478218078613, -0.993428776661555, -0.831533102194468, -0.90623961687088, -0.987325487534205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990760748807812, 1.21844398856973, 1.07564099976171, 0.794560562792031, 1.01207969297542, 1.0123586482551, 1.0991074330946, 1.07978596841365, 0.330262995023502, 0.702160126051356, 0.606565519646946, 0.426402452650389, 0.164993104791858, 0.422679624477267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.8569091796875, -99.0486839294434, -94.7892723083496, -94.9693850199381, -0.802204595009486, -0.885766949256261, -0.972010080019633, -0.994273793697357, -0.990658320983251, -0.978333226839701, -0.98887690504392, -0.823381193478902, -0.914801994959513, -0.987519115209579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961267567242419, 1.20573621611165, 1.07964850988911, 0.849153723697087, 1.01440251635587, 1.00684816625022, 1.04170367981725, 1.04837778884695, 0.119947598419978, 0.693690805055454, 0.481038502745627, 0.532473321317626, 0.0844610441940865, 0.532571589677155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.6553484598796, -98.882568359375, -94.8141128540039, -95.0205790201823, -0.802287642161051, -0.885653110345205, -0.971395732959112, -0.994085750977198, -0.987724783023198, -0.977733488877614, -0.985330466429392, -0.827272288004557, -0.909877560536067, -0.988584715127945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.900305649281549, 1.18974821959904, 1.03585022381696, 0.581853536298614, 0.999273683543084, 0.984599656466443, 1.02444380953547, 1.03240373705738, 0.0969564550391, 0.599471944746418, 0.417319255873554, 0.625222748867525, 0.256571924690544, 0.476708703535251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.238725789388, -98.673573811849, -94.5426292419434, -94.769921875, -0.801746745904287, -0.885193487008413, -0.97121101419131, -0.993990113337835, -0.987404096126556, -0.971061569452286, -0.983530245224635, -0.830674699942271, -0.920401924848557, -0.988043024142583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938687432127403, 1.20526710129063, 1.06398456388351, 0.721119346519019, 1.01388581471728, 1.0182588273311, 1.09195282589254, 1.05719710080388, 0.213612929977345, 0.685434747610261, 0.578540980787834, 0.763474525956935, 0.152446889936699, 0.456216780174867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.5010325113932, -98.8764361063639, -94.7170199076335, -94.9005165100098, -0.802269168694814, -0.885888838768005, -0.971933509906133, -0.994138552745183, -0.989031253258387, -0.977148852745692, -0.988085144758225, -0.835746316115061, -0.914034809668859, -0.987844318151474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850848866390107, 1.1338813194171, 1.03118782178406, 0.146787241716924, 1.00074798925096, 1.00004750995881, 1.00456429000933, 0.981252988746589, 0.262153618334229, 0.477154538439709, 0.452082241113598, 0.641289372429601, 0.0225098336685965, 0.292275861136302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.9007308959961, -97.943283589681, -94.5137293497721, -94.361944325765, -0.801799456278483, -0.885512618223826, -0.970998259385427, -0.993683870633443, -0.989708312352498, -0.96239990790685, -0.984512382745743, -0.831264086564382, -0.906089321772258, -0.98625461657842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896542572520029, 1.13977259847277, 1.00081420435188, 0.608283771726429, 0.956121483457182, 0.97163116884115, 1.01640497092877, 1.02268278186643, 0.139230548007317, 0.483700138597458, 0.475260963600648, 0.596724217322949, -0.0966747398583228, 0.491526889246439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.2130083719889, -98.0202941894531, -94.3254585266113, -94.7947064717611, -0.800203939278921, -0.884925576051076, -0.971124980847041, -0.993931913375855, -0.987993746995926, -0.962863421440124, -0.985167237122854, -0.829629262288411, -0.898801334698995, -0.988186713059743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.976716927727757, 1.16460216327826, 1.00703108229729, 0.338237152628056, 0.95288034489306, 1.01404544414116, 0.999381799164917, 1.04664319584577, 0.203800382285963, 0.598673125307893, 0.6146693066299, 0.658840049658736, 0.0251179681199397, 0.140762621971178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.7609316507975, -98.3448654174805, -94.3639938354492, -94.5414738972982, -0.800088059902191, -0.885801796118418, -0.970942795276642, -0.994075365861257, -0.988894385099411, -0.971005002657572, -0.98910585641861, -0.831907914082209, -0.906248805920283, -0.984785423676173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967862710456468, 1.20034280614669, 1.08019738496189, 0.869252819790996, 1.0086263833147, 1.01002431278863, 1.11917853918585, 1.09245576489185, 0.19302108042577, 0.722849131455361, 0.52233789349359, 0.591175900627921, -0.0372987172862661, 0.105889553180047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.7004206339518, -98.8120658874512, -94.8175150553385, -95.0394266764323, -0.802081129948298, -0.885718725124995, -0.972224885225296, -0.99434964855512, -0.988744032382965, -0.979798277219137, -0.986497273047765, -0.829425728321075, -0.902432103951772, -0.984447266658147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.936814173445822, 1.21334596160679, 1.09003746201611, 0.917693561465868, 1.0154589261375, 1.01874662188804, 1.0779560535321, 1.0411195110353, 0.0643393630476024, 0.603000262672459, 0.557988438029958, 0.139541665127596, -0.202439821385797, 0.291440505663565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.4882303873698, -98.9820426940918, -94.8785087585449, -95.0848513285319, -0.802325411637624, -0.885898915926615, -0.971783713499705, -0.994042295217514, -0.986949143807093, -0.971311420202255, -0.98750448624293, -0.812858017285665, -0.892333932717641, -0.986246516307195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987480611084225, 1.21494201812406, 1.09322211084437, 0.854733641957715, 1.01592528020838, 1.02016134151196, 1.07710208240858, 1.09041586759355, 0.234674980724036, 0.508328557512952, 0.490057627007796, 0.688732403367525, -0.0716159389698328, 0.538957336222061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.8344922383626, -99.0029062906901, -94.8982487996419, -95.025811513265, -0.802342085043589, -0.88592814207077, -0.971774574120839, -0.994337435563405, -0.989325032631556, -0.964607433478038, -0.985585278272629, -0.833004482587179, -0.900333648920059, -0.988646636406581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00515708040615, 1.21959742777299, 1.07203622230844, 0.878253912722743, 1.0158568164077, 1.0200086171909, 1.13645270420166, 1.04577407415647, 0.332384384420317, 0.601515919179932, 0.521731067634466, 0.222270900535304, 0.151663322142245, 0.456785772607492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9552958170573, -99.0637616475423, -94.7669281005859, -95.0478673299154, -0.802339637279511, -0.88592498699824, -0.972409756978353, -0.994070162375768, -0.990687910715739, -0.971206309398015, -0.986480128765106, -0.81589284936587, -0.913986895481745, -0.987849835554759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99290163713655, 1.18124341477614, 1.02980143834973, 0.824683171834349, 1.00354967023732, 1.01907938394778, 1.0777434889807, 0.974192495023069, 0.610399921713854, 0.702622706785541, 0.626800760483816, 0.707658271526193, 0.124803316068261, 0.197199008227908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.8715403238932, -98.5623992919922, -94.5051358540853, -94.9976320902506, -0.80189962387085, -0.88590579032898, -0.971781438589096, -0.993641599019368, -0.994565749168396, -0.978365983565648, -0.98944859902064, -0.833698757489522, -0.912344439824422, -0.985332675774892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0088545893926, 1.22290160074903, 1.09335340103969, 0.918591229968556, 1.01580974754473, 1.02014229905883, 1.10364944559637, 1.09850078997491, 0.175039054048068, 0.575211413171657, 0.565595315577224, 0.957500799680752, -0.140740875761457, 0.337207208111669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9805651346842, -99.1069536844889, -94.8990626017253, -95.0856931050618, -0.802337954441706, -0.885927748680115, -0.972058689594269, -0.994385840495427, -0.988493214050929, -0.969343608617783, -0.987719398736954, -0.84286395907402, -0.896106745799383, -0.986690306663513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00229688158248, 1.21558465076072, 1.07977348174377, 0.774526012046656, 1.01536328798736, 1.01979059071997, 1.14761410678611, 1.05755649705801, 0.40973283712222, 0.701291219473024, 0.622357408405615, 0.341759507806103, -0.0107822775524139, 0.347262207981555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9357487996419, -99.0113067626953, -94.814887491862, -94.9505978902181, -0.802321992317836, -0.885920482873917, -0.972529208660126, -0.99414070447286, -0.991766788562139, -0.9782716969649, -0.989323063691457, -0.82027615904808, -0.904053550958633, -0.986787807941437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00182949721537, 1.17883562405773, 1.04958166020391, 0.795011837833865, 0.999957487980904, 1.01420384272856, 1.08592453234405, 0.998019836151182, 0.474044139086686, 0.770395119196676, 0.712527553825113, 0.734195161533343, 0.0330119035307027, 0.300910326423776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9325546264648, -98.5309247334798, -94.6277435302734, -94.9698081970215, -0.801771193742752, -0.885805068413417, -0.971868993838628, -0.993784254789352, -0.992663820584615, -0.983165150880814, -0.991870586077372, -0.834672234455744, -0.906731510162354, -0.986338343222936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962843575420454, 1.21093887126301, 1.08050796833018, 0.832622792101592, 1.01528343207699, 1.01891031004575, 1.07354510703321, 1.07968740822209, 0.314412756312001, 0.698391300934595, 0.648237697957685, 0.699431119079689, 0.1068398391782, 0.408623441955481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.6661191304525, -98.9505772908529, -94.8194402058919, -95.0050773620605, -0.802319137255351, -0.885902297496796, -0.971736506621043, -0.994273203611374, -0.990437237421672, -0.978066345055898, -0.990054243803024, -0.833396953344345, -0.911245995759964, -0.98738281528155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.926904843408194, 0.933927415740944, 0.88667223172982, 0.0578377850640058, 0.924265365913726, 0.95575505250138, 0.891191826233942, 0.819683299888166, 0.0290301163794261, 0.332590890366485, 0.371222009726518, 0.454650708219801, -0.0292218540813929, 0.249360472585365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.4205085754395, -95.3294929504395, -93.6179496765137, -94.2785331726074, -0.79906499783198, -0.884597597519557, -0.969784923394521, -0.99271654287974, -0.986456640561422, -0.952162923415502, -0.982227887709936, -0.824417450030645, -0.902925993998845, -0.985838474829992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.962713370173596, 1.01444658867165, 0.973256802637357, 0.155898441419679, 0.95233908075455, 0.965804659053521, 0.968167855078863, 0.924177677809093, 0.125603259871699, 0.328289565719543, 0.411563587494847, 0.482738594353495, -0.0803780503412772, 0.462873602336765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.665229288737, -96.3820368448893, -94.1546440124512, -94.3704882303874, -0.800068708260854, -0.884805208444595, -0.970608737071355, -0.993342157204946, -0.987803669770559, -0.951858333746592, -0.98336763381958, -0.825447823603948, -0.899797856807709, -0.987908867994944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.992103325287207, 1.20317486825467, 1.07807114024878, 0.71809493590213, 1.01329348058459, 1.01701058491106, 1.12753130500339, 1.08737012537723, 0.582978545806302, 0.7381899101117, 0.657701058974063, 0.44880234198952, -0.21072544321894, 0.307087490218812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.8660845438639, -98.8490865071615, -94.804335530599, -94.8976804097494, -0.802247991164525, -0.885863051811854, -0.972314278284709, -0.994319200515747, -0.994183268149694, -0.980884603659312, -0.990321606397629, -0.82420290907224, -0.891827277342478, -0.986398241917292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862417113233951, 0.960465038640642, 0.841391966549883, 0.501395047364896, 1.01358211774429, 1.01781411872873, 0.83956500196134, 0.817434335516842, 0.419761184513875, 0.669787723505167, 0.701955886453448, 0.592912667495607, -0.55316542901231, -0.211607609541367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.9797899881999, -95.6763918558757, -93.3372800191243, -94.6944730122884, -0.802258310715357, -0.885879651705424, -0.969232402245204, -0.992703078190486, -0.991906666755676, -0.976040840148926, -0.991571911176046, -0.829489439725876, -0.870887502034505, -0.981368561585744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845411280939427, 0.988176897979268, 0.811377920140111, 0.740029235246085, 0.9843613563857, 1.01382972584637, 0.972786168044052, 0.747767877142913, 0.609934705990358, 0.756546006988624, 0.715569770381565, 0.615706141667355, -0.358224055095908, 0.114320148294498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.8635696411133, -96.0386403401693, -93.1512379964193, -94.9182490030924, -0.801213590304057, -0.885797339677811, -0.970658163229624, -0.992285980780919, -0.994559260209401, -0.982184453805288, -0.991956535975138, -0.830325593551, -0.882807922363281, -0.984529016415278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00703588369527, 1.21207161050486, 1.08457373848175, 0.857047782541825, 1.01364113442962, 1.02007699690896, 1.11987879550713, 1.08594846928061, 0.444806911971815, 0.662528093074823, 0.718735616542875, 0.611706762997367, -0.0728211179643548, 0.316788022350696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9681358337402, -98.9653844197591, -94.8446418762207, -95.0279815673828, -0.802260420719783, -0.885926399628321, -0.972232379515966, -0.994310688972473, -0.992256011565526, -0.975526763995488, -0.992045978705088, -0.830178880691528, -0.900259953737259, -0.986492305994034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975531460866034, 1.21060535675314, 1.08178575015607, 0.729221143754423, 1.01411299005591, 1.02005766593381, 1.10338267244321, 1.09636100507506, 0.294498646017133, 0.627022475526036, 0.577463124727715, 0.548466773955131, 0.0289070753124094, 0.396524617989276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.7528299967448, -98.9462176005046, -94.827360534668, -94.908113861084, -0.802277290821075, -0.885926000277201, -0.972055834531784, -0.994373029470444, -0.990159469842911, -0.973012504975001, -0.988054692745209, -0.827858990430832, -0.906480505069097, -0.987265495459239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.971567289747835, 1.21023641495968, 1.08354745943625, 0.789825158041169, 1.00324847397133, 1.01653183071066, 1.07778266026484, 1.08875063176423, 0.341168642978838, 0.602650135603745, 0.545606630710002, 0.333200242769314, 0.0989334919703933, 0.449447061062885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.7257382710775, -98.9413948059082, -94.8382804870605, -94.9649444580078, -0.80188885529836, -0.885853161414464, -0.971781857808431, -0.994327465693156, -0.990810436010361, -0.97128662665685, -0.987154670556386, -0.819962171713511, -0.910762532552083, -0.987778673569361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.953021507830349, 1.20445454998576, 1.07312826953615, 0.836799527029036, 1.01355055326475, 1.00572514238561, 1.03764360406259, 1.07423308058345, 0.15564927292594, 0.674172574739461, 0.569227409907037, 0.26049379921096, 0.258773134151933, 0.577679760732216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.5989936828613, -98.8658144632975, -94.7736971537272, -95.0089940388997, -0.80225718220075, -0.885629910230637, -0.97135228117307, -0.994240548213323, -0.988222759962082, -0.976351344585419, -0.987822014093399, -0.817295014858246, -0.92053652604421, -0.989022119839986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.856172061749666, 1.14505881220898, 1.04490530858776, 0.713945320869016, 1.00412516627617, 1.01315131441012, 1.01574202943266, 1.04203276910669, 0.112089213162957, 0.599260673264134, 0.446864551390852, 0.564788331301044, 0.335860661137438, 0.509168113393604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.9371103922526, -98.0893953959147, -94.5987571716309, -94.8937891642253, -0.801920199394226, -0.885783324639002, -0.971117885907491, -0.994047762950261, -0.987615172068278, -0.971046608686447, -0.984364970525106, -0.828457729021708, -0.925250331560771, -0.988357776403427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92743783276251, 1.20709766658129, 1.06660626497118, 0.749733004640208, 1.01316055411443, 1.01929192850039, 1.0489470257578, 1.05739256192455, 0.366552670296948, 0.634976945034566, 0.505223280481327, 0.515198375529644, 0.274803587373252, 0.503516094576898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.4241511027018, -98.9003651936849, -94.733270517985, -94.9273485819499, -0.802243238687515, -0.885910181204478, -0.971473252773285, -0.994139722983042, -0.991164499521256, -0.9735757847627, -0.986013744274775, -0.826638575394948, -0.921516768137614, -0.988302969932556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.845278880176829, 1.13658180836809, 1.02116475902013, 0.187413385837453, 0.995839823825743, 1.00110840541574, 1.00827609406231, 1.00332416646124, 0.264890499813473, 0.47088822066372, 0.48620830181939, 0.554780054483357, -0.0119603585397791, 0.509557003432173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.8626647949219, -97.9785842895508, -94.4516014099121, -94.4000409444173, -0.801623976230621, -0.88553453485171, -0.971037983894348, -0.993816012144089, -0.989746487140655, -0.961956171194712, -0.985476525624593, -0.828090586264928, -0.903981512784958, -0.98836154739062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905929481448585, 1.12125228074082, 1.01850420424028, 0.704626382775612, 0.942569596482025, 1.00325395130902, 1.06206680690357, 0.98853748290548, 0.374953474866605, 0.554164957743178, 0.463678247975815, 0.482568530176475, 0.118121772790616, 0.451395404254042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.2771598815918, -97.7781972249349, -94.4351099650065, -94.8850504557292, -0.799719423055649, -0.885578858852387, -0.971613663434982, -0.993727483352025, -0.991281676292419, -0.967853246132533, -0.984839997688929, -0.825441584984462, -0.911935871839523, -0.987797566254934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983997853306584, 1.17979478711938, 0.994943768409347, 0.416838471197318, 0.979375446758251, 0.998643754171538, 1.02027401705603, 1.0155184183114, 0.466160541587453, 0.613895193520468, 0.491820579547177, 0.636027565128345, 0.0642608769987322, 0.458376574640953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.8106905619303, -98.5434628804525, -94.2890706380208, -94.6151812235514, -0.801035330692927, -0.885483618577321, -0.971166388193766, -0.993889019886653, -0.99255385796229, -0.972082922856013, -0.985635085900625, -0.831071062882741, -0.908642345666885, -0.987865261236827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.985966300619619, 1.21133158688434, 1.08308966693647, 0.8284975849734, 1.01572133365927, 1.00287435250849, 1.0979516017435, 1.08843935412217, 0.486681739884014, 0.529374002878566, 0.596408693594431, 0.390074253052674, -0.203487123621601, 0.186373194698841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.8241432189941, -98.9557108561198, -94.8354428609212, -95.0012090047201, -0.802334793408712, -0.885571016867955, -0.971997710069021, -0.994325602054596, -0.992840093374252, -0.966097724437714, -0.988589950402578, -0.822048532962799, -0.892269891500473, -0.985227700074514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.941635451580565, 1.22009578323499, 1.0872871785934, 0.898419723756739, 1.01540752271573, 1.01983425371856, 0.996365981577605, 1.03586927268224, 0.267031403770641, 0.544776058681958, 0.56546479421965, 0.570783201862166, -0.21077275101081, 0.413250782646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.5211797078451, -99.0702761332194, -94.861461130778, -95.0667775472005, -0.802323573827744, -0.885921384890874, -0.970910519361496, -0.994010861714681, -0.989776349067688, -0.967188390096029, -0.987715711196264, -0.82867764433225, -0.891824384530385, -0.987427685658137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98843469291452, 1.22354520612823, 1.09493852500717, 0.833002199423417, 1.01595951210873, 1.02018038396509, 1.08842852419494, 1.10772695309303, 0.408942853532974, 0.606415425500485, 0.591600641214298, 0.589307686066724, -0.00428252486234231, 0.230584132097999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.8410125732422, -99.1153668721517, -94.9088879903158, -95.0054331461589, -0.802343308925629, -0.885928535461426, -0.971895792086919, -0.994441078106562, -0.991755769650141, -0.971553258101145, -0.988454111417135, -0.829357194900513, -0.904451002677282, -0.985656404495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00412515079751, 1.21999226397307, 1.06385302751908, 0.803255200917731, 1.01550877356381, 1.01946898484489, 1.1244002013144, 1.03778406158922, 0.505987195314685, 0.593900578277823, 0.732878547978025, 0.548248181911037, -0.0200104486536491, 0.3610399386791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9482434590658, -99.0689229329427, -94.7162045796712, -94.9775382995605, -0.802327193816503, -0.885913838942846, -0.972280768553416, -0.994022325674693, -0.993109371264776, -0.970667044321696, -0.992445550362269, -0.827850971619288, -0.903489259878794, -0.986921407779058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01727041054693, 1.19564591875553, 1.03864313552496, 0.828418394881916, 1.00345664393672, 1.01595555606847, 1.09269875110435, 0.953192205315854, 0.591598711127386, 0.720954253523421, 0.718578372062519, 0.639557534173418, 0.0739981592200254, 0.303005169286992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-89.0380800882975, -98.7506683349609, -94.5599411010742, -95.0011347452799, -0.801896297931671, -0.885841256380081, -0.97194149295489, -0.993515868981679, -0.994303504625956, -0.979664095242818, -0.992041536172231, -0.831200555960337, -0.909237768252691, -0.986358656485875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01410443964169, 1.22186566884552, 1.09748428292249, 0.842638440280625, 1.01592528020838, 1.02018038396509, 1.06502024746968, 1.10764863590376, 0.398592159790349, 0.627059623393571, 0.655358988234442, 0.557156999240338, -0.0218530156654132, 0.420783529420902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-89.0164433797201, -99.0934120178223, -94.9246678670247, -95.0144694010417, -0.802342085043589, -0.885928535461426, -0.971645271778107, -0.99444060921669, -0.991611395279566, -0.973015135526657, -0.990255437294642, -0.82817778189977, -0.903376589218775, -0.987500729163488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999865478145934, 1.21709658450248, 1.07592528406275, 0.876520680275417, 1.01052558692843, 1.01326797347904, 1.09218562584665, 1.04710347525895, 0.549513781196764, 0.678733513599626, 0.764412747070211, 0.634486155421971, -0.0838469526650167, 0.530525921529027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.919132232666, -99.0310707092285, -94.7910344441732, -95.0462420145671, -0.802149031559626, -0.885785734653473, -0.971936001380285, -0.994078121582667, -0.993716492255529, -0.976674318313599, -0.993336466948191, -0.831014517943064, -0.899585737784704, -0.988564878702164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01234036135287, 1.16353060954266, 1.03274972379825, 0.710971353255595, 1.00704526963206, 1.01689892689043, 1.03507110887592, 0.954392515797047, 0.649524905920588, 0.672442000366653, 0.731758989781566, 0.593474312564303, 0.138147362536991, 0.357439325060619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-89.0043874104818, -98.3308581034342, -94.5234107971191, -94.8910003662109, -0.802024600903193, -0.885860745112101, -0.971324749787648, -0.993523055315018, -0.995111475388209, -0.976228797435761, -0.992413920164108, -0.829510043064753, -0.913160411516825, -0.98688649336497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00352186772748, 1.20973681438722, 1.0851588414428, 0.838641781451615, 1.01560580099562, 1.01961613107362, 1.10550423374748, 1.07277326144971, 0.397599623611142, 0.688906333672135, 0.6643097575615, 0.633335297556521, 0.0375531591256374, 0.398321748931505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9441205342611, -98.9348640441895, -94.8482686360677, -95.0107215881348, -0.802330662806829, -0.885916878779729, -0.9720785399278, -0.994231808185577, -0.991597551107407, -0.977394686142604, -0.990508317947388, -0.83097229997317, -0.907009202241898, -0.98728292187055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.923185342052239, 0.942201174753939, 0.892796016721118, 0.0605128914417822, 0.939606814393245, 0.939870857545128, 0.83676230586311, 0.85080110852011, 0.131906035540149, 0.297446903380136, 0.325502825442808, 0.392964585814105, -0.0351971271173712, 0.14625810127815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.3950889587402, -95.4376472473145, -93.6559079488118, -94.2810417175293, -0.799613495667776, -0.884269452095032, -0.969202407201131, -0.992902847131093, -0.987891582647959, -0.949674272537231, -0.98093621134758, -0.822154561678568, -0.902560613552729, -0.984838712215424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.947496027325915, 0.998594795570568, 0.993949491348962, 0.0752587915917568, 0.956694478789028, 0.977272158971772, 0.923507578715241, 0.954506009350982, 0.0711847004707333, 0.349245283834116, 0.382334609362452, 0.455686258240389, -0.172888697275006, 0.104729029903703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.5612317403158, -96.1748227437337, -94.2829076131185, -94.2948694864909, -0.80022442539533, -0.885042111078898, -0.970130773385366, -0.993523734807968, -0.987044624487559, -0.953342270851135, -0.982541845242182, -0.824455438057582, -0.894140946865082, -0.984436013301214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01258942214659, 1.2162471468002, 1.08502098673772, 0.755281463823412, 1.01559151918006, 1.01955361796991, 1.12586569002072, 1.0614959180484, 0.461101997194175, 0.591181068189737, 0.676808513705621, 0.591105696928642, 0.0763068716212933, 0.430469309138265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-89.0060895284017, -99.0199668884277, -94.8474141438802, -94.932551574707, -0.802330152193705, -0.885915587345759, -0.972296452522278, -0.994164290030797, -0.992483299970627, -0.970474467674891, -0.990861437718074, -0.829423152974674, -0.909378943118182, -0.987594650189082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.648060390227993, 0.860895267105571, 0.548034282167571, 0.278445107977867, 1.01366747521007, 1.00708561987031, 0.77921059280632, 0.549671183953482, 0.527455633219711, 0.626989452081859, 0.624825710738368, 0.319562915567246, -0.588575166491253, -0.735617471530539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-86.5148447672526, -94.3748191833496, -91.5189028422038, -94.4854047139486, -0.80226136247317, -0.88565801580747, -0.96858647664388, -0.991099963585536, -0.993408819039663, -0.973010166486104, -0.989392799139023, -0.819461901187897, -0.868722241033207, -0.976287345091502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.668578415095893, 0.833289378340081, 0.540006379062362, 0.502497471069854, 0.85037164118233, 0.994837571721752, 0.416757029806738, 0.136620354438384, 0.287543628218281, 0.577527347031169, 0.53746817399144, 0.366610325235276, 0.0107063446474637, -0.33623313896354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-86.655067952474, -94.0139559427897, -91.4691418965658, -94.6955067952474, -0.796423099438349, -0.885404988129934, -0.96470742225647, -0.988627002636592, -0.990062459309896, -0.969507606824239, -0.986924739678701, -0.821187784274419, -0.9053675532341, -0.980160093307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00603431918565, 1.21873433276534, 1.08264590607631, 0.875536228110843, 1.01528343207699, 1.01989166959996, 1.09452253639077, 1.05296033997628, 0.469169344933244, 0.787486196508964, 0.672644980852531, 0.745817531536881, -0.0117555783292928, 0.270962228286614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.96129099528, -99.0524792989095, -94.8326922098796, -95.0453188578288, -0.802319137255351, -0.885922571023305, -0.971961011489232, -0.994113186995188, -0.992595825592677, -0.984375421206156, -0.990743807951609, -0.835098588466644, -0.903994034837793, -0.986047942638397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02142789868641, 1.22086135107481, 1.08026413782057, 0.709203136144579, 1.01562002723992, 1.01991619397142, 1.08137713611129, 1.05190504903622, 0.405322831366137, 0.743741973156681, 0.693500760729948, 0.584189512586316, 0.084058220110147, 0.555911753515012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-89.0664929707845, -99.080283610026, -94.8179288228353, -94.8893422444661, -0.802331171433131, -0.885923077662786, -0.971820326646169, -0.994106868902842, -0.991705276568731, -0.981277761856715, -0.991333033641179, -0.82916944026947, -0.90985292834895, -0.988811039924622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01253758564791, 1.2058845009856, 1.07585016145412, 0.709404094561639, 1.01479707235006, 1.02006334020015, 1.10110349777289, 1.05409693477809, 0.288096160916212, 0.679360650408657, 0.640364644042729, 0.500427976791975, 0.117002776555988, 0.369625071640206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-89.0057352701823, -98.8845067342122, -94.7905687967936, -94.8895306905111, -0.802301748593648, -0.885926117499669, -0.97203144232432, -0.9941199918588, -0.990070166190465, -0.976718727747599, -0.989831811189651, -0.826096739371618, -0.911867446624316, -0.987004656058091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956836346666283, 1.19061703433287, 1.07485551514006, 0.809254935142768, 1.01551021841675, 1.01974423484921, 1.02186908659804, 1.0304687051481, 0.240021685377145, 0.690843634244341, 0.484378541473056, 0.297691979979216, 0.19548084613012, 0.522347141934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.6250648498535, -98.6849309285482, -94.7844034830729, -94.983164469401, -0.802327245473862, -0.885919525225957, -0.97118345896403, -0.993978528181712, -0.989399609963099, -0.977531872193019, -0.985424830516179, -0.818659589687983, -0.916666282074792, -0.988485570748647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85433590356283, 1.16944690753666, 1.02996587931937, 0.661542633829898, 0.991994403306576, 0.997585551586762, 0.991124455338138, 0.964386917445429, 0.211215345452592, 0.611621906759638, 0.48046712018619, 0.476182241205375, 0.436763599877325, 0.544827158047727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.9245618184408, -98.4081957499186, -94.5061551411947, -94.8446492513021, -0.801486492156982, -0.885461757580439, -0.970854423443476, -0.993582892417908, -0.988997811079025, -0.971921944618225, -0.985314323504766, -0.825207310914993, -0.93142041961352, -0.988703554868698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.939299087926948, 1.20238130488433, 1.05564558507178, 0.847108612464836, 1.01252270711425, 1.0156121186941, 1.07031783876987, 1.01780189534238, 0.454554363647994, 0.663334740500541, 0.550309408051184, 0.426856751477411, 0.189880284968361, 0.508418403882988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.5052126566569, -98.8387130737305, -94.6653307596842, -95.0186612447103, -0.802220433950424, -0.885834161440531, -0.971701967716217, -0.993902691205343, -0.99239197174708, -0.975583885113398, -0.987287535270055, -0.823397858937581, -0.916323814789454, -0.988350506623586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884257992151743, 1.11744531659677, 1.03166694894059, 0.0871063886335274, 0.996905958579063, 1.01623898086329, 1.02992351946005, 0.924214513436239, 0.283357968685254, 0.479368989038741, 0.508773025398571, 0.577120583842228, -0.0669985880118774, 0.37937759972886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.1290537516276, -97.7284327189128, -94.51669921875, -94.3059794108073, -0.801662093400955, -0.88584711154302, -0.971269659201304, -0.993342377742132, -0.990004076560338, -0.962556719779968, -0.986114033063253, -0.82891012430191, -0.900615994135539, -0.987099224328995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.940176959312669, 1.18923784103916, 1.06395543387143, 0.621635166909392, 1.00691073159517, 1.00856669955816, 1.06127502715534, 1.03496032869329, 0.360788895332018, 0.543578544985366, 0.460784837018842, 0.629694652987929, -0.0603018311602081, 0.456481299163171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.5112121582031, -98.6669021606445, -94.7168393452962, -94.8072265625, -0.80201979080836, -0.885688612858454, -0.971605189641317, -0.994005419810613, -0.991084104776382, -0.967103590567907, -0.984758251905441, -0.83083874688429, -0.901025492411393, -0.987846883138021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.005805427367, 1.21192569912272, 1.05772879121774, 0.534163473299105, 1.00819626170977, 1.01439215143173, 1.0326829600644, 1.0166108767311, 0.35843404342118, 0.565607735465433, 0.514169408423904, 0.602604754929391, -0.0530340316703758, 0.532741433208225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9597267150879, -98.9634770711263, -94.6782435099284, -94.7252011617025, -0.802065751949946, -0.885808958609899, -0.971299191315969, -0.993895560503006, -0.991051258643468, -0.968663543462753, -0.986266493797302, -0.829844983418783, -0.901469909227811, -0.98858636206594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00134432544956, 1.21731416755553, 1.08752062897194, 0.801219581648495, 1.01354382914147, 1.01910919788955, 1.0978428132482, 1.09118410612381, 0.399527149382824, 0.725351393855888, 0.631915355211833, 0.36913025388631, -0.116078245138259, 0.220564959520537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9292388916016, -99.0339149475098, -94.8629081726074, -94.9756294250488, -0.802256941795349, -0.885906406243642, -0.971996545791626, -0.994342035055161, -0.991624436775843, -0.979975469907125, -0.989593098560969, -0.821280225118001, -0.897614834705989, -0.985559250627245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901107980041054, 1.21306125931795, 1.08797735473889, 0.896587232496132, 1.01582258450736, 0.981658655371981, 0.909385124082926, 1.02973365186752, 0.214631817935139, 0.561099768790999, 0.531827485364697, 0.614712891048759, -0.277090793177126, 0.418039375423723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.2442090352376, -98.9783210754395, -94.8657391866048, -95.0650591532389, -0.802338413397471, -0.885132730007172, -0.969979631900787, -0.993974127372106, -0.989045464992523, -0.968344320853551, -0.986765376726786, -0.830289157231649, -0.887769119492893, -0.987474119663239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.983947356444626, 1.21500116087096, 1.09168338975529, 0.820101536884403, 1.01592528020838, 1.02019942641822, 1.06895668305733, 1.08611505923405, 0.270271817883859, 0.604969436339469, 0.594371758722549, 0.615151397401799, 0.0701148082923014, 0.406708906380954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.8103454589844, -99.0036794026693, -94.8887110392253, -94.993335723877, -0.802342085043589, -0.885928928852081, -0.971687400341034, -0.994311686356862, -0.989821547269821, -0.971450863281886, -0.988532402118047, -0.830305243360585, -0.909000306217759, -0.987364250421524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02083287670948, 1.21906763327186, 1.08066986555228, 0.795724548657156, 1.01446358917807, 1.0197473124174, 1.09560113904895, 1.07838754199182, 0.445925936688219, 0.647555117587309, 0.679796862072469, 0.751137778088777, -0.0617097053477148, 0.265160974454309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-89.0624265034994, -99.0568361918131, -94.8204437255859, -94.9704765319824, -0.802289825677872, -0.885919588804245, -0.971972554922104, -0.994265421231588, -0.992271620035172, -0.974466482798258, -0.990945865710576, -0.835293755928675, -0.900939402671961, -0.985991689066092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.981365653210404, 1.19186325372032, 1.04704488746133, 0.799283492391498, 0.994195859040367, 1.01286837048534, 1.08120170073918, 0.968135523250126, 0.637552936806014, 0.72099128916175, 0.761180655694009, 0.519020215864512, 0.0970216087390577, 0.139250909271171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.7927017211914, -98.7012214660645, -94.6120193481445, -94.9738138834635, -0.801565200090408, -0.885777479410171, -0.971818449099859, -0.993605335553487, -0.994944487015406, -0.979666717847188, -0.993245152632395, -0.826778775453567, -0.910645623292242, -0.984770764907201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00607688986367, 1.22340137641514, 1.0980721758002, 0.774935251252251, 1.01589104830804, 1.02013412426835, 1.06664947585665, 1.08735618757236, 0.422887787432026, 0.668475062642134, 0.531704488675902, 0.620974123273126, -0.141119598029335, 0.418926539971312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9615819295247, -99.113486735026, -94.928311920166, -94.950981648763, -0.80234086116155, -0.885927579800288, -0.971662708123525, -0.994319117069244, -0.991950277487437, -0.975947886705399, -0.986761901775996, -0.830518843730291, -0.896083587408066, -0.987482722316469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02815268896534, 1.18925005868556, 1.05094789879889, 0.717849229659393, 1.00744766117487, 1.01068233533567, 1.05126240137793, 0.986646255525789, 0.601753119730092, 0.677343891557855, 0.723342823558118, 0.514467045407889, 0.0886937594101783, 0.362289796021206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-89.112451171875, -98.6670618693034, -94.6362121582031, -94.8974500020345, -0.80203898747762, -0.885732318957647, -0.97149803241094, -0.993716160456339, -0.994445141156515, -0.976575915018717, -0.992176143328349, -0.826611747344335, -0.910136385758718, -0.986933527390162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.990837852343533, 1.21855274118656, 1.07903021512555, 0.797001624481669, 1.0149497821912, 1.02009603936208, 1.07334628027814, 1.07912657750237, 0.561634602249814, 0.701048327411652, 0.66763882574379, 0.634317174456268, -0.104079254067896, 0.353781340941185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.8574361165365, -99.0501055399577, -94.8102803548177, -94.9716740926107, -0.80230720837911, -0.885926793018977, -0.971734378735224, -0.994269845883052, -0.993885556856791, -0.978254497051239, -0.990602372090022, -0.831008319060008, -0.898348557949066, -0.986851022640864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998100469553839, 1.2132349716821, 1.08132951672736, 0.775215128561852, 1.0117676603124, 0.994527506727364, 1.08356441606289, 1.08260306425962, 0.464946935352252, 0.71346929490261, 0.581667304857035, 0.464233553792106, -0.00759277062859551, 0.293036317017853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.907069905599, -98.9805918375651, -94.8245325724284, -94.9512440999349, -0.802193439006805, -0.885398582617442, -0.971843735376994, -0.994290659825007, -0.992536930243174, -0.979134062925974, -0.988173470894496, -0.824768986304601, -0.904248585303625, -0.986261990563623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90084176445488, 0.940955169369848, 0.889728052053935, 0.0409537524441893, 0.92575023016229, 0.952889259479379, 0.81610660084405, 0.827549863326577, 0.0823035841695093, 0.325958172286758, 0.339956518666281, 0.449884957541901, -0.135968409832083, 0.394441044331596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.2423896789551, -95.4213595072428, -93.6368911743164, -94.262700398763, -0.79911808570226, -0.884538394212723, -0.968981345494588, -0.99276364048322, -0.987199713786443, -0.951693240801493, -0.981344562768936, -0.824242623647054, -0.896398576100667, -0.987245291471481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.965498698189415, 1.01162787259143, 1.00411939399072, 0.0725283606295189, 0.941545251321328, 0.975514963713536, 0.963172495298043, 0.920465243926551, 0.206501083485425, 0.360145910314385, 0.425068187915598, 0.571495575785847, -0.0652437483614098, 0.0480650056949834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.6842646280924, -96.3451906840007, -94.3459457397461, -94.2923090616862, -0.799682799975077, -0.885005809863408, -0.970555275678635, -0.993319930632909, -0.988932055234909, -0.954114176829656, -0.983749171098073, -0.828703776995341, -0.900723300377528, -0.983886553843816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0141284786784, 1.21548811579029, 1.08494163822593, 0.905138135181815, 1.01547887622228, 1.01884770076803, 1.14030467090643, 1.03042954655347, 0.408947126794366, 0.675162099658076, 0.547650387010595, 0.750354237181462, -0.0624124614962205, 0.456665909239438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-89.0166076660156, -99.0100448608398, -94.8469223022461, -95.0730776468913, -0.80232612490654, -0.885901004076004, -0.972450981537501, -0.993978293736776, -0.991755829254786, -0.976421415805817, -0.987212411562602, -0.835265012582143, -0.900896430015564, -0.987848673264186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.675686118204264, 0.857463003390864, 0.531965470022178, 0.134313717513764, 1.01064056387942, 1.01799684933956, 0.903443155876269, 0.59011769812509, 0.542822993393967, 0.645769943705269, 0.697255078184472, 0.436551167815531, -0.559944284677763, -0.606267276460575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-86.7036430358887, -94.3299527486165, -91.4193003336589, -94.350247446696, -0.802153142293294, -0.88588342666626, -0.969916039705277, -0.991342119375865, -0.993623167276382, -0.974340069293976, -0.991439102093379, -0.823753488063812, -0.870472983519236, -0.977541627486547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.649261560609057, 0.889159235659373, 0.591767087254805, 0.566528355205524, 0.858936395962168, 0.981965642798192, 0.582603234434181, 0.186019917123166, 0.387126144824536, 0.620739660056609, 0.597073607083598, 0.252126370898696, 0.0864211983616027, -0.267873728347082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-86.5230537414551, -94.7442848205566, -91.7899805704753, -94.7555508931478, -0.796729312340419, -0.885139071941376, -0.966482343276342, -0.988922760883967, -0.991451464096705, -0.972567600011826, -0.988608735799789, -0.816988064845403, -0.909997421503067, -0.980822960535685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998093213188266, 1.2126392836008, 1.07391215405854, 0.831553454667729, 1.01508659865003, 1.01896743740514, 1.11094681449277, 1.05103260882194, 0.493801563130533, 0.591657256715276, 0.691101868192416, 0.787746041972918, 0.05024132984802, 0.366420062300241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9070203145345, -98.9728050231934, -94.778556060791, -95.004074605306, -0.802312099933624, -0.885903477668762, -0.972136787573497, -0.994101645549138, -0.992939402659734, -0.970508188009262, -0.991265259186427, -0.836636690298716, -0.907785067955653, -0.986973577737808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00042105526385, 1.2135290512091, 1.07361096614485, 0.743078324966839, 1.01563858804303, 1.01901937136822, 1.11794566478773, 1.05199498106287, 0.604972025094298, 0.666212044853749, 0.722001463442589, 0.49109280748767, -0.122918250023697, 0.377914037270725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9229291280111, -98.9844360351562, -94.7766891479492, -94.9211082458496, -0.802331835031509, -0.885904550552368, -0.972211690743764, -0.994107407331467, -0.994490039348602, -0.975787635644277, -0.992138246695201, -0.825754288832347, -0.897196576992671, -0.987085032463074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.987885106949716, 1.21924095653899, 1.08189841355493, 0.82736505818573, 1.01341701551066, 1.01895406921835, 1.07608789887645, 1.04127415429885, 0.334156648361445, 0.622783802833932, 0.573211757189489, 0.568830280175852, 0.0126231550001762, 0.475602477340178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.8372566223145, -99.0591018676758, -94.8280588785807, -95.0001469930013, -0.802252407868703, -0.885903201500575, -0.971763720115026, -0.99404322107633, -0.990712630748749, -0.972712351878484, -0.9879345814387, -0.828606003522873, -0.90548476378123, -0.988032297293345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.967447981254914, 1.20408512182103, 1.06342834476543, 0.802914032646921, 1.01312904520617, 1.01209003425717, 1.03859819526197, 1.03265329013503, 0.24183468774353, 0.704724282859575, 0.539144346705796, 0.336352604348718, 0.272685004089557, 0.563455359705859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.6975863138835, -98.8609853108724, -94.7135721842448, -94.9772183736165, -0.802242112159729, -0.885761400063833, -0.971362497409185, -0.993991607427597, -0.989424898227056, -0.978514802455902, -0.986972095568975, -0.820077812671661, -0.921387219429016, -0.988884188731511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877541760662963, 1.1929332705227, 1.03899331109277, 0.67216441164745, 0.979811736773799, 1.00520349457866, 0.990142202900187, 0.972435999757127, 0.27319444379159, 0.542404795823368, 0.416792529058761, 0.643001550400356, 0.344447382769522, 0.470075649152321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.0831540425618, -98.7152086893717, -94.5621116638184, -94.8546096801758, -0.801050929228465, -0.885619133710861, -0.970843911170959, -0.993631082773209, -0.989862312873205, -0.967020473877589, -0.983515363931656, -0.831326895952225, -0.925775398810705, -0.987978704770406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.956079675191684, 1.20848549782882, 1.05886994918413, 0.834520099909675, 1.01454466765631, 1.01868420495834, 1.07492612685665, 1.02958133157146, 0.268531460961122, 0.632687300866807, 0.569560464405679, 0.789423990466002, 0.182829799399041, 0.51240462922571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.6198936462402, -98.9185068766276, -94.6853169759115, -95.0068565368652, -0.802292724450429, -0.885897626479467, -0.971751286586126, -0.993973215421041, -0.989797272284826, -0.973413648207982, -0.987831423679988, -0.836698244015376, -0.915892686446508, -0.988389160235723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862830837707964, 1.11020538836338, 1.03757595137799, 0.237615564649766, 0.988943596331204, 1.00926501901359, 1.02920488419501, 0.914235708855226, 0.134270573510144, 0.500147665579184, 0.534235730995203, 0.629352979464801, -0.049731926303431, 0.363111628447296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-87.9826174418131, -97.6337926228841, -94.5533261617025, -94.4471173604329, -0.801377417643865, -0.885703039169311, -0.971261968215307, -0.993282634019852, -0.987924563884735, -0.964028120040894, -0.986833415428797, -0.830826212962469, -0.901671828826269, -0.986941496531169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.961574678960716, 1.18230302323326, 1.0572876151333, 0.676672822882676, 1.00176494343317, 1.01675707023202, 1.0562191468123, 1.04006787047269, 0.149034691617961, 0.482162037314752, 0.476603659872315, 0.569239734054285, -0.0825083306064778, 0.310003345929535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.6574473063151, -98.5762504577637, -94.6755088806152, -94.8588373819987, -0.801835815111796, -0.8858578145504, -0.97155108054479, -0.994035998980204, -0.988130497932434, -0.962754503885905, -0.98520517150561, -0.828621023893356, -0.899667592843374, -0.986426516373952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00668307547994, 1.20539476402258, 1.05854808306468, 0.560621371019136, 1.0090095471992, 1.01330778951741, 1.06380482378584, 1.00349706161211, 0.184846758709874, 0.707485570269988, 0.651647498100371, 0.746724504373948, -0.0886725748770123, 0.0353863298799092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9657246907552, -98.8781049092611, -94.6833218892415, -94.7500116984049, -0.802094829082489, -0.885786557197571, -0.971632264057795, -0.993817047278086, -0.988630014657974, -0.978710337479909, -0.990150578816732, -0.835131859779358, -0.899290657043457, -0.983763611316681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.975087743414322, 1.21499497422836, 1.07483496001885, 0.778481991034154, 1.01404035841022, 1.01833240044547, 1.08486393733781, 1.09184482444509, 0.265696436911918, 0.676272523489993, 0.553273846255547, 0.537103074814477, -0.0953791042068188, 0.294553060234685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.7497975667318, -99.0035985310872, -94.7842760721842, -94.9543075561523, -0.802274694045385, -0.885890358686447, -0.971857643127441, -0.994345990816752, -0.98975772857666, -0.976500048240026, -0.987371287743251, -0.82744212547938, -0.89888056119283, -0.986276698112488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94760948711376, 1.20249311191275, 1.08725702287666, 0.924723851675854, 1.01442707885579, 1.01955900371423, 1.06524673546332, 1.05742574717423, 0.159250777626744, 0.649675407881621, 0.524326726744467, 0.483391608296917, -0.238689546872262, 0.178909907209322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.5620071411133, -98.8401746114095, -94.861274210612, -95.0914438883463, -0.802288520336151, -0.885915698607763, -0.971647695700328, -0.994139921665192, -0.988272994756699, -0.974616626898448, -0.986553462346395, -0.825471778710683, -0.890117307504018, -0.985155330101649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.978607006292613, 1.22436112312232, 1.08988758605252, 0.839081123739938, 1.01592528020838, 1.02016134151196, 1.09905378143054, 1.09379213489675, 0.245202017720074, 0.63342324389208, 0.634368256586987, 0.368810923189586, -0.111508689346402, 0.270594319459813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.7738487243652, -99.1260325113932, -94.8775797526042, -95.0111335754395, -0.802342085043589, -0.88592814207077, -0.972009505828222, -0.99435764948527, -0.989471866687139, -0.973465762535731, -0.989662398894628, -0.821268510818481, -0.897894257307053, -0.986044375101725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01408140533251, 1.21346455837819, 1.08303079148951, 0.838757312201501, 1.01479429378672, 1.01087949204736, 1.13583710240914, 1.05200792331025, 0.533675507617163, 0.543006400487792, 0.597067066950915, 0.379790082312139, -0.056957509187575, 0.412213196157716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-89.0162859598796, -98.9835929870605, -94.8350779215495, -95.0108299255371, -0.802301649252574, -0.885736391941706, -0.972403168678284, -0.994107484817505, -0.993495575586955, -0.967063075304031, -0.988608551025391, -0.821671269337336, -0.901229993502299, -0.987417624394099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01562500174432, 1.20918207876717, 1.05094859627805, 0.792548809029832, 1.00249503873623, 1.01539572718126, 1.10683717128376, 0.957144236701137, 0.565275563397463, 0.691848282048607, 0.645221501283938, 0.457842173727809, 0.0400088754096313, 0.398567622507001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-89.0268351236979, -98.9276125590007, -94.6362164815267, -94.9674985249837, -0.801861917972565, -0.885829691092173, -0.972092805306117, -0.993539530038834, -0.993936342000961, -0.977603014310201, -0.98996902902921, -0.824534525473913, -0.907159366210302, -0.987285306056341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00053421735465, 1.22293825368822, 1.08659376122121, 0.846441191865108, 1.01570705184371, 1.01306841241721, 1.0845953077257, 1.10460355739244, 0.208125492582407, 0.580132102755041, 0.587398289509169, 0.403206132189254, -0.104602466548992, 0.423941980392793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9237024943034, -99.1074328104655, -94.8571629842122, -95.0180353800456, -0.802334282795588, -0.885781611998876, -0.971854768196742, -0.994422378142675, -0.98895471294721, -0.96969205737114, -0.988335384925206, -0.822530261675517, -0.898316564162572, -0.987531356016795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01087572908333, 1.18914286245681, 1.04057277317059, 0.785374240981944, 1.00478774249008, 1.00717621578368, 1.05277095993222, 0.959231257053977, 0.508971213744402, 0.731602252058606, 0.566656293875588, 0.596790672337343, 0.224650179836215, 0.29844790256519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9943778991699, -98.6656606038411, -94.571901957194, -94.9607706705729, -0.801943888266881, -0.885659887393316, -0.971514177322388, -0.9935520251592, -0.993150993188222, -0.98041811188062, -0.987749373912811, -0.829631700118383, -0.918449950218201, -0.986314465602239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.980150751552949, 1.20046902921967, 1.08418561184185, 0.80654864088648, 1.01382840959869, 1.01249752351934, 1.13635431187656, 1.07301883229739, 0.470807713350768, 0.687854830173922, 0.542790646485085, 0.542772169571528, -0.0630982295286363, 0.138718592980214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.7843989054362, -98.8137158711751, -94.8422360738118, -94.9806266784668, -0.802267116308212, -0.885769818226496, -0.972408703962962, -0.994233278433482, -0.992618678013484, -0.977320226033529, -0.987075112263362, -0.827650090058645, -0.900854496161143, -0.984765603144964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00449098325875, 1.20997393011063, 1.06917077276753, 0.810629913785851, 1.01195615804935, 1.01979876551045, 1.10115065183058, 1.07750282323516, 0.313574342426982, 0.715231321510697, 0.666734740305747, 0.275550057415609, -0.260966643100503, 0.314015797786983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.9507436116536, -98.9379636128744, -94.749166615804, -94.9844538370768, -0.802200178305308, -0.885920651753743, -0.97203194697698, -0.994260124365489, -0.990425542990367, -0.979258837302526, -0.990576829512914, -0.817847337325414, -0.888755091031392, -0.98646542429924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.915943377574716, 0.927030690533204, 0.908100022450623, 0.120847062779857, 0.933270356269055, 0.941579484930487, 0.880975546908163, 0.804864094787727, 0.12048617179736, 0.296117127563026, 0.341033812134344, 0.297657154735323, -0.0993290448950006, 0.327585560418583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.3455963134766, -95.2393391927083, -93.7507698059082, -94.3376192728678, -0.799386950333913, -0.884304749965668, -0.969675586620967, -0.992627819379171, -0.987732295195262, -0.949580107132594, -0.98137499888738, -0.818658312161764, -0.898639027277629, -0.986597007513046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.964776782845302, 1.02169756726038, 0.973249991958476, 0.146548857845662, 0.957808960544453, 0.973887314840985, 0.986144318520819, 0.889061046589796, 0.122298746837608, 0.365139633054262, 0.405898004169512, 0.139294476304691, -0.0234740223524801, 0.355043901751346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-88.6793309529622, -96.4768213907878, -94.1546017964681, -94.3617207845052, -0.800264271100362, -0.884972184896469, -0.970801124970118, -0.993131911754608, -0.987757577498754, -0.954467797279358, -0.983207567532857, -0.812848949432373, -0.903277466694514, -0.986863265434901</t>
+    <t xml:space="preserve">0.783974769978844, 1.01804520337531, 0.809051813029318, 0.0699800171760647, 0.762006389109329, 0.631334520378782, 0.596754943226575, 0.736281244661235, 0.147225833284692, -0.018067750917726, 0.159056849946966, 0.364194320524456, 0.0281802309257867, 0.0634594701743719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.4633298238118, -96.3966550191244, -93.3627527872721, -94.2603680928548, -0.793800477186839, -0.879575977722804, -0.967446716626485, -0.992554003000259, -0.98676856358846, -0.933086506525675, -0.978655258814494, -0.821144010623296, -0.907895119984945, -0.984274731079737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.883936404048425, 0.873170854604923, 0.78096955973942, 0.0961596674320601, 0.908948964231186, 0.868622597408322, 0.66397655778597, 0.6808531999216, 0.0672931731968171, 0.270896524572188, 0.16649113281274, 0.191577269725432, 0.23428950452088, 0.168796466959198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.1374005635579, -94.7631660461426, -93.2219123840332, -94.2857495625814, -0.798722714185715, -0.883396408955256, -0.968030621608098, -0.992292938629786, -0.985528347889582, -0.951915520429611, -0.978843887646993, -0.814823919534683, -0.920188997189204, -0.985269292195638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.740192692536687, 0.778015157320348, 0.520765164288484, 0.0492826591162854, 0.808230930833676, 0.758016474914261, 0.356566715660875, 0.473173725694559, 0.02065514917019, -0.0251325157954741, 0.0739751080727214, 0.459538661316864, -0.248733349728243, -0.0286208376094366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.1680943806966, -93.6902654012044, -91.9169141133626, -94.240301767985, -0.795348892609278, -0.881615606943766, -0.965360377232234, -0.991314774751663, -0.984804723660151, -0.932626163959503, -0.976496493816376, -0.824634887774785, -0.891377951701482, -0.983405335744222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.764605914990861, 0.782740782043245, 0.55522664318023, 0.0560030574926877, 0.800072360874353, 0.634749672151583, 0.432187572479202, 0.484434564172508, 0.0570981963127372, 0.213501141394723, 0.111929964576342, 0.0758446742503671, -0.163509480053745, -0.0655429407257589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.332719930013, -93.7435478210449, -92.0897481282552, -94.2468172709147, -0.795075599352519, -0.879630963007609, -0.966017240285873, -0.991367812951406, -0.985370165109634, -0.948175617059072, -0.977459516127904, -0.810586559772491, -0.89646133184433, -0.983056728045146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905840623633242, 0.890657752423278, 0.834656997460914, 0.0851407847389402, 0.895277859826308, 0.905921237653457, 0.67780313645513, 0.693053039203132, 0.0633928415937178, 0.22726386124474, 0.195307396712083, 0.179984328289764, 0.138057892963206, 0.154147570992379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.2851071675618, -94.9603345235189, -93.4911699930827, -94.2750666300456, -0.798264763752619, -0.883996931711833, -0.968150722980499, -0.992350399494171, -0.985467831293742, -0.949072400728861, -0.979575037956238, -0.814399462938309, -0.914449034134547, -0.985130981604258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866955906484584, 0.890984349783789, 0.788782138573973, 0.172954252501229, 0.900074377488885, 0.888299177907861, 0.678758318385718, 0.735458248000047, 0.0530719897312824, 0.262987700525411, 0.214957034793903, 0.20901991576998, 0.281585664570407, 0.122583865423947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.0228960673014, -94.964016977946, -93.2610946655273, -94.3602027893066, -0.798425436019897, -0.883713209629059, -0.968159019947052, -0.992550126711528, -0.985307695468267, -0.951400178670883, -0.980073604981105, -0.815462553501129, -0.923010089000066, -0.984832966327667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906268332290369, 0.894708845332401, 0.865014705980038, 0.138063266176525, 0.90129442928029, 0.911819362102695, 0.806991035105203, 0.770491077172331, 0.12214431547063, 0.18982741914105, 0.218187980078553, 0.117099393263872, 0.0315627060293853, 0.20791714600941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.2879913330078, -95.0060114542643, -93.6434224446615, -94.326375579834, -0.798466304937998, -0.884091893831889, -0.969272883733114, -0.992715130249659, -0.986379404862722, -0.94663302898407, -0.980155583222707, -0.812097033858299, -0.908096875747045, -0.985638658205668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882659387661952, 0.8902544227271, 0.800311436264357, 0.0264451086149188, 0.909720556538157, 0.918231209291961, 0.748150135569021, 0.786805477926584, 0.11844848268792, 0.201636014866192, 0.268144262360794, 0.321092993258664, -0.0632757043142399, 0.289052973096299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.1287892659505, -94.955786895752, -93.3189173380534, -94.2181605021159, -0.798748560746511, -0.884195127089818, -0.968761775890986, -0.992791970570882, -0.986322061220805, -0.947402481238047, -0.981423115730286, -0.819565925995509, -0.902440013488134, -0.986404718955358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755054370968641, 0.81641051140974, 0.663018081994171, 0.0657439627896216, 0.828270800489203, 0.697779861352846, 0.563485288688611, 0.66411654408902, 0.137534228262188, 0.17426684289397, 0.141741329240992, 0.140775044212342, 0.325217684775123, 0.208857138227699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.2683110555013, -94.1231811523437, -92.63035252889, -94.2562611897786, -0.796020181973775, -0.880645773808161, -0.967157727479935, -0.992214109500249, -0.986618191003799, -0.945619096358617, -0.978215914964676, -0.812963879108429, -0.925612624486287, -0.985647533337275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82926851712417, 0.862762142593266, 0.710933366137803, 0.0981199147804902, 0.873502752678833, 0.861827586849425, 0.599165999914887, 0.725496234083754, 0.106070989902362, 0.237591892665623, 0.224926835662557, 0.188772587096556, 0.186917099131636, 0.165063643596726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.7687589009603, -94.6458056131999, -92.8706611633301, -94.2876500447591, -0.797535347938538, -0.883287006616592, -0.967467659711838, -0.99250320593516, -0.986130015055339, -0.949745378891627, -0.980326567093531, -0.814721230665843, -0.917363357543945, -0.985234047969182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762193760356361, 0.833869170285045, 0.664093489903013, 0.00099179649726875, 0.839298657053342, 0.852436197128838, 0.523857361328184, 0.619160509658989, 0.0590157729159256, 0.202753489199179, 0.17240535775782, 0.155017904711873, 0.135019204732131, 0.137439614390677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.3164540608724, -94.3200312296549, -92.6357460021973, -94.1934832255046, -0.796389589707057, -0.883135801553726, -0.966813508669535, -0.992002367973328, -0.985399917761485, -0.947475296258926, -0.97899394830068, -0.813485358158747, -0.914267784357071, -0.984973229964574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.822359519429103, 0.844271860093992, 0.824084857432136, 0.0586980369196659, 0.904392720258788, 0.883962829821275, 0.646233184246241, 0.678734331531461, 0.0980486689265432, 0.232666425358798, 0.179220090949755, 0.200595177693205, 0.185450050858544, 0.431346373138848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.7221694946289, -94.4373237609863, -93.4381477355957, -94.2494300842285, -0.798570090532303, -0.883643392721812, -0.96787649790446, -0.992282958825429, -0.986005542675654, -0.949424433708191, -0.97916685740153, -0.815154095490774, -0.917275851964951, -0.987748211622238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.881037896284368, 0.912881552497696, 0.847387001671172, 0.068682628793169, 0.91102489095453, 0.901980393141646, 0.673398915173142, 0.813847098103695, 0.118759648707669, 0.249762053798842, 0.221481882635416, 0.203425636161273, 0.192658649680715, 0.317009482200462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.1178550720215, -95.2109125773112, -93.5550145467122, -94.2591102600098, -0.798792252937953, -0.883933482567469, -0.968112466732661, -0.99291933576266, -0.986326889197032, -0.950538390874863, -0.98023915886879, -0.815257728099823, -0.91770582596461, -0.986668676137924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.877984800936715, 0.917959600132057, 0.811874657374725, 0.0813711186551287, 0.879384090334837, 0.886034873666522, 0.766725633597128, 0.660096051429959, 0.0863922361645234, 0.27207342637864, 0.135075375672451, 0.247847663162413, 0.0603126285432683, 0.196666489203792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.0972671508789, -95.2681686401367, -93.3769101460775, -94.271411895752, -0.797732359170914, -0.883676753441493, -0.968923127651215, -0.992195173104604, -0.985824684302012, -0.951992207765579, -0.978046780824661, -0.816884167989095, -0.909811733166377, -0.985532432794571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806131330505805, 0.826361964561616, 0.80760649279046, 0.203739815133923, 0.904553041114022, 0.925760585458807, 0.683905001484441, 0.682024630843239, 0.12226340370041, 0.094768129030728, 0.152918202685757, 0.461368583104827, 0.0613108462543248, 0.336649785245365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.6127380371094, -94.2353858947754, -93.355504099528, -94.3900497436523, -0.798575460910797, -0.884316353003184, -0.968203725417455, -0.992298456033071, -0.98638125260671, -0.940438932180405, -0.97849950393041, -0.824701887369156, -0.909871274232864, -0.986854114135106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826804581871891, 0.878061244087388, 0.88751947237267, 0.0558315063397479, 0.914090975412722, 0.922849531066019, 0.621252066015487, 0.770341326370337, 0.113447417296443, 0.219327656042924, 0.18759239018849, 0.336853046785586, 0.148486783158492, 0.27293001277104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.7521438598633, -94.8183062235514, -93.7562901814779, -94.2466509501139, -0.798894959688187, -0.884269483884176, -0.967659505208333, -0.992714424928029, -0.986244465907415, -0.948555274804433, -0.979379286368688, -0.820142954587936, -0.915071090062459, -0.986252490679423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895075723590766, 0.914816483973262, 0.847787541423713, 0.054836299804225, 0.906739763012202, 0.895029402389767, 0.70697941555489, 0.69582785828941, 0.0887789947826724, 0.193823146827108, 0.163420712911226, 0.161333907817998, 0.0770503292856054, 0.270951126086291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.2125162760417, -95.2327293395996, -93.5570233662923, -94.2456860860189, -0.798648711045583, -0.883821568886439, -0.96840415596962, -0.992363468805949, -0.985861716667811, -0.946893392006556, -0.97876598238945, -0.813716608285904, -0.910810093084971, -0.986233806610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854914518044453, 0.880387528518909, 0.721636940403648, 0.158011727383669, 0.874268591703169, 0.849020304943732, 0.693453389820792, 0.663521759213429, 0.0748230067191535, 0.199335083105, 0.187964104331776, 0.203369906083692, 0.269061076780727, 0.043649139434722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.9416974385579, -94.8445355733236, -92.9243426005046, -94.3457158406575, -0.797561001777649, -0.883080804347992, -0.96828666528066, -0.992211308081945, -0.985645178953807, -0.947252551714579, -0.979388717810313, -0.81525568763415, -0.922263030211131, -0.984087687730789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.856678226981868, 0.887790890716938, 0.87958727418424, 0.0940575100320303, 0.905602333104384, 0.920436157146572, 0.65848540534158, 0.706559717877994, 0.0961609284067332, 0.199534892357751, 0.140065444241066, 0.249643994962039, 0.124082778389511, 0.31239200979261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.9535906473796, -94.9280100504557, -93.7165079752604, -94.2837114969889, -0.798610609769821, -0.884230627616246, -0.967982923984528, -0.99241401553154, -0.985976252953211, -0.94726557135582, -0.978173393011093, -0.816949937740962, -0.913615455230077, -0.986625079313914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882511022803727, 0.898112607837746, 0.847503477150547, 0.126326439285277, 0.90206940238221, 0.882105752349593, 0.697637571587162, 0.726778185315622, 0.0650700648557268, 0.242820534610034, 0.186197542066642, 0.238535747833061, 0.120650472343048, 0.308934850143131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.1277887980143, -95.0443895975749, -93.5555987040202, -94.3149965922038, -0.79849226474762, -0.883613493045171, -0.968323010206223, -0.992509243885676, -0.985493854681651, -0.950086079041163, -0.979343895117442, -0.816543227434158, -0.913410727183024, -0.986592437823613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843172989540205, 0.865784769587706, 0.665789458071589, 0.127507361747841, 0.865337836314953, 0.871583999838085, 0.647560054547818, 0.613200005905728, 0.0332066644334621, 0.190052414177835, 0.170310305745245, 0.222916783110147, 0.242725057073255, 0.0174482504508204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.8625208536784, -94.6798863728841, -92.644251759847, -94.3161415100098, -0.797261842091878, -0.883444088697434, -0.967888023455938, -0.991974294185638, -0.984999469916026, -0.946647689739863, -0.978940790891647, -0.815971364577611, -0.92069215575854, -0.983840306599935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872006572103117, 0.848068622075136, 0.815222275222987, 0.0487533162621185, 0.884668035592056, 0.914328125807886, 0.640379721414393, 0.696260659198873, 0.062021662277063, 0.237514963206644, 0.144022277477742, 0.270621783785744, 0.348552655934298, 0.177611392865635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.0569541931152, -94.4801330566406, -93.3936993916829, -94.2397885640462, -0.797909359137217, -0.884132285912832, -0.967825653155645, -0.9923655072848, -0.9854465564092, -0.949740366141001, -0.978273789087931, -0.817718005180359, -0.927004494269689, -0.985352520147959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.908545321787125, 0.968630932509672, 0.895353956913402, 0.0299212491022054, 0.93119441706198, 0.955764190032728, 0.819568740847869, 0.792883673155214, 0.128342921856626, 0.313480349401828, 0.241251875602057, 0.156418265356563, 0.00460699724368048, 0.420440611619946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.3033457438151, -95.839498647054, -93.7955823262533, -94.2215306599935, -0.799467885494232, -0.884799422820409, -0.969382137060165, -0.992820598681768, -0.98647558093071, -0.954690297444661, -0.98074077963829, -0.813536630074183, -0.906489038467407, -0.987645242611567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.965281303203127, 1.18136668680308, 0.990833019748755, 0.42540856192391, 0.967822364729644, 0.990686476973839, 0.965212484520598, 1.02951946865888, 0.145435028022883, 0.579511139053302, 0.294870720686916, 0.185316236987945, 0.412290728776545, 0.475775788182557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.6859331766764, -98.2381393432617, -94.2744366963704, -94.6049601236979, -0.800694837172826, -0.885361685355504, -0.970647237698237, -0.993935145934423, -0.986740777889887, -0.972024957338969, -0.982101241747538, -0.814594682057699, -0.930806303024292, -0.988167701164881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966135287404872, 1.20114630711425, 0.974357596150964, 0.385577741788736, 0.962713271814725, 0.987055988621329, 0.927635819505373, 1.06022766340242, 0.12780446378541, 0.548468958932807, 0.341943653867797, 0.151719574063749, 0.241455433932751, 0.44047589236661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.6916918436686, -98.4611587524414, -94.1918078104655, -94.5663436889648, -0.800523694356283, -0.885303233067195, -0.970320836702983, -0.994079780578613, -0.986467226346334, -0.970002237955729, -0.983295615514119, -0.813364595174789, -0.920616426070531, -0.987834409872691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756583879151205, 1.0097647197577, 0.829616200365002, 0.232300983612372, 0.610484141699197, 0.654214864937055, 0.620952885468264, 0.725083259336808, 0.130719180222253, 0.0788224786110566, 0.180309157792994, 0.497009134414756, 0.118605671594039, 0.122407735250068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.2786249796549, -96.3032908121745, -93.4658889770508, -94.4177401224772, -0.788724831740061, -0.879944360256195, -0.967656906445821, -0.992501260836919, -0.986512450377146, -0.939399907986323, -0.979194490114848, -0.82600680788358, -0.913288760185242, -0.984831303358078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.793335332902421, 1.03274993376141, 0.784164598259236, 0.303070031167716, 0.688075639652331, 0.670016867826392, 0.880870103034286, 0.552117286515521, 0.106150510107407, 0.502566800337315, 0.336768237210463, 0.146316035665076, -0.135745517371925, 0.0963760322396325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.5264508565267, -96.5624539693197, -93.2379364013672, -94.4863515218099, -0.791323967774709, -0.880198778708776, -0.969914617141088, -0.991686596473058, -0.986131248871485, -0.96701123714447, -0.983164300521215, -0.81316675345103, -0.898117379347483, -0.984585519631704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99104176455674, 1.18704327823274, 0.988197438766579, 0.39736152228299, 0.952173080093995, 0.982298716137383, 0.949482403929406, 1.03907652265988, 0.167779181226177, 0.626505037354998, 0.260294336210301, 0.457480935375354, 0.396050471417046, 0.435965108128588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8596435546875, -98.3021441141764, -94.2612185160319, -94.5777681986491, -0.800170622269313, -0.885226639111837, -0.970510601997375, -0.993980159362157, -0.987087464332581, -0.975087096293767, -0.981223940849304, -0.824559547503789, -0.929837614297867, -0.987791820367177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97499641061887, 1.17946024237629, 1.00246515255981, 0.412821061655043, 0.955096755978962, 1.00339775208354, 0.922506977448454, 1.04802782412088, 0.156656084460972, 0.624571311885715, 0.326623894352047, 0.121456622518529, 0.297730956677163, 0.390626213262318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.7514450073242, -98.2166437784831, -94.3327751159668, -94.5927563985189, -0.800268558661143, -0.885566341876984, -0.970276286204656, -0.994022319714228, -0.986914881070455, -0.974961094061534, -0.982906909783681, -0.812256566683451, -0.923973113298416, -0.987363743782044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988316701119826, 1.20612434558449, 1.00365206659801, 0.413168360931009, 0.959300626218121, 1.00032689203418, 1.04713351640986, 1.04946627548669, 0.334736781718714, 0.533868857500568, 0.58677070382001, 0.428785697502344, 0.0787242292667105, 0.0236809859586355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8412676493327, -98.5172871907552, -94.3387278238932, -94.5930931091309, -0.800409378608068, -0.885516899824143, -0.971358825763067, -0.994029094775518, -0.989677937825521, -0.969050890207291, -0.989507571856181, -0.82350891828537, -0.910909936825434, -0.983899154265722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981044861965436, 1.18675035558626, 1.02651731369717, 0.395749098831802, 0.980081483089499, 0.998534353835376, 0.940436080808006, 1.04338808025804, 0.18391448389468, 0.607085364775678, 0.403476791866534, 0.6783713034055, -0.0829564618458327, 0.487700874148602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.7922314961751, -98.2988413492838, -94.4534034729004, -94.5762049357096, -0.801105489333471, -0.885488039255142, -0.970432023207347, -0.994000466664632, -0.987337815761566, -0.973821703592936, -0.984856885671616, -0.832647087176641, -0.901266107956568, -0.988280294338862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788527202719386, 1.06920767232234, 0.916159864801225, 0.328043314829909, 0.782191455011106, 0.79382232054348, 0.806136037486298, 0.960138023837841, 0.144827806102864, 0.393361240767584, 0.247408219807942, 0.258549248946307, 0.626770101847324, 0.358624602207818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.4940282185872, -96.9735226949056, -93.8999298095703, -94.5105634053548, -0.794476630290349, -0.882192095120748, -0.969265456994375, -0.99360836148262, -0.98673135638237, -0.959895364443461, -0.980896983544032, -0.817275989055634, -0.943599434693654, -0.987061593929927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.893537729873606, 1.16205585099059, 0.954051107939404, 0.311073653152913, 0.882527517891518, 0.977211466567966, 0.934846802633685, 0.997552523511973, 0.163735943747344, 0.585206327827613, 0.339007996983053, 0.419605266085339, 0.451248599878751, 0.342625795768573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.202145131429, -98.0204055786133, -94.089965057373, -94.4941111246745, -0.797837656736374, -0.885144732395808, -0.970383473237356, -0.993784582614899, -0.987024730443954, -0.972396057844162, -0.983221129576365, -0.823172791798909, -0.933130037784576, -0.986910537878672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.718393655867371, 0.978515532444934, 0.824014018840631, 0.0142762561137712, 0.684148935286838, 0.698347387387281, 0.712016078895803, 0.797081335777217, 0.174136059711112, 0.303972776911668, 0.238250990598212, 0.317564904919709, 0.043480229023817, 0.420081617502101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.021097056071, -95.950949605306, -93.4377924601237, -94.2063626607259, -0.791192432244619, -0.880654911200205, -0.968447905778885, -0.99284036954244, -0.987186096111933, -0.954070780674616, -0.980664638678233, -0.819436750809352, -0.908807724714279, -0.987641853094101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.861383701053035, 1.12155683097439, 0.98033313812577, 0.58818358806316, 0.928736104636195, 0.916018487108113, 0.958808465437082, 1.00310848918318, 0.128152764844558, 0.502553231724851, 0.282753403412178, 0.392196975164567, 0.157543623642881, 0.540463750537418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.9853210449219, -97.5637705485026, -94.2217768351237, -94.7627723693848, -0.799385537703832, -0.884159501393636, -0.97059161067009, -0.993810751040777, -0.986472630500793, -0.967010353008906, -0.981793791055679, -0.822169282039007, -0.915611306826274, -0.988778465986252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991158902647652, 1.24291914705671, 1.08868880099675, 0.803274371149591, 1.01117643360533, 1.00715398712644, 1.06181234792226, 1.07892921849068, 0.201551706828867, 0.64194907599121, 0.497560562311794, 0.492234689287178, 0.348432375496679, 0.519230279575644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8604334513346, -98.9321563720703, -94.7652109781901, -94.9713053385417, -0.802147098382314, -0.885626818736394, -0.971486330032349, -0.994167864322662, -0.987611470619837, -0.976093435287476, -0.987244057655335, -0.825831999381383, -0.92699731985728, -0.98857798576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.990554166882108, 1.20906218808458, 0.995850542031854, 0.285601454669799, 0.966142346888538, 0.98744766673251, 0.96061384162917, 1.01842103598031, 0.149687630292781, 0.535814901440492, 0.352928836513576, 0.313657993141995, 0.41613420672054, 0.390673139222612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8563555399577, -98.5504119873047, -94.299600982666, -94.4694155375163, -0.800638560454051, -0.885309539238612, -0.97060729265213, -0.993882872660955, -0.986806760231654, -0.969177695115407, -0.98357434074084, -0.819293705622355, -0.931035556395849, -0.987364186843236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960325864139504, 1.23021942673728, 1.1026746309459, 0.878329312111334, 1.01453332574137, 1.0243095871177, 1.03883788943219, 1.06120420736484, 0.0218962277971043, 0.496540659383946, 0.271168169053734, 0.657874247548986, -0.0665740397375742, 0.309222508384096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.652517191569, -98.7889643351237, -94.8353538513184, -95.0440719604492, -0.802259546518326, -0.885903030633926, -0.971286767721176, -0.994084380070368, -0.984823979934057, -0.966618571678797, -0.981499840815862, -0.831896620988846, -0.902243276437124, -0.986595153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956566206611154, 1.25748940413733, 1.10816500209499, 0.803746005664845, 1.01462745419022, 1.02545660918557, 1.04516482606584, 1.10082489491083, 0.093343147227898, 0.444040862074624, 0.285936817522405, 0.607354091114062, 0.165855997835156, 0.485437275247302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.6271647135417, -99.0964391072591, -94.8628896077474, -94.9717625935872, -0.802262699604034, -0.885921498139699, -0.971341725190481, -0.994270992279053, -0.985932532946269, -0.963197666406632, -0.981874563296636, -0.83004690806071, -0.91610711812973, -0.988258922100067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98971281669854, 1.20793301379872, 1.02988714149752, 0.573222963512043, 0.987380678697549, 1.00830310702918, 0.971259454036657, 1.00879901965959, 0.177300093119328, 0.598331749769536, 0.380903320964776, 0.442433217513893, 0.371473757130184, 0.422502618279221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8506820678711, -98.5376803080241, -94.470304107666, -94.7482678731283, -0.801349995533625, -0.885645320018133, -0.970699763298035, -0.993837553262711, -0.987235188484192, -0.973251314957937, -0.98428413271904, -0.824008599917094, -0.928371677796046, -0.987664711475372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91350773784586, 1.08018427579415, 0.857788409031661, 0.270319237284585, 0.889203105111878, 0.873699851411578, 0.8590344977129, 0.92062701293557, 0.209413066616692, 0.592489440646601, 0.338135521949447, 0.381779737585672, 0.381240955026014, 0.364663952255908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.3368087768555, -97.0972862243652, -93.6071805318197, -94.4545992533366, -0.798061273495356, -0.883478154738744, -0.969724947214127, -0.993422265847524, -0.987733445564906, -0.972870628039042, -0.983198992411296, -0.821787871917089, -0.92895426551501, -0.987118615706762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94572667157772, 1.25793482158728, 1.10658221340833, 0.754801727263018, 1.01692425951694, 1.02575055287202, 1.05279896210882, 1.11831494491918, 0.147563762143177, 0.61516341533745, 0.326438781178518, 0.369066496781273, 0.102853530970319, 0.476733877407951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.5540705362956, -99.1014612833659, -94.8549514770508, -94.9243105570475, -0.802339637279511, -0.885926230748494, -0.971408037344615, -0.994353369871775, -0.986773806810379, -0.974348072210948, -0.982902212937673, -0.821322397391001, -0.912349186340968, -0.988176747163137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957345480394968, 1.21420769792234, 1.04321159152612, 0.558474810572357, 0.992054420122488, 1.01726345338418, 1.03407478873232, 1.03366777679121, 0.148893708760914, 0.567119184466014, 0.421563382547012, 0.411850048648501, 0.424829139989547, 0.412204158650179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.6324195861816, -98.608428700765, -94.5371299743652, -94.7339693705241, -0.801506555080414, -0.885789585113525, -0.971245394150416, -0.99395468433698, -0.9867944419384, -0.971217493216197, -0.98531579375267, -0.822888847192129, -0.931554186344147, -0.987567476431529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899723760021089, 1.06847555742422, 0.823514345626102, 0.391311589880449, 0.825685559972333, 0.858213757773849, 0.909725700844135, 0.960935710504323, 0.225622639363977, 0.561255379001987, 0.376088890656831, 0.275312281074941, 0.364590025410788, 0.438548140248468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.2438593546549, -96.9652679443359, -93.4352864583333, -94.5719027201335, -0.795933582385381, -0.883228822549184, -0.970165264606476, -0.993612118562063, -0.987984949350357, -0.97083540558815, -0.984161976973216, -0.817889740069707, -0.927961081266403, -0.987816208600998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976721802653397, 1.20225718924132, 1.01469604133972, 0.475012813874322, 0.945626318954868, 0.992907713899237, 0.89732297454996, 1.0356769685376, 0.182188088718443, 0.537756432673349, 0.39040352635896, 0.292023598730413, 0.293617905323678, 0.431154671121639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.7630798339844, -98.4736841837565, -94.3941164652506, -94.6530520121257, -0.799951320886612, -0.88539744814237, -0.970057531197866, -0.993964147567749, -0.987311029434204, -0.969304205973943, -0.984525179862976, -0.818501597642899, -0.923727780580521, -0.987746401627858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.899396180672195, 0.887102216876573, 0.772610352403483, -0.000554524674819127, 0.899744661013024, 0.911174833188177, 0.745365789390602, 0.698410743249152, 0.0580925190054755, 0.197883912379199, 0.184617032635818, 0.179591884354928, 0.239876932227291, 0.258384858949636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.241650390625, -94.920245107015, -93.1799886067708, -94.1919840494792, -0.798414391279221, -0.884081516663233, -0.968737590312958, -0.992375634113948, -0.985385592778524, -0.947157992919286, -0.979303793112437, -0.814385094245275, -0.920522272586823, -0.986115159591039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909283110735135, 0.956135967082416, 0.883432232694985, 0.10899321507317, 0.920304402032268, 0.919484233721989, 0.84434560202307, 0.889928098523419, 0.10434984485238, 0.288411255435405, 0.197802979131846, 0.218439709769471, 0.104248764061049, 0.362069346468695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.3083208719889, -95.6986152648926, -93.7357915242513, -94.2981918334961, -0.799103095134099, -0.884215301275253, -0.969597355524699, -0.993277674913406, -0.986103310187658, -0.953056786457698, -0.979638357957204, -0.815807443857193, -0.912432408332825, -0.987094118197759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.960015406713752, 1.22122356408076, 1.09311796237989, 0.78485990251486, 1.01472781041925, 1.01940855124386, 1.08481494036287, 1.08756245768489, 0.307538182503622, 0.68073618961468, 0.509543194874827, 0.306117447746943, 0.353392519569392, 0.418617653798815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.6504236857096, -98.6875340779622, -94.7874244689941, -94.9534523010254, -0.802266061306, -0.88582412203153, -0.971686136722565, -0.994208526611328, -0.989255930980047, -0.978620817263921, -0.987548091014226, -0.819017620881399, -0.927293179432551, -0.987628030776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.813242962767022, 0.961686633576731, 0.742645932442496, 0.48149975578877, 1.00867405222082, 0.985608976166481, 0.699854206666034, 0.819058004180425, 0.376887740519822, 0.441794174272021, 0.358278873465737, 0.236669360015753, -0.193679950843236, -0.406948030235455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.6606938680013, -95.761200205485, -93.0297086079915, -94.6593411763509, -0.802063274383545, -0.885279935598373, -0.968342264493307, -0.992943878968557, -0.990331941843033, -0.963051271438599, -0.983710086345673, -0.816474892695745, -0.894661742448807, -0.979833281040192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828126892156361, 0.948206147081092, 0.749104059152708, 0.57525036238211, 1.00102965965477, 1.01776693375394, 0.996565828183434, 0.617909352254016, 0.610073122734127, 0.549660588019754, 0.584259538692325, 0.0299468583593159, -0.164277895843133, -0.163375361177309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.7610605875651, -95.6092048645019, -93.0620979309082, -94.7502334594727, -0.801807204882304, -0.885797691345215, -0.970919581254323, -0.991996475060781, -0.993949989477793, -0.970079884926478, -0.989443856477737, -0.808906086285909, -0.896415497859319, -0.982133022944133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968580215059656, 1.24751458393673, 1.08734180289743, 0.805292589147563, 1.01424530573655, 1.02211463482925, 1.09500309015993, 1.06261270857021, 0.218686454264502, 0.731297230396165, 0.505308613572793, 0.197153913233637, 0.285696484190489, 0.49053010973733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.7081787109375, -98.983970896403, -94.7584554036458, -94.9732620239258, -0.802249898513158, -0.885867691040039, -0.971774633725484, -0.994091014067332, -0.987877329190572, -0.981915392478307, -0.987440647681554, -0.815028099219004, -0.923255288600922, -0.988307007153829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.940343938705329, 1.24563274708731, 1.09163922579758, 0.839692792280919, 1.01636708078439, 1.02493906098195, 1.05226304466069, 1.07932531990784, 0.227882882744466, 0.637149568095817, 0.472206791774135, 0.143026658729511, 0.182742658454826, 0.512404972300029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.5177731831868, -98.9627527872721, -94.7800081888835, -95.0066134134928, -0.80232097307841, -0.88591316541036, -0.971403382221858, -0.994169729948044, -0.988020018736521, -0.975780697663625, -0.986600760618846, -0.813046318292618, -0.917114363114039, -0.98851354320844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.982563584090689, 1.23460586837265, 1.09675243342225, 0.745704794566155, 1.01652538502509, 1.02563504855191, 1.09429150706938, 1.1081753392067, 0.31555000322692, 0.595528901312247, 0.498730909812444, 0.548026140499484, -0.00855150276099976, 0.308700641202244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8024726867676, -98.8384223937988, -94.8056523640951, -94.9154909769694, -0.802326275904973, -0.885924371083577, -0.971768452723821, -0.99430561264356, -0.989380240440369, -0.97306868036588, -0.987273752689362, -0.827874712149302, -0.905704168478648, -0.986590226491292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01753782747611, 1.24706871538545, 1.09465572267051, 0.802477209140768, 1.01536933108896, 1.02511713014213, 1.12947175419984, 1.10473908559212, 0.432705802388332, 0.648394563297863, 0.565281131627202, 0.388077724736826, -0.0224873787981359, 0.440106797593636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-89.0383143107096, -98.9789436340332, -94.7951367696126, -94.9705324808756, -0.802287550767263, -0.885916032393773, -0.972074037790298, -0.994289427995682, -0.991198001305262, -0.976513425509135, -0.988962320486705, -0.82201846241951, -0.904872930049896, -0.987830924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860529943132213, 1.16591687235572, 1.03990372847796, 0.641198140532374, 0.999644304783999, 0.980109316941247, 0.990997593289192, 1.01807007072039, 0.197718602452257, 0.498837749245879, 0.297541863062281, 0.416049828224375, 0.580648866161186, 0.477563814571355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.9795639038086, -98.0639394124349, -94.5205401102702, -94.8141705830892, -0.801760798692703, -0.885191388924917, -0.97087121407191, -0.993881219625473, -0.987551997105281, -0.966768250862757, -0.982169016202291, -0.82304261525472, -0.940848424037298, -0.988184583187103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.920322640390627, 1.22410305662425, 1.07540699610449, 0.763797932677434, 0.999565656817281, 1.00399106914672, 1.03406037866009, 1.07564271567812, 0.18928228981313, 0.58533923924723, 0.358072148094285, 0.489185597437824, 0.24598362100877, 0.560212214764364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.382763671875, -98.72000096639, -94.6985989888509, -94.9330324808757, -0.801758164167404, -0.88557589451472, -0.971245268980662, -0.994152384996414, -0.987421101331711, -0.972404718399048, -0.983704841136932, -0.82572036186854, -0.920886520544688, -0.988964925209681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83446479451637, 1.11000881745208, 1.03509583163315, 0.220810991025273, 0.963146725314559, 0.962327451539076, 0.843790471145302, 0.972914087332177, 0.201282541819193, 0.419341108788588, 0.250972901279383, 0.356593052678755, 0.166817575147049, 0.461106059614511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.8037989298503, -97.4335642496745, -94.496427154541, -94.4066004435221, -0.80053821404775, -0.88490509390831, -0.969592533508937, -0.993668536345164, -0.98760729432106, -0.961588221788406, -0.980987429618835, -0.820865702629089, -0.916164473692576, -0.988029193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879150411682312, 1.12991386648714, 1.00276164020801, 0.734176242316238, 0.950868389804467, 0.93871891147543, 0.839482317011505, 0.977128201450725, 0.195512140852966, 0.422293791316991, 0.305908289421144, 0.282887393226973, 0.141042519950784, 0.574260332181117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.1051272074381, -97.6579978942871, -94.3342620849609, -94.9043139139811, -0.800126918156942, -0.884524987141291, -0.969555111726125, -0.993688384691874, -0.987517762184143, -0.961780619621277, -0.982381296157837, -0.818167090415955, -0.914627059300741, -0.9890975634257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981290980182208, 1.19049772197213, 0.995007172344006, 0.41542606853545, 0.965468323137566, 0.953703499176217, 0.953166579062565, 1.01901666452238, 0.123188578388753, 0.613686814897505, 0.355301793201638, 0.240443159933381, 0.446024511694238, 0.4773575928624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.7938911437988, -98.3410936991374, -94.2953712463379, -94.5952819824219, -0.80061598221461, -0.884766244888306, -0.970542603731155, -0.993885678052902, -0.986395607391993, -0.97425185640653, -0.983634549379349, -0.81661306420962, -0.932818434635798, -0.988182636102041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972017346846382, 1.23955731441968, 1.09190833131306, 0.886632755148229, 1.01380242159818, 1.02108570852459, 1.05584291831867, 1.09149647452869, 0.155113443703807, 0.641839215967151, 0.424843894937771, 0.278159073285319, 0.108847933583085, 0.402764254707405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.7313563028971, -98.8942509969076, -94.781357828776, -95.0521222432454, -0.802235062917074, -0.885851124922434, -0.971434477965037, -0.994227055708567, -0.986890945831935, -0.976086276769638, -0.985399029652278, -0.817993970712026, -0.912706736723582, -0.987478347619375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.936507760511667, 1.25134779490507, 1.09700389267441, 0.859878119988213, 1.01488291180158, 1.02459970534057, 1.04352893977092, 1.04328937127867, 0.0879722680648055, 0.360861700194703, 0.245938512044012, 0.562601482192147, 0.108296262409483, 0.314533348680749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.491904703776, -99.0271911621094, -94.8069135030111, -95.0261833190918, -0.802271256844203, -0.885907701651255, -0.971327515443166, -0.994000001748403, -0.985849199692408, -0.957777682940165, -0.980859692891439, -0.828408364454905, -0.912673830986023, -0.986645297209422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.956938627296204, 1.23428942079199, 1.10901689066857, 0.884151296575205, 1.01482531966306, 1.02533394754646, 1.0600742187339, 1.08385285612748, 0.201040267700114, 0.5142147680839, 0.388763661688906, 0.395502034663345, 0.0483859787584997, 0.486546663869372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.6296760559082, -98.8348543802897, -94.8671620686849, -95.0497164408366, -0.802269327640533, -0.885919523239136, -0.971471232175827, -0.994191054503123, -0.987603535254796, -0.967770222822825, -0.98448357184728, -0.82229029138883, -0.909100339810054, -0.988269396622976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961439128565016, 1.24478963870776, 1.0942905768599, 0.820445225080867, 1.01591951098283, 1.00529431821167, 1.07578943179026, 1.04266210524321, 0.312937745283351, 0.611792880527694, 0.517865848702388, 0.380790433744965, 0.162573617640186, 0.554262508030572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.6600242614746, -98.9532465616862, -94.793305460612, -94.9879526774089, -0.802305980523427, -0.885596877336502, -0.971607738733292, -0.993997047344844, -0.989339709281921, -0.974128446976344, -0.987759260336558, -0.821751650174459, -0.915911332766215, -0.988908749818802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992008248090486, 1.20939074773586, 1.0404497484875, 0.696125199815106, 0.996489548598627, 1.00988006184416, 0.971931237880086, 0.9545584355049, 0.398975277795716, 0.670693983302188, 0.505820650392462, 0.383266270930657, 0.20389592700993, 0.237204205996997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8661608378092, -98.5541165669759, -94.5232785542806, -94.8674229939779, -0.801655121644338, -0.885670709609985, -0.970705598592758, -0.993582081794739, -0.990674646695455, -0.977966463565826, -0.987453639507294, -0.821842298905055, -0.918376100063324, -0.985915178060532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95128367847397, 1.24111135849007, 1.10544555065444, 0.788237414204728, 1.01696079582727, 1.02536924053316, 1.08417495017088, 1.08497661989244, 0.183494473793946, 0.64106970793851, 0.432438468271483, 0.376808310781732, 0.180587936508322, 0.426793713268103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.5915430704753, -98.9117731730143, -94.849250793457, -94.9567268371582, -0.80234086116155, -0.885920091470083, -0.971680577596029, -0.994196347395579, -0.987331298987071, -0.976036135355631, -0.985591725508372, -0.821605851252874, -0.916985839605331, -0.987705226739248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.968852393296009, 1.22651701259861, 1.0816195456503, 0.729612037329923, 1.01204256954651, 1.02496682644352, 1.05526811654866, 1.03699266642907, 0.356202499162556, 0.688129589335422, 0.481914505590422, 0.366213464104561, 0.184638132922512, 0.541504328446394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.7100140889486, -98.7472188313802, -94.7297566731771, -94.899888865153, -0.802176111936569, -0.885913612445196, -0.971429485082626, -0.993970344463984, -0.990010994672775, -0.97910257379214, -0.986847072839737, -0.821217938264211, -0.917227423191071, -0.988788290818532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.986316113769979, 1.22173490998961, 1.06185806329522, 0.748179957684035, 0.998127751344309, 1.01238709792062, 0.997121416523811, 0.971819008227899, 0.478090198705763, 0.65281341825394, 0.538403231305478, 0.442636602451358, 0.406305353025753, 0.235999492442103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8277770996094, -98.6932996114095, -94.630647277832, -94.9178906758626, -0.801709997653961, -0.885711073875427, -0.970924407243729, -0.993663378556569, -0.991902174552282, -0.976801359653473, -0.988280351956685, -0.824016046524048, -0.930449291070302, -0.985903803507487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963468906153875, 1.23922052216918, 1.09467904819098, 0.797708401861962, 1.0154095447552, 1.02493215046707, 1.06838562817164, 1.09059501688393, 0.216359880020541, 0.62104969286302, 0.453742692375564, 0.509091165616005, 0.297469477464944, 0.447021958613851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.6737116495768, -98.8904535929362, -94.7952537536621, -94.9659090677897, -0.802288897832235, -0.885913054148356, -0.9715434273084, -0.994222809871038, -0.987841230630875, -0.974731624126434, -0.986132274071375, -0.826449171702067, -0.9239575167497, -0.98789621591568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888243359701474, 0.894955913529019, 0.847476855632623, 0.113996003435189, 0.904879495419316, 0.928971753640626, 0.719990109658346, 0.750078988275192, 0.0860384288754032, 0.267904904699702, 0.220771812306507, 0.227864387612181, 0.0270549043390838, 0.217086646997065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.1664436340332, -95.0087972005208, -93.5554651896159, -94.3030420939128, -0.798586396376292, -0.884368054072062, -0.968517170349757, -0.992618989944458, -0.985819194714228, -0.951720585425695, -0.980221142371496, -0.816152513027191, -0.907827997207642, -0.985725233952204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906670358062787, 1.00785845577144, 0.964837335679949, 0.137607632609799, 0.936901554809802, 0.95594188898676, 0.864309041611237, 0.876824270597636, 0.204667592737732, 0.284602134284802, 0.291526467973294, 0.310277017013677, 0.041076119196818, 0.480212290519274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.2907023111979, -96.281797281901, -94.1440610249837, -94.3259338378906, -0.799659061431885, -0.884802283843358, -0.969770763317744, -0.993215956290563, -0.987659815947215, -0.952808582782745, -0.982016388575236, -0.819169916709264, -0.908664325873057, -0.988209589322408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01145731966552, 1.24963674501793, 1.09129147271201, 0.775364519968908, 1.01568671062886, 1.0254811661938, 1.10768486864646, 1.107804125951, 0.262362766821678, 0.621852558334434, 0.497151809872787, 0.448176888460072, 0.0524505981661796, 0.464234106250919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9973116556803, -99.0078987121582, -94.7782641092936, -94.9442464192708, -0.802298182249069, -0.885921893517176, -0.971884791056315, -0.994303864240646, -0.988555000225703, -0.974783939123154, -0.987233686447144, -0.824218895037969, -0.909342783689499, -0.98805872797966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801300760797949, 0.936786900432488, 0.774393487027889, 0.428035078276085, 1.00997209954484, 1.02543563083682, 0.712760141831681, 0.733079952164171, 0.368502008365384, 0.574061008567462, 0.583531928028864, 0.0529550778674492, -0.578439916423912, -0.0473560798683832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.5801640828451, -95.4804504394531, -93.1889315287272, -94.6075065612793, -0.802106755971909, -0.885921160380046, -0.9684543689092, -0.992538925011953, -0.990201830863953, -0.971669824918111, -0.989425394932429, -0.809748494625092, -0.871711820363998, -0.983228443066279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785770158245416, 0.933321066384591, 0.787901752299299, 0.724725452577634, 0.967211271214486, 1.0216200394072, 0.999154609095904, 0.690345291602834, 0.653621127327602, 0.645204689227089, 0.555172339268274, 0.0849357313365229, -0.0898321659868668, 0.0778253373671675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.4754366556803, -95.4413724263509, -93.256679280599, -94.8951512654622, -0.800674366950989, -0.885859727859497, -0.970942068099976, -0.992337646087011, -0.994625669717789, -0.976305572191874, -0.988705831766129, -0.810919413963954, -0.900855990250905, -0.98441036939621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00133004154933, 1.25460824251893, 1.09700886202443, 0.822893894824957, 1.01675071204286, 1.02526780404691, 1.11577257886768, 1.09854952638677, 0.39313227142488, 0.729112500841939, 0.511323617136457, 0.398995067860997, 0.108215287127329, 0.476896329611341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9290204366048, -99.0639533996582, -94.8069384256999, -94.9903266906738, -0.802333823839823, -0.885918458302816, -0.971955043077469, -0.994260275363922, -0.990583988030752, -0.981773034731547, -0.987593265374502, -0.822418183088303, -0.912669001022975, -0.988178280989329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981487769157862, 1.25363329977666, 1.09257097892494, 0.775228118440577, 1.01392051217264, 1.01501605522388, 1.13641031834365, 1.11377180086945, 0.304497591088424, 0.546411835318265, 0.579021008152644, 0.394817536904215, -0.108976174980152, 0.399096033451714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.795218149821, -99.0529607137044, -94.7846811930338, -94.9441141764323, -0.802239018678665, -0.885753401120504, -0.972134308020274, -0.994331971804301, -0.989208753903707, -0.969868195056915, -0.98931094010671, -0.822265229622523, -0.89971410036087, -0.987443713347117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01446044464277, 1.25579344358957, 1.1030148792988, 0.793412802962209, 1.0146808944753, 1.02550930186152, 1.11429108620379, 1.0960299164138, 0.386898066621806, 0.734604465341935, 0.476768140112183, 0.674072490342197, -0.131153442763546, 0.563847188030249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-89.0175626118978, -99.077316792806, -94.8370602925618, -94.9617444356283, -0.802264489730199, -0.885922346512477, -0.971942174434662, -0.994248408079147, -0.990487259626389, -0.982130893071492, -0.986716494957606, -0.832489693164825, -0.898391284545263, -0.988999245564143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952481722818469, 1.23207679133972, 1.09270885303396, 0.774232649594424, 1.01421831868915, 1.02485490078289, 1.04767652452845, 1.10287500448201, 0.187964636173947, 0.642365281744308, 0.570036911441503, 0.308129428357001, 0.397114408680421, 0.469693510350149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.5996218363444, -98.8099065144857, -94.7853726704915, -94.9431490580241, -0.802248994509379, -0.885911810398102, -0.97136354247729, -0.994280648231506, -0.987400656938553, -0.976120555400848, -0.989082988103231, -0.819091286261876, -0.929901075363159, -0.988110274076462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.829308493420488, 1.17451538240863, 1.05667680599997, 0.699084326047899, 1.00149348099696, 0.989227864726161, 1.00133418970333, 1.02571326728836, 0.183983375795342, 0.471704579656731, 0.343224333204953, 0.631246991688238, 0.387389313934178, 0.512002629537248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.7690284729004, -98.1608894348145, -94.6046618143717, -94.8702919006348, -0.801822741826375, -0.885338201125463, -0.970961000521978, -0.993917218844096, -0.987338884671529, -0.965000243981679, -0.983328109979629, -0.830921707550685, -0.929320998986562, -0.988509744405746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.916924164928173, 1.20695613132074, 1.08626243979163, 0.722255535672391, 1.01264352067682, 1.02383029355002, 1.11659029328385, 1.04379050917387, 0.169812388658925, 0.662304921847991, 0.496248326033461, 0.40526934124009, 0.279782956931513, 0.416516507100894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.3598467508952, -98.5266657511393, -94.7530420939128, -94.892756652832, -0.802196242411931, -0.885895313819249, -0.971962145964305, -0.994002362092336, -0.987119011084239, -0.977419829368591, -0.987210762500763, -0.822647905349731, -0.922902562220891, -0.987608192364375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828368220760273, 1.16405662070478, 1.04979379986369, 0.167120201748315, 0.978645772167632, 1.00556790055965, 1.01393545477043, 0.965660664682693, 0.301291428618274, 0.495262587563665, 0.411688565722136, 0.492832688756465, 0.142503972235641, 0.4001159891898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.7626879374186, -98.0429646809896, -94.5701416015625, -94.3545466105143, -0.801057396332423, -0.885601282119751, -0.971070458491643, -0.9936343729496, -0.989159007867177, -0.966535292069117, -0.985065241654714, -0.825853894154231, -0.914714231093725, -0.987453343470891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879414632372891, 1.14704443936755, 1.02540747529181, 0.713581972334595, 0.945568489567575, 0.962296971232374, 0.957713986141611, 1.01048129064103, 0.18014630181108, 0.430365011835636, 0.427704457265234, 0.251392410833228, -0.0174965567184844, 0.59778475798518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.1069089253744, -97.8511487325033, -94.4478373209635, -94.8843475341797, -0.799949383735657, -0.884904603163401, -0.970582103729248, -0.993845476706823, -0.987279349565506, -0.962306543191274, -0.985471610228221, -0.81701395312945, -0.905170619487762, -0.989319674173991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992545099579261, 1.20390867119827, 1.02370963094007, 0.387707441805048, 0.939398004975105, 1.00839775640261, 1.04733525742106, 1.02569006645987, 0.231372552032605, 0.591674531125922, 0.437490319536337, 0.568438271748971, 0.28973718741035, 0.386299345119845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8697809855143, -98.4923049926758, -94.4393221537272, -94.5684084574382, -0.799742686748505, -0.885646843910217, -0.971360578139623, -0.993917109568914, -0.988074163595835, -0.972817528247833, -0.985719905296962, -0.828622068961461, -0.923496305942535, -0.987322890758514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941215685959494, 1.24960221321138, 1.09669427174404, 0.822936913768507, 1.01665023718945, 1.02316614370932, 1.07526151993781, 1.09094640397708, 0.247458938890591, 0.590330445719159, 0.499057990068712, 0.278546579112015, -0.0342422850391838, 0.275634042322194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.5236516316732, -99.007509358724, -94.8053606669108, -94.9903683980306, -0.802330458164215, -0.885884620745977, -0.971603153149287, -0.994224464893341, -0.988323756059011, -0.972729947169622, -0.987282051642736, -0.818008158604304, -0.904171780745188, -0.986278021335602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.945055824069301, 1.25337193166798, 1.11361825524194, 0.915093196344215, 1.01653149418088, 1.02502297437691, 1.03796322092104, 1.0702495776395, 0.132026333608914, 0.506500539283737, 0.340365415283852, 0.429231321063305, -0.182606822502277, 0.274505083680795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.5495468139648, -99.0500137329102, -94.8902392069499, -95.0797149658203, -0.802326480547587, -0.885914516448975, -0.971279170115789, -0.994126983483632, -0.986532731850942, -0.967267560958862, -0.983255571126938, -0.823525234063466, -0.895322225491206, -0.986267362038294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979220811448671, 1.25837243498429, 1.11145050306809, 0.858628209829599, 1.01703386844793, 1.02591813285784, 1.15169666020271, 1.10982512902829, 0.280290923581734, 0.549031278822817, 0.519528735061538, 0.36772696711708, -0.115337148131833, 0.430953920600884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.7799313863118, -99.1063954671224, -94.8793673197428, -95.0249715169271, -0.802343308925629, -0.885928928852081, -0.97226708928744, -0.994313383102417, -0.988833169142405, -0.970038878917694, -0.987801452477773, -0.821273352702459, -0.899334685007731, -0.987744506200155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01132569959556, 1.24482710267294, 1.10097582314875, 0.787726433094764, 1.01638232401776, 1.02484786686596, 1.0827735134638, 1.0500424996995, 0.444080777162115, 0.619290987248886, 0.51375193550543, 0.430065644279305, 0.313001276051871, 0.498770560883096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9964241027832, -98.9536689758301, -94.8268338521322, -94.95623143514, -0.802321483691533, -0.885911697149277, -0.971668404340744, -0.994031808773677, -0.991374492645264, -0.974617026249568, -0.987654878695806, -0.823555781443914, -0.924883947769801, -0.988384811083476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00146694150748, 1.20963903390606, 1.04422092736286, 0.732492994994572, 1.00101293361661, 1.01944668247775, 1.07474618830716, 0.982868930083306, 0.540176143016518, 0.698335625209186, 0.587211404725513, 0.414901799479161, 0.0468949143692257, 0.357898617620155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9299435933431, -98.5569160461426, -94.5421920776367, -94.9026819864909, -0.801806644598643, -0.885824735959371, -0.971598676840464, -0.993715423345566, -0.992865484952927, -0.979767602682114, -0.989518753687541, -0.823000582059224, -0.909011401732763, -0.987054739395777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.974746671907336, 1.24813769019926, 1.11365121521652, 0.870563868179453, 1.01703386844793, 1.02566281401347, 1.11499146146037, 1.12118973848453, 0.272024279657084, 0.547608678411349, 0.49312614648402, 0.452913999319515, -0.119859106339995, 0.487187634609667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.749760945638, -98.9909965515137, -94.890404510498, -95.0365432739258, -0.802343308925629, -0.885924818118413, -0.971948258082072, -0.994366910060247, -0.988704905907313, -0.969946181774139, -0.987131543954213, -0.824392336606979, -0.899064962069194, -0.988275448481242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02335369974777, 1.24424010707161, 1.09540056738822, 0.812736964866623, 1.01637775697897, 1.02550189773843, 1.10963160078519, 1.05380398674604, 0.313030070674395, 0.637156581086528, 0.644816995581859, 0.590567182418594, 0.0138811152951151, 0.563365092177975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-89.0775324503581, -98.9470504760742, -94.7988723754883, -94.9804794311523, -0.802321330706279, -0.885922227303187, -0.971901700894038, -0.994049525260925, -0.989341141780217, -0.975781154632568, -0.990980370839437, -0.829432282845179, -0.907042215267817, -0.988994693756103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01978555130688, 1.21879702237939, 1.04126036103139, 0.791756573635565, 1.00694741499673, 1.01827720123652, 1.06434669078409, 0.941143294644237, 0.595999198907571, 0.690289925878479, 0.570036128390852, 0.474355427659153, 0.17964308054223, 0.25011410583848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-89.0534713745117, -98.6601743062337, -94.5273440043132, -94.9601387023926, -0.802005436023076, -0.885805906852086, -0.971508344014486, -0.993518896897634, -0.993731621901194, -0.979243342081706, -0.989082968235016, -0.825177379449209, -0.916929481426875, -0.986037069559097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995896998885156, 1.2411160273888, 1.0939853167877, 0.812087746053914, 1.01573540593857, 1.02567700524939, 1.1120257313569, 1.10092360389019, 0.284840990322364, 0.590534554240128, 0.539732224867703, 0.540086313789092, -0.0303462780865693, 0.409497603935239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8923838297526, -98.9118258158366, -94.7917744954427, -94.9798500061035, -0.802299813429515, -0.885925046602885, -0.9719224969546, -0.994271457195282, -0.988903766870499, -0.972743246952693, -0.988314072291056, -0.827584008375804, -0.904404167334239, -0.987541921933492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907533091793537, 0.925972129561626, 0.859855962882808, -0.0320349481700763, 0.931488012412853, 0.925819571639382, 0.774247005106629, 0.798427405662313, 0.151313888914515, 0.252973180280599, 0.223994065728946, 0.219883862208329, -0.069659461132311, 0.284246534265337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.2965199788411, -95.3585116068522, -93.6175498962402, -94.1614634195964, -0.79947772026062, -0.884317302703857, -0.968988460302353, -0.992846709489822, -0.986831992864609, -0.950747629006704, -0.980302900075912, -0.815860319137573, -0.902059239149094, -0.986359337965647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.979532739700423, 0.98511467119777, 0.954515184381394, 0.14013289705825, 0.954715082022827, 0.97653917219188, 0.915265115593925, 0.890577299887638, 0.158846155422189, 0.286144870276284, 0.264466038545188, 0.365580952143215, 0.132895260720926, 0.481983692913181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.7820348103841, -96.0253562927246, -94.0922925313314, -94.3283821105957, -0.800255773464839, -0.885133908192317, -0.970213381449382, -0.993280732631683, -0.986948861678441, -0.952909108002981, -0.981329788764318, -0.821194779872894, -0.914141096671422, -0.988226314385732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.991568433404, 1.22870253086114, 1.09134167328866, 0.868612277081856, 1.01620723442669, 1.02556150092926, 1.13151432475545, 1.04930893168626, 0.460622132278607, 0.753688520578811, 0.496949626195098, 0.625874601356295, 0.0316074406258188, 0.297504485848276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8631950378418, -98.7718610127767, -94.7785158793131, -95.034651184082, -0.802315618594488, -0.885923186937968, -0.972091780106227, -0.994028353691101, -0.991631144285202, -0.983374416828156, -0.98722855647405, -0.830725006262461, -0.908099544048309, -0.986484515666962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64791261694528, 0.854673828140816, 0.480400452535376, 0.31007503657918, 1.0119308253766, 0.991456999382854, 0.673074345451032, 0.444014502627039, 0.352363888555965, 0.596092837239246, 0.567800518786706, 0.259999099202247, -0.356150142629413, -0.625517790094483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-86.545822652181, -94.5546081542969, -91.7144737243652, -94.4931429545085, -0.802172368764877, -0.885374091068904, -0.968109647432963, -0.991177435715993, -0.989951435724894, -0.973105426629384, -0.989026244481405, -0.817329072952271, -0.884970821936925, -0.977769609292348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.659661499579514, 0.818376501211648, 0.40670240575868, 0.394829437758119, 0.884002374860168, 0.989495893981827, 0.370433551039757, -0.0744818305874501, 0.588253341897446, 0.4488702514087, 0.463339917745216, -0.0373657417933849, 0.264997323418846, -0.455923160949509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-86.625048828125, -94.1453481038411, -91.3448572794596, -94.5753133138021, -0.797887061039607, -0.885342516501745, -0.965480828285217, -0.988735334078471, -0.993611439069112, -0.963512351115545, -0.986375782887141, -0.80644154548645, -0.922020637989044, -0.979370872179667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02127727057538, 1.23739807280942, 1.09091892358402, 0.762324533860866, 1.01624833777581, 1.02512083220367, 1.08519303321041, 1.05732376334315, 0.443530282216063, 0.724888728992699, 0.545807914856699, 0.317169584943866, 0.0994301851669245, 0.500819100002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-89.063530476888, -98.869905090332, -94.7763956705729, -94.9316040039062, -0.802316995461782, -0.885916091998418, -0.971689420938492, -0.994066103299459, -0.991365951299667, -0.981497812271118, -0.98846822977066, -0.819422276814779, -0.912144992748896, -0.988404152790705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993981757156599, 1.24404387799451, 1.1017517009502, 0.755694108031035, 1.01675984612045, 1.02370516386989, 1.14693836286025, 1.0507553978837, 0.363076323006217, 0.693643141650305, 0.49479889928135, 0.43930858888947, -0.00964521867606026, 0.435777614717692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8794687906901, -98.9448379516602, -94.8307250976563, -94.9251757303874, -0.802334129810333, -0.885893299182256, -0.972225757439931, -0.994035166501999, -0.990117647250493, -0.979461838801702, -0.987173986434936, -0.823894196748734, -0.905638931194941, -0.987790050109227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00272408288625, 1.25577147495496, 1.10286153935555, 0.761267946637605, 1.01670658377194, 1.02501927231536, 1.1127574428023, 1.06704322314351, 0.565120005081108, 0.645826558555619, 0.620564585782641, 0.63994489939554, -0.104936604281719, 0.353598263697412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9384208679199, -99.0770690917969, -94.8362912495931, -94.9305796305339, -0.802332345644633, -0.88591445684433, -0.971928852796555, -0.994111881653468, -0.993252507845561, -0.976346093416214, -0.99036501844724, -0.831240167220434, -0.899955050150553, -0.987014136711756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963383711386532, 1.24381744768358, 1.07969914540871, 0.782103804710759, 1.01589519298408, 1.02519820528991, 1.09427183617714, 1.03406008170915, 0.335931761676036, 0.658255438063565, 0.486407493606771, 0.33415342105077, 0.097944616837527, 0.409918674996091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.6731371561686, -98.9422849019368, -94.7201253255208, -94.9507802327474, -0.802305165926615, -0.885917337735494, -0.971768281857173, -0.993956532080968, -0.989696478843689, -0.977155963579814, -0.986961072683334, -0.820044112205505, -0.912056382497152, -0.987545897563299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.844162214306666, 1.20659369395982, 1.03084171306882, 0.626389656147457, 0.989179024361886, 0.981281883233759, 1.01315205005005, 0.963087903720819, 0.224768149302337, 0.528984797330206, 0.350045644022345, 0.475177107147718, 0.330715276884673, 0.568591339487889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.8691914876302, -98.5225791931152, -94.4750915527344, -94.7998135884603, -0.801410235961278, -0.885210267702738, -0.971063653628031, -0.993622255325317, -0.987971691290538, -0.968732643127441, -0.983501185973485, -0.825207463900248, -0.925940541426341, -0.989044038454692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.949423385296111, 1.23359454430838, 1.07988209862142, 0.82004834909556, 1.00974356966869, 1.02132029582432, 1.04630528035366, 1.02520791106073, 0.294268296305869, 0.640816417008768, 0.445470858535155, 0.638197623087768, 0.332971725903038, 0.518904743877931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.5789985656738, -98.8270195007324, -94.7210428873698, -94.9875679016113, -0.802099100748698, -0.885854901870092, -0.971351631482442, -0.993914838631948, -0.989050038655599, -0.976019630829493, -0.985922394196192, -0.831176193555196, -0.926075132687887, -0.988574912150701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821577002285401, 1.1628452557572, 1.03827738191721, 0.193227454270036, 0.994733551839447, 1.01512884469887, 0.972659289624594, 0.900125073557229, 0.367945751085633, 0.476586383473561, 0.412423850281959, 0.59678084187689, 0.0967882791493496, 0.524827936391993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-87.7168927510579, -98.0293062845866, -94.5123835245768, -94.3798578898112, -0.801596299807231, -0.885755217075348, -0.970711922645569, -0.993325702349345, -0.990193200111389, -0.965318344036738, -0.985083897908529, -0.829659785827001, -0.911987409989039, -0.988630837202072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963137404602323, 1.19724628803943, 1.04948002090575, 0.679090485101516, 0.995243933252428, 1.02193397422599, 1.0506809102225, 1.04437854471754, 0.207771825927339, 0.488629792422484, 0.294599785162213, 0.716373192910176, 0.00471858391386267, 0.551805313239232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.6714762369792, -98.4171852111816, -94.5685679117839, -94.8509076436361, -0.801613396406174, -0.885864782333374, -0.971389639377594, -0.994005131721497, -0.987707980473836, -0.966103096803029, -0.982094367345174, -0.834038464228312, -0.906495694319407, -0.988885549704234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00829383694114, 1.23813889396315, 1.05868908850914, 0.561807991765523, 1.00499568800363, 1.02334717451875, 0.982092626114427, 1.04629198031731, 0.292397714735296, 0.590179605436333, 0.470178220761699, 0.606900653403952, 0.285246107065848, 0.353764503646464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9759793599447, -98.878258005778, -94.6147539774577, -94.7372009277344, -0.801940057675044, -0.885887535413106, -0.970793863137563, -0.994014143943787, -0.989021015167236, -0.972720118363698, -0.986549290021261, -0.830030306180318, -0.923228424787521, -0.987015706300735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.984859505757967, 1.24839511117133, 1.09366124417616, 0.79561437609152, 1.01360514924727, 1.02463117286368, 1.07826704928839, 1.10996855233161, 0.309703667507722, 0.645615284587618, 0.452355048319695, 0.563037663656226, 0.0681395840655208, 0.455283663221462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8179547627767, -98.9938990275065, -94.7901491800944, -94.9638788859049, -0.802228454748789, -0.885908208290736, -0.971629259983699, -0.994314058621724, -0.989289530118306, -0.976332326730092, -0.986097065607707, -0.828424334526062, -0.910278590520223, -0.987974220514298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.947052149795107, 1.25252345518265, 1.11779032882341, 0.825619039974551, 1.01679644174297, 1.02509985385494, 1.07340811017163, 1.02063270768438, 0.166249857862451, 0.388838898461616, 0.397692709939391, 0.361799934990615, -0.020589972382128, 0.380682539144796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.5630086263021, -99.0404469807943, -94.9111633300781, -94.99296875, -0.802335355679194, -0.885915754238764, -0.971587053934733, -0.99389328956604, -0.987063735723495, -0.959600687026978, -0.98471012711525, -0.82105634411176, -0.904986105362574, -0.987269858519236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.995304670856865, 1.24896654377689, 1.10999488917564, 0.84210919781735, 1.01703386844793, 1.0258448320393, 1.09198132088668, 1.09565448482564, 0.271387989964843, 0.598058883448329, 0.502236314349719, 0.458707485466492, 0.0237938421945349, 0.389634244756152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8883895874023, -99.0003420511882, -94.872067006429, -95.0089561462402, -0.802343308925629, -0.885927748680115, -0.971748385826747, -0.994246639808019, -0.988695033391317, -0.9732335348924, -0.987362694740295, -0.824604455629985, -0.907633483409882, -0.987354377905528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99826521730719, 1.23279347857247, 1.09687935467818, 0.811795532010541, 1.01563665113873, 1.02570489411301, 1.10346020143908, 1.04966622444485, 0.373261824052658, 0.612699751700488, 0.536241698292768, 0.589670671598983, 0.102613303189614, 0.515854556458163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9083534240723, -98.81798731486, -94.8062889099121, -94.9795667012533, -0.80229650537173, -0.885925495624542, -0.971848094463348, -0.994030036528905, -0.990275683005651, -0.974187539021174, -0.988225507736206, -0.829399458567301, -0.912334857384364, -0.988546113173167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.983164699361473, 1.20295894502016, 1.05190780192516, 0.741983918259792, 1.00174217701842, 1.01963548761641, 1.0824711306783, 0.948496691772815, 0.546609340410002, 0.685743525965245, 0.632426941765923, 0.475066243906725, 0.0475503444913715, 0.294432624106034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.806526184082, -98.4815966288249, -94.5807439168294, -94.9118835449219, -0.801831072568893, -0.885827775796254, -0.971665777762731, -0.993553531169891, -0.992965300877889, -0.978947097063065, -0.99066600004832, -0.825203404823939, -0.909050496419271, -0.986455512046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996007461688852, 1.25387276691592, 1.1095610852026, 0.895998031621009, 1.0168374857799, 1.0258448320393, 1.06230434895978, 1.11169469397056, 0.264862083024744, 0.676649933365913, 0.520363545358901, 0.702774022946463, 0.120629220911534, 0.47358415644908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.893128712972, -99.055660756429, -94.8698913574219, -95.0612019856771, -0.802336730559667, -0.885927748680115, -0.971490603685379, -0.994322188695272, -0.988593779007594, -0.978354555368423, -0.987822633981705, -0.833540552854538, -0.913409459590912, -0.988147008419037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0029787620646, 1.22567909188431, 1.04724437118428, 0.748918362111409, 1.00290594153953, 1.01853819657526, 1.09596765007403, 0.939577027805194, 0.519919235130882, 0.595469321382463, 0.636039154411782, 0.440391553990068, 0.101244584424098, 0.216849071171134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9401382446289, -98.737771097819, -94.5573554992676, -94.9186065673828, -0.801870055993398, -0.885810108979543, -0.971783012151718, -0.993511519829432, -0.992551183700562, -0.973064798116684, -0.990757652123769, -0.82393384774526, -0.912253216902415, -0.985722990830739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.993766111437399, 1.25219665482654, 1.08570541622135, 0.801251956181516, 1.01573997297736, 1.01634176346219, 1.12489529824502, 1.11148335551478, 0.326538517487288, 0.796804082560707, 0.478340662426383, 0.407004353674899, -0.00986183005403093, 0.369031643879543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8780146280924, -99.0367622375488, -94.7502484639486, -94.9693445841471, -0.80229996641477, -0.885774745543798, -0.972034285465876, -0.994321193297704, -0.989550735553106, -0.986183842023214, -0.986756394306819, -0.822711429993312, -0.905626010894775, -0.98715985417366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.958732507023292, 1.25652366386212, 1.09697154119168, 0.824741610912526, 1.01638997529054, 1.02505419509591, 1.09037882936232, 1.07411863216357, 0.374230024165958, 0.701969665522114, 0.527234344977338, 0.797669918401829, 0.0407387943583283, 0.397944979627213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.6417727152507, -99.085550181071, -94.8067512512207, -94.9921180725098, -0.802321739991506, -0.885915019114812, -0.97173446615537, -0.994145206610362, -0.990290705362956, -0.980004398028056, -0.987996965646744, -0.837015010913213, -0.908644205331802, -0.987432845433553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894393109474373, 0.911240355650994, 0.888671043176603, 0.136839849391686, 0.927531533326925, 0.931464845285284, 0.815579209422244, 0.754083873104172, 0.182257748930269, 0.266359668424574, 0.251960876283779, 0.350683114003548, -0.0625752731200295, 0.295755809928427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.2079132080078, -95.1924077351888, -93.762065633138, -94.3251894632975, -0.799345187346141, -0.884408193826675, -0.969347482919693, -0.992637852827708, -0.987312110265096, -0.951619897286097, -0.981012497345606, -0.820649319887161, -0.902481792370478, -0.986468005180359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94812804015491, 1.01391620526707, 0.946788200065422, 0.045336195666911, 0.944137998118613, 0.963858870997085, 0.882012844635157, 0.875577331525122, 0.15207259618489, 0.264249764432112, 0.276484299912773, 0.514906194938057, -0.0159226184081927, 0.440145306341327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.570263671875, -96.3500996907552, -94.0535395304362, -94.2364756266276, -0.7999014655749, -0.884929750363032, -0.969924543301264, -0.993210083246231, -0.986843764781952, -0.95148241519928, -0.981634726126989, -0.826662079493205, -0.905264500776927, -0.987831288576126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0045815098391, 1.25952481843341, 1.10666892349528, 0.790142838631195, 1.01703386844793, 1.02579917328028, 0.990063683369987, 1.09897431246458, 0.217761279576153, 0.653154097146202, 0.534492911277376, 0.314715942112346, -0.0614670342831184, 0.206057994174047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9509460449219, -99.1193888346354, -94.8553863525391, -94.9585741678874, -0.802343308925629, -0.885927013556163, -0.970863101879756, -0.994262276093165, -0.987862974405289, -0.976823558410009, -0.988181136051814, -0.819332440694173, -0.902547895908356, -0.985621104637782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884945654676534, 0.889561982190656, 0.905876555565013, 0.598386160071363, 0.993476726488941, 1.02290379094803, 0.611401981087552, 0.811567511247182, 0.349099334437668, 0.5124353893928, 0.569015186954115, 0.712496018311154, -0.341946292036569, -0.261954388387424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.144206237793, -94.947979482015, -93.8483561197917, -94.7726638793945, -0.801554199059804, -0.885880396763484, -0.96757394472758, -0.992908598979314, -0.989900783697764, -0.967654277880987, -0.989057064056396, -0.833896507819494, -0.885818044344584, -0.981202268600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903077394147391, 1.03625794578335, 0.967380882271585, 0.840229742143383, 1.010916349643, 1.01538897622325, 1.11628264967833, 0.846497834940912, 0.607956937696122, 0.673143681940256, 0.646375892814765, 0.135006574195611, -0.203580353244754, 0.0240925876553001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.2664738972982, -96.6020075480143, -94.1568176269531, -95.007133992513, -0.802138386170069, -0.885759405295054, -0.971959473689397, -0.993073119719823, -0.993917155265808, -0.978126086791356, -0.99101992448171, -0.812752676010132, -0.894071209430695, -0.983903040488561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96125874495625, 1.25783490264343, 1.10851894151425, 0.799209343294826, 1.01703386844793, 1.02562789123292, 1.11742310396614, 1.11352882492026, 0.200907862076895, 0.666978439840687, 0.514712973567489, 0.558547620998569, -0.0761505743199325, 0.471094344958867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.6588078816732, -99.1003346761068, -94.8646647135417, -94.96736424764, -0.802343308925629, -0.885924255847931, -0.971969379981359, -0.994330827395121, -0.987601480881373, -0.977724357446035, -0.987679262955984, -0.828259938955307, -0.901672061284383, -0.988123500347137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966195100995403, 1.25879714688335, 1.11683768414294, 0.905530924587257, 1.01696079582727, 1.02589369925167, 1.13465892273959, 1.09651207181294, 0.250183882470944, 0.42130215443038, 0.468774915692839, 0.420078022108611, -0.0354270023819891, 0.505464559641981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.6920951843262, -99.1111841837565, -94.9063855489095, -95.0704442342122, -0.80234086116155, -0.885928535461426, -0.972119094928106, -0.994250679016113, -0.988366035620372, -0.961716004212697, -0.986513684193293, -0.823190100987752, -0.904101115465164, -0.988448013861974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996807440177079, 1.25923577525834, 1.11413714665703, 0.840361684390982, 1.01638534893955, 1.02589369925167, 1.11754181551355, 1.13018322327005, 0.314636097102249, 0.69181095209002, 0.565215433677713, 0.735260208453277, 0.191098734650467, 0.426251223915349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8985232035319, -99.1161298116048, -94.8928415934245, -95.007261912028, -0.80232158501943, -0.885928535461426, -0.971970411141713, -0.994409269094467, -0.989366060495377, -0.979342452685038, -0.988960653543472, -0.834729981422424, -0.917612781127294, -0.98770010471344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.961922012053762, 1.24388310548168, 1.10742015737729, 0.859715749707381, 1.0169973321376, 1.02524657889406, 1.08900301056143, 1.09749789610674, 0.134961538343356, 0.588484443616299, 0.397418563907025, 0.481484916250224, 0.142322469021962, 0.499315364969321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.6632804870605, -98.9430252075195, -94.8591540018717, -95.0260258992513, -0.802342085043589, -0.885918116569519, -0.971722515424093, -0.994255322217941, -0.986578273773193, -0.972609661022822, -0.984703171253204, -0.825438414017359, -0.914703404903412, -0.98838995496432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875272974933771, 1.23092880612854, 1.0888374758359, 0.717191366622634, 1.00182592583366, 1.02307174113999, 0.984800804768211, 1.06311173729917, 0.187687019741517, 0.466793168822594, 0.441339718223912, 0.50711885266584, 0.363162115745893, 0.473648548125547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.0789805094401, -98.7969627380371, -94.765956624349, -94.887846883138, -0.801833877960841, -0.885883100827535, -0.970817387104034, -0.994093364477158, -0.987396349509557, -0.964680214722951, -0.985817575454712, -0.8263769586881, -0.927875910202662, -0.988147616386414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969068114442183, 1.24391946424861, 1.10335020900934, 0.756680133694464, 1.01660456680154, 1.02567700524939, 1.0401487485424, 1.08784972612481, 0.163881410660282, 0.552853358760604, 0.423545518655934, 0.363204799624048, 0.462055385827238, 0.455520397326134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.7114687601725, -98.943435160319, -94.8387420654297, -94.9261316935221, -0.802328928311666, -0.885925046602885, -0.97129815419515, -0.994209879636765, -0.98702698747317, -0.970287926991781, -0.98536608616511, -0.82110778093338, -0.933774634202321, -0.987976455688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90491977341888, 1.20841488023587, 1.09278060436322, 0.206715729247137, 1.01279429226913, 1.02508245416569, 1.06569391817182, 1.06559591327957, 0.195205072492736, 0.428756170783883, 0.359660566336674, 0.393301483440239, 0.0515527418393803, 0.445654582425264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.2788976033529, -98.5431134541829, -94.7857325236003, -94.3929349263509, -0.802201292912165, -0.885915474096934, -0.971520046393077, -0.994105064868927, -0.987512997786204, -0.962201710542043, -0.983745143810908, -0.822209721803665, -0.909289228916168, -0.987883305549622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969495709958849, 1.25467825344483, 1.11463332104349, 0.798334799649737, 1.0169973321376, 1.02591109894091, 1.09098450985854, 1.14204348678929, 0.16643438059268, 0.616478137657017, 0.37481729470721, 0.399823476200215, -0.0974001071964808, 0.440568060844694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.714352162679, -99.064742787679, -94.8953300476074, -94.9665163675944, -0.802342085043589, -0.885928815603256, -0.971739727258682, -0.994465130567551, -0.987066598733266, -0.974433739980062, -0.984129712978999, -0.822448513905207, -0.900404582420985, -0.987835280100505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.988176482374812, 1.2608301703424, 1.10986918490338, 0.836057166929751, 1.0169973321376, 1.02586223172856, 1.07957058899683, 1.11703889935274, 0.217049055130949, 0.539415279398004, 0.491037280571579, 0.548640365181232, -0.0779093467892824, 0.468170626158584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8403221130371, -99.1341069539388, -94.8714365641276, -95.0030886332194, -0.802342085043589, -0.885928028821945, -0.971640582879384, -0.99434735973676, -0.987851923704147, -0.969412297010422, -0.987078543504079, -0.827897200981776, -0.901567155122757, -0.988095895449321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9774590258991, 1.24708481970281, 1.0998384504877, 0.815437190506224, 1.0168877232066, 1.02505802055951, 1.04265907461718, 1.12378570027486, 0.242233526640437, 0.519275464146401, 0.509752974143814, 0.48846767248513, -0.0832150764450254, 0.396768884595206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.7680511474609, -98.979125213623, -94.8211296081543, -94.9830973307292, -0.802338413397471, -0.885915080706278, -0.97131995956103, -0.994379136959712, -0.988242679834366, -0.96809997955958, -0.987553413709005, -0.825694076220195, -0.901250682274501, -0.987421741088231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.951406134166564, 1.25738628237405, 1.11154710114742, 0.819351389747939, 1.01666091338403, 1.02451208988406, 0.975941355123181, 1.08482096342499, 0.068293898482552, 0.5949410602343, 0.25861383121154, 0.684283521207541, -0.183826214986473, 0.299093024298206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.5923688252767, -99.0952763875326, -94.8798517862956, -94.986892191569, -0.802330815792084, -0.885906291007996, -0.970740431547165, -0.994195614258448, -0.985543874899546, -0.973030376434326, -0.981181301673253, -0.832863553365072, -0.895249491930008, -0.986499514182409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969610547527049, 1.24991807436031, 1.10719496468947, 0.924461358233944, 1.01625764978997, 1.02580990925876, 1.10114109473547, 1.10990105901241, 0.299973774979092, 0.626357490128679, 0.419311720404551, 0.55446391409645, -0.0664774756310493, 0.23170966003512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.715126546224, -99.0110707600911, -94.858024597168, -95.0887975056966, -0.802317307392756, -0.885927186409632, -0.971827950080236, -0.994313740730286, -0.989138563474019, -0.975077482064565, -0.985258662700653, -0.828110420703888, -0.90224903623263, -0.985863300164541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.996934760909508, 1.23908997344525, 1.08742161674354, 0.878649331081648, 1.0154568165723, 1.0252713827064, 1.12153569283398, 1.04525722336707, 0.394138630992454, 0.678516486580685, 0.623190389525402, 0.633266298063119, -0.00768432444113653, 0.478160805375771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8993817647298, -98.888981628418, -94.7588556925456, -95.0443822224935, -0.802290481328964, -0.885918515920639, -0.972005103031794, -0.994009270270665, -0.990599602460861, -0.978476180632909, -0.990431642532349, -0.830995641152064, -0.905755893389384, -0.988190219799678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998226711836868, 1.20292933021806, 1.03498904131553, 0.728167230372189, 1.00638525404005, 1.01354152411158, 1.06122267861741, 0.974526755828197, 0.640386967598786, 0.698947157999232, 0.571764634394425, 0.317710714772157, 0.143833818868591, 0.335261576455562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.908093770345, -98.4812627156576, -94.4958915710449, -94.8984881083171, -0.80198660492897, -0.88572966059049, -0.971481208006541, -0.99367613196373, -0.994420331716537, -0.979807450373967, -0.989126825332642, -0.819442089398702, -0.914793552954992, -0.98684100707372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00351704666588, 1.24958392105258, 1.09577458703814, 0.794082744314794, 1.01477674297773, 1.02551979103589, 1.09559664789697, 1.03253431086163, 0.349671214044328, 0.654138599077045, 0.48350535128982, 0.467092176028899, 0.11461056901641, 0.507620418221867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9437680562337, -99.0073031107585, -94.8007481892904, -94.962393951416, -0.802267700433731, -0.885922515392303, -0.971779789527257, -0.99394934574763, -0.98990965684255, -0.976887708902359, -0.986887437105179, -0.824911447366079, -0.913050462802251, -0.988468368848165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00007904746895, 1.21420666038929, 1.03349179643981, 0.736149867506878, 1.00701016729596, 1.01585173391604, 1.05577109668883, 0.961309876592723, 0.533230097923826, 0.660129187216632, 0.655467893905395, 0.427511991191713, 0.112346125729137, 0.363873575991779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9205846150716, -98.60841700236, -94.4883824666341, -94.9062273661296, -0.802007538080215, -0.885766855875651, -0.971433854103088, -0.993613880872726, -0.992757711807887, -0.977278057734172, -0.991250614325205, -0.823462283611298, -0.912915394703547, -0.987111153205236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.963676481186837, 1.2385469376682, 1.08838308455567, 0.782056326486478, 1.0168374857799, 1.02261786839491, 1.08720678362155, 1.09674492376424, 0.280597735838245, 0.692197886229713, 0.52073157916414, 0.570057862689117, 0.34154564592644, 0.443980188406709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.6751113891602, -98.8828587849935, -94.7636777242025, -94.9507342020671, -0.802336730559667, -0.885875793298086, -0.971706912914912, -0.994251775741577, -0.988837929566701, -0.979367665449778, -0.98783197204272, -0.828681367635727, -0.926586544513702, -0.987867496411006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0065968431624, 1.24917608034313, 1.08541349226194, 0.756425167760743, 1.01502579487234, 1.02100586739732, 1.14427798904926, 1.10077764958739, 0.302714853093799, 0.643784650081794, 0.498110968613282, 0.503152140941199, -0.108114526029619, 0.323355008357262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9645360310872, -99.0027046203613, -94.748784383138, -94.9258845011393, -0.802276043097178, -0.885849839448929, -0.972202648719152, -0.994270769755046, -0.989181093374888, -0.976213041941325, -0.987258023023605, -0.826231724023819, -0.899765495459239, -0.986728588740031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.888585986731719, 0.954723230502607, 0.847815481340622, 0.192078271393884, 0.920192657862362, 0.938839968887861, 0.814506459600777, 0.797568975008551, 0.117986599628973, 0.262857990688511, 0.257678163990528, 0.374789764115796, 0.111233156949787, 0.344065559985612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.1687540690104, -95.6826863606771, -93.5571634928385, -94.3787437438965, -0.799099351962407, -0.884526936213175, -0.969338164726893, -0.992842666308085, -0.986314894755681, -0.951391726732254, -0.981157561143239, -0.821531945466995, -0.912849009037018, -0.986924131711324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941481566043504, 0.995082544437936, 0.985709822716409, 0.183118002535983, 0.957894274831341, 0.965631171259454, 0.914260756432706, 0.934295253743292, 0.143796732526312, 0.239580715848886, 0.239080945981554, 0.378926433584341, 0.0409431478573049, 0.489606741513956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.525444539388, -96.1377461751302, -94.2487424214681, -94.3700566609701, -0.800362269083659, -0.884958285093308, -0.970204657316208, -0.993486642837524, -0.986715358495712, -0.949874971310298, -0.980685696999232, -0.821683402856191, -0.908656394481659, -0.98829828898112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00124601590009, 1.25590152746744, 1.10821870149972, 0.861683866374753, 1.01691055840056, 1.02586926564549, 1.16248339982552, 1.12538191727432, 0.364633305571703, 0.61433173562159, 0.476668770984768, 0.713330504321927, -0.0678237105152601, 0.485231263968661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9284538269043, -99.0785354614258, -94.8631589253743, -95.0279340108236, -0.802339178323746, -0.88592814207077, -0.972360785802205, -0.994386655092239, -0.990141805013021, -0.974293879667918, -0.986713973681132, -0.833927061160405, -0.902168736855189, -0.988256977001826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937762073378909, 1.02292167638185, 0.934025793664778, 0.635995733779872, 0.963714639553873, 1.02242832284394, 0.827073643703392, 0.823081871505434, 0.472283431011302, 0.713085774151388, 0.494395080061438, 0.383901116283759, -0.563855423770833, -0.271046850111044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.5003629048665, -96.451638285319, -93.9895324707031, -94.8091267903646, -0.800557237863541, -0.885872741540273, -0.969447326660156, -0.992962831258774, -0.991812078158061, -0.980728727579117, -0.9871637403965, -0.821865542729696, -0.872581747071496, -0.981116420236127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.881863029668487, 1.0476650352512, 0.937923488134839, 0.965250923726866, 0.991258747065526, 1.01468385690149, 1.12943126875881, 0.864326195211822, 0.523812267777961, 0.715106399722966, 0.515314356466258, 0.789941670632525, -0.488397734330922, 0.473253149563168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.1234191894531, -96.7306248982747, -94.0090805053711, -95.1283434549967, -0.801479901870092, -0.885748052597046, -0.972073686122894, -0.993157090743383, -0.992611587047577, -0.980860392252604, -0.987694521745046, -0.836732053756714, -0.877082600196203, -0.988143883148829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00122391579665, 1.24134545752355, 1.11287295415536, 0.848133948399284, 1.01680094946957, 1.02567700524939, 1.12506135717262, 1.13129728487035, 0.365633902805578, 0.478249712414016, 0.514941467746993, 0.554616507064475, -0.0657093263172931, 0.479004210079349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9283047993978, -98.914412689209, -94.8865013122559, -95.0147972106934, -0.802335506677628, -0.885925046602885, -0.97203572789828, -0.994414516290029, -0.990157330036163, -0.965426727135976, -0.987685060501099, -0.828116007645925, -0.902294854323069, -0.98819818298022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.989442637277004, 1.24840126870444, 1.11110700942539, 0.84222461449516, 1.0153179667306, 1.02591813285784, 1.06358021218029, 1.11612900504306, 0.378089507225719, 0.528705680299886, 0.633708560763858, 0.408957076987273, -0.0843143550388679, 0.300444828643462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.848860168457, -98.9939684549967, -94.8776446024577, -95.0090680440267, -0.80228583017985, -0.885928928852081, -0.971501686175664, -0.994343074162801, -0.99035058816274, -0.968714455763499, -0.990698518355687, -0.82278292576472, -0.901185113191605, -0.986512277523677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00053805832037, 1.25636625205418, 1.11181291066544, 0.84655719919395, 1.0164052185239, 1.02571883854481, 1.08497185003826, 1.11939441619337, 0.194770592531829, 0.574218892332264, 0.477942559476208, 0.476826218206856, 0.162978793836036, 0.507915862384491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9236798604329, -99.0837753295898, -94.8811848958333, -95.0132685343424, -0.802322250604629, -0.885925720135371, -0.971687499682109, -0.994358454147975, -0.98750625650088, -0.971680112679799, -0.986746293306351, -0.825267843405406, -0.91593550046285, -0.98847115834554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.957338616540317, 1.2553710097522, 1.1030609218479, 0.816920032505515, 1.01696079582727, 1.02389730086393, 1.07228458200039, 1.09063593470869, 0.236336098229105, 0.562784790311118, 0.347245533205017, 0.323096345745706, 0.406524162827673, 0.465515416440566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.6323733011882, -99.0725537618001, -94.837291208903, -94.984534962972, -0.80234086116155, -0.88589639266332, -0.971577294667562, -0.994223002592723, -0.988151176770528, -0.970935062567393, -0.983430139223735, -0.819639275471369, -0.930462342500687, -0.988070825735728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895658623247282, 1.22806683887159, 1.09280829074186, 0.701241306369877, 0.987083702551725, 1.02275644889864, 0.993419629080152, 1.04404529645391, 0.203407306331821, 0.451233842717335, 0.389855390904356, 0.622164888314641, 0.193506708374104, 0.489810227628811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.2164469401042, -98.7646934509277, -94.7858713785807, -94.8723831176758, -0.801340047518412, -0.885878024498622, -0.970892252524694, -0.994003562132518, -0.987640261650085, -0.96366636355718, -0.984511272112529, -0.830589181184769, -0.917756410439809, -0.988300210237503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.952495940803103, 1.2554008275499, 1.10591170611021, 0.726215639274592, 1.0137902032866, 1.02582039843312, 1.07313569118711, 1.09499389396382, 0.281653011216329, 0.52927272633581, 0.487036283278273, 0.694883414522702, 0.284462735331713, 0.53373944981313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.5997177124023, -99.0728899637858, -94.8515886942546, -94.8965960184733, -0.802234653631846, -0.885927355289459, -0.971584687630335, -0.994243528445562, -0.988854302962621, -0.968751404682795, -0.986977026859919, -0.833251651128133, -0.92318169871966, -0.988714977105459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.907784527611988, 1.22508447267056, 1.09735686864827, 0.258559064747156, 1.0142501693363, 1.02529236105514, 1.06052436194258, 1.07014285382849, 0.254897855592345, 0.456674398946291, 0.431199368923811, 0.270172578739757, -0.101983188252337, 0.336715860364359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.2982154846191, -98.7310666402181, -94.8086837768555, -94.4431976318359, -0.802250061432521, -0.885918853680293, -0.971475142240524, -0.994126480817795, -0.988439176479975, -0.964020872116089, -0.985560286045075, -0.817701558272044, -0.900131213665009, -0.986854737997055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9575233372001, 1.25012928000146, 1.11391717685749, 0.879247923942495, 1.01703386844793, 1.02576079524229, 1.11623072767204, 1.12887174371104, 0.185990076493073, 0.444770365564943, 0.443400237702843, 0.386800002821772, -0.137306764780325, 0.517891311479618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.6336189270019, -99.0134521484375, -94.8917383829753, -95.0449625651042, -0.802343308925629, -0.885926395654678, -0.971959022680918, -0.994403092066447, -0.987370020151138, -0.96324520111084, -0.985869856675466, -0.821971680720647, -0.898024255037308, -0.988565343618393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998043273435646, 1.25072619983198, 1.11681030201022, 0.789989911533103, 1.01703386844793, 1.02591813285784, 1.11136629900396, 1.13652759527636, 0.264682298213331, 0.560828989166724, 0.560111979375061, 0.609147438342833, -0.136971571746877, 0.439321261226751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9068567911784, -99.0201825459798, -94.9062482198079, -94.9584259033203, -0.802343308925629, -0.885928928852081, -0.971916768948237, -0.994439150889715, -0.988590989510218, -0.970807621876399, -0.988831164439519, -0.830112568537394, -0.898044248421987, -0.987823508183161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.992633122858136, 1.24810960914168, 1.097680180645, 0.802565870134187, 1.01652846925908, 1.02572574905969, 1.14866482675204, 1.12152003391543, 0.416031785544902, 0.590548488747761, 0.422931841861971, 0.598078696078974, -0.120665561525605, 0.0878984261285654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.8703745524088, -98.9906799316406, -94.8103052775065, -94.9706184387207, -0.802326379219691, -0.885925831397374, -0.972240753968557, -0.994368465741475, -0.990939291318258, -0.972744154930115, -0.985350515445073, -0.829707304636637, -0.899016859134038, -0.984505476554235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.941768980528643, 1.23972038754927, 1.10738466202005, 0.827006400904003, 1.01681465058594, 1.02555446701234, 1.08858466100418, 1.06267978005619, 0.305751090745753, 0.469870743568192, 0.404333370971958, 0.339871587482379, -0.336718206717601, 0.189509754181647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.5273826599121, -98.8960896809896, -94.858975982666, -94.9943138122559, -0.802335965633392, -0.885923073689143, -0.971718881527583, -0.994091329971949, -0.989228202899297, -0.964880750576655, -0.984878619511922, -0.820253473520279, -0.886129885911942, -0.985464860995611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.972211382737478, 1.26003679588412, 1.11406884344818, 0.821156086891959, 1.01703386844793, 1.02589369925167, 1.1377232360356, 1.12415860086353, 0.329245533807239, 0.581055003221551, 0.438129367171344, 0.195929588004409, -0.055503243058381, 0.333013970258222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.7326647440592, -99.1251614888509, -94.89249903361, -94.9886418660482, -0.802343308925629, -0.885928535461426, -0.972145712375641, -0.994380893309911, -0.989592736959457, -0.972125556071599, -0.985736119747162, -0.81498327255249, -0.902903620402018, -0.986819785833359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00671865772571, 1.2552447239358, 1.09784761731583, 0.779933971167847, 1.01685581324726, 1.02516994622014, 1.10793624435089, 1.06870102779676, 0.442285746188928, 0.630409962056972, 0.636194589965698, 0.396592813913089, 0.0726772310264149, 0.295930467090093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9653574625651, -99.0711298624674, -94.8111450195313, -94.948676554362, -0.802337344487508, -0.885916882753372, -0.971886974573135, -0.994119689861933, -0.991346641381582, -0.975341542561849, -0.990761595964432, -0.822330228487651, -0.910549249251684, -0.986469654242198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.997136603492431, 1.22907168963182, 1.03932530627803, 0.852051033057948, 0.998762332487539, 1.01073462105018, 1.10300616979821, 0.960405887948495, 0.639675511464746, 0.73574261275189, 0.635421875584832, 0.496120926128611, 0.0422255618280632, 0.468538668779975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9007428487142, -98.7760233561198, -94.5176391601562, -95.0185948689779, -0.80173125465711, -0.885684468348821, -0.971844150622686, -0.993609623114268, -0.994409292936325, -0.982205055157344, -0.990741990009944, -0.825974287589391, -0.908732887109121, -0.988099370400111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00841912114527, 1.24704210040717, 1.09865863552094, 0.848674570610588, 1.01696079582727, 1.02539367413935, 1.13647550676564, 1.05590598180637, 0.430399844493829, 0.49785943704162, 0.657092254172591, 0.499561159554613, -0.101129500261259, 0.311206655826731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9768241882324, -98.978643544515, -94.815212504069, -95.0153213500977, -0.80234086116155, -0.885920484860738, -0.972134874264399, -0.994059425592422, -0.991162222623825, -0.96670450369517, -0.991291828950246, -0.826100246111552, -0.90018213391304, -0.986613887548447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.976165679572717, 1.24217760414086, 1.04587556879409, 0.820968797101135, 0.999391812782247, 1.00387753925942, 1.06704343287262, 0.965755155329597, 0.681343202546291, 0.724800151870886, 0.616119285550841, 0.753301450881287, -0.000199223843090327, 0.30625018018098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.7593297322591, -98.9237953186035, -94.5504905700684, -94.9884602864583, -0.80175234079361, -0.885574066638947, -0.971531768639882, -0.993634817997615, -0.995055798689524, -0.981492040554682, -0.990252228577932, -0.835390532016754, -0.906202359994252, -0.986567089955012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00387649391137, 1.25487301644262, 1.10070154545264, 0.798314339420491, 1.01380781900766, 1.02559987896725, 1.16610581750627, 1.1055591294206, 0.290716393813776, 0.675313592740199, 0.514744843728921, 0.700564735070496, 0.045270514533652, 0.218196877340404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9461919148763, -99.0669387817383, -94.8254582722982, -94.9664965311686, -0.802235243717829, -0.885923804839452, -0.972392251094182, -0.994293290376663, -0.98899492820104, -0.978267478942871, -0.987680071592331, -0.833459663391113, -0.908914510546059, -0.985735716422399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00745580554444, 1.23074980912211, 1.09680547362748, 0.701439613207208, 1.0154995806628, 1.02402625600766, 1.10090024067107, 1.10959480807645, 0.384910957858657, 0.700826090667174, 0.525465355255191, 0.56808538694418, -0.0825766341443104, 0.476986393786268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.9703282674154, -98.7949445088704, -94.805918375651, -94.872575378418, -0.80229191382726, -0.88589846889178, -0.971825857957204, -0.994312298297882, -0.990456428130468, -0.979929882287979, -0.987952081362406, -0.828609148661296, -0.901288763682048, -0.988179131348928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901259151507638, 0.903276906045767, 0.911956960966618, 0.156246901455635, 0.923274282114881, 0.951001981466723, 0.871039460267299, 0.852263873568199, 0.110554341623942, 0.206041484157388, 0.26855520734162, 0.469188592861663, -0.0430349815550516, 0.180646218872388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.2542129516602, -95.10261815389, -93.8788510640462, -94.3440048217773, -0.799202579259872, -0.884722749392192, -0.969829225540161, -0.993100277582804, -0.986199577649434, -0.94768954316775, -0.981433542569478, -0.824988204240799, -0.90364731947581, -0.985381174087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.942649100176944, 1.00996803112563, 0.989265798311626, 0.147115868376686, 0.950770880560664, 0.981668872066983, 0.977077006053592, 0.934243790087393, 0.158165175630825, 0.258976818681162, 0.274075636115098, 0.5318343552323, 0.0664226482701265, 0.188326925379542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-88.533317565918, -96.305583190918, -94.2665766398112, -94.3351521809896, -0.800123651822408, -0.885216498374939, -0.970750296115875, -0.993486400445302, -0.986938295761744, -0.951138828198115, -0.981573611497879, -0.82728187640508, -0.910176179806391, -0.985453693072001</t>
   </si>
 </sst>
 </file>
@@ -1698,7 +1698,7 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.371492748957058</v>
+        <v>0.337422783036357</v>
       </c>
       <c r="P2" t="s">
         <v>27</v>
@@ -1710,7 +1710,7 @@
         <v>29</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="3">
@@ -1753,7 +1753,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.370904192846159</v>
+        <v>0.324727862841079</v>
       </c>
       <c r="P3" t="s">
         <v>31</v>
@@ -1765,7 +1765,7 @@
         <v>29</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="4">
@@ -1808,7 +1808,7 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.361021303639726</v>
+        <v>0.353789846310612</v>
       </c>
       <c r="P4" t="s">
         <v>34</v>
@@ -1820,7 +1820,7 @@
         <v>29</v>
       </c>
       <c r="S4" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="5">
@@ -1863,7 +1863,7 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.505114885018147</v>
+        <v>0.498157567244936</v>
       </c>
       <c r="P5" t="s">
         <v>37</v>
@@ -1875,7 +1875,7 @@
         <v>29</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="6">
@@ -1918,7 +1918,7 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.368715067775915</v>
+        <v>0.325144658857461</v>
       </c>
       <c r="P6" t="s">
         <v>40</v>
@@ -1930,7 +1930,7 @@
         <v>29</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="7">
@@ -1973,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.369627021773555</v>
+        <v>0.341265125755625</v>
       </c>
       <c r="P7" t="s">
         <v>43</v>
@@ -1985,7 +1985,7 @@
         <v>29</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="8">
@@ -2028,7 +2028,7 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.352050252698033</v>
+        <v>0.375157559757409</v>
       </c>
       <c r="P8" t="s">
         <v>46</v>
@@ -2040,7 +2040,7 @@
         <v>29</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="9">
@@ -2083,7 +2083,7 @@
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.40689344370944</v>
+        <v>0.37373162810647</v>
       </c>
       <c r="P9" t="s">
         <v>49</v>
@@ -2095,7 +2095,7 @@
         <v>29</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="10">
@@ -2138,7 +2138,7 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.311562229024629</v>
+        <v>0.267019905380408</v>
       </c>
       <c r="P10" t="s">
         <v>52</v>
@@ -2150,7 +2150,7 @@
         <v>29</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="11">
@@ -2193,7 +2193,7 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.343699251864271</v>
+        <v>0.322547527200165</v>
       </c>
       <c r="P11" t="s">
         <v>55</v>
@@ -2205,7 +2205,7 @@
         <v>29</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="12">
@@ -2248,7 +2248,7 @@
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0.311148318485908</v>
+        <v>0.263257944209897</v>
       </c>
       <c r="P12" t="s">
         <v>58</v>
@@ -2260,7 +2260,7 @@
         <v>29</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="13">
@@ -2303,7 +2303,7 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.376323118256591</v>
+        <v>0.352385460841415</v>
       </c>
       <c r="P13" t="s">
         <v>61</v>
@@ -2315,7 +2315,7 @@
         <v>29</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="14">
@@ -2358,7 +2358,7 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.378607627133661</v>
+        <v>0.342977254109414</v>
       </c>
       <c r="P14" t="s">
         <v>64</v>
@@ -2370,7 +2370,7 @@
         <v>29</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="15">
@@ -2411,7 +2411,7 @@
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0.472877633813054</v>
+        <v>0.427434471139488</v>
       </c>
       <c r="P15" t="s">
         <v>67</v>
@@ -2423,7 +2423,7 @@
         <v>29</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="16">
@@ -2464,7 +2464,7 @@
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0.40061591718081</v>
+        <v>0.372908107764386</v>
       </c>
       <c r="P16" t="s">
         <v>70</v>
@@ -2476,7 +2476,7 @@
         <v>29</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="17">
@@ -2521,7 +2521,7 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.456301659806277</v>
+        <v>0.460391517384964</v>
       </c>
       <c r="P17" t="s">
         <v>74</v>
@@ -2533,7 +2533,7 @@
         <v>29</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="18">
@@ -2578,7 +2578,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0.24437849171693</v>
+        <v>0.201942175606432</v>
       </c>
       <c r="P18" t="s">
         <v>77</v>
@@ -2590,7 +2590,7 @@
         <v>29</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="19">
@@ -2635,7 +2635,7 @@
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0.021554650655378</v>
+        <v>-0.0846816499410969</v>
       </c>
       <c r="P19" t="s">
         <v>79</v>
@@ -2647,7 +2647,7 @@
         <v>29</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="20">
@@ -2692,7 +2692,7 @@
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0.482071645274388</v>
+        <v>0.433831847449604</v>
       </c>
       <c r="P20" t="s">
         <v>81</v>
@@ -2704,7 +2704,7 @@
         <v>29</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="21">
@@ -2749,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0.250629312462163</v>
+        <v>0.213391979662332</v>
       </c>
       <c r="P21" t="s">
         <v>83</v>
@@ -2761,7 +2761,7 @@
         <v>29</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="22">
@@ -2806,7 +2806,7 @@
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0109676007244819</v>
+        <v>-0.0727415491702983</v>
       </c>
       <c r="P22" t="s">
         <v>85</v>
@@ -2818,7 +2818,7 @@
         <v>29</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="23">
@@ -2861,7 +2861,7 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.179606984844753</v>
+        <v>0.121518160789893</v>
       </c>
       <c r="P23" t="s">
         <v>87</v>
@@ -2873,7 +2873,7 @@
         <v>29</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="24">
@@ -2916,7 +2916,7 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0.442522404382321</v>
+        <v>0.378890062723472</v>
       </c>
       <c r="P24" t="s">
         <v>90</v>
@@ -2928,7 +2928,7 @@
         <v>29</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="25">
@@ -2971,7 +2971,7 @@
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0.50424073046997</v>
+        <v>0.439391275348143</v>
       </c>
       <c r="P25" t="s">
         <v>93</v>
@@ -2983,7 +2983,7 @@
         <v>29</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>45979.6170230213</v>
+        <v>45985.4279445581</v>
       </c>
     </row>
     <row r="26">
@@ -3026,7 +3026,7 @@
         <v>2</v>
       </c>
       <c r="O26" t="n">
-        <v>0.512888514104533</v>
+        <v>0.489712991211369</v>
       </c>
       <c r="P26" t="s">
         <v>95</v>
@@ -3038,7 +3038,7 @@
         <v>29</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="27">
@@ -3081,7 +3081,7 @@
         <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>0.363397887677481</v>
+        <v>0.338280409699414</v>
       </c>
       <c r="P27" t="s">
         <v>97</v>
@@ -3093,7 +3093,7 @@
         <v>29</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="28">
@@ -3136,7 +3136,7 @@
         <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>0.374524753586166</v>
+        <v>0.338524437367095</v>
       </c>
       <c r="P28" t="s">
         <v>99</v>
@@ -3148,7 +3148,7 @@
         <v>29</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="29">
@@ -3191,7 +3191,7 @@
         <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>0.500015249337224</v>
+        <v>0.489036094513592</v>
       </c>
       <c r="P29" t="s">
         <v>101</v>
@@ -3203,7 +3203,7 @@
         <v>29</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="30">
@@ -3246,7 +3246,7 @@
         <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>0.50371605392064</v>
+        <v>0.504748067138644</v>
       </c>
       <c r="P30" t="s">
         <v>103</v>
@@ -3258,7 +3258,7 @@
         <v>29</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="31">
@@ -3301,7 +3301,7 @@
         <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>0.526204541897271</v>
+        <v>0.505813572388054</v>
       </c>
       <c r="P31" t="s">
         <v>105</v>
@@ -3313,7 +3313,7 @@
         <v>29</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="32">
@@ -3356,7 +3356,7 @@
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>0.541737786027767</v>
+        <v>0.50697691118212</v>
       </c>
       <c r="P32" t="s">
         <v>107</v>
@@ -3368,7 +3368,7 @@
         <v>29</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="33">
@@ -3411,7 +3411,7 @@
         <v>2</v>
       </c>
       <c r="O33" t="n">
-        <v>0.484122135174963</v>
+        <v>0.441590834956726</v>
       </c>
       <c r="P33" t="s">
         <v>109</v>
@@ -3423,7 +3423,7 @@
         <v>29</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="34">
@@ -3466,7 +3466,7 @@
         <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>0.49006533257233</v>
+        <v>0.476458540158435</v>
       </c>
       <c r="P34" t="s">
         <v>111</v>
@@ -3478,7 +3478,7 @@
         <v>29</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="35">
@@ -3521,7 +3521,7 @@
         <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>0.485378455165533</v>
+        <v>0.425539448994189</v>
       </c>
       <c r="P35" t="s">
         <v>113</v>
@@ -3533,7 +3533,7 @@
         <v>29</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="36">
@@ -3576,7 +3576,7 @@
         <v>2</v>
       </c>
       <c r="O36" t="n">
-        <v>0.52076357886025</v>
+        <v>0.499290294761311</v>
       </c>
       <c r="P36" t="s">
         <v>115</v>
@@ -3588,7 +3588,7 @@
         <v>29</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="37">
@@ -3631,7 +3631,7 @@
         <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>0.528673659392835</v>
+        <v>0.522381266414557</v>
       </c>
       <c r="P37" t="s">
         <v>117</v>
@@ -3643,7 +3643,7 @@
         <v>29</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="38">
@@ -3684,7 +3684,7 @@
         <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>0.525642617160156</v>
+        <v>0.491414188946583</v>
       </c>
       <c r="P38" t="s">
         <v>119</v>
@@ -3696,7 +3696,7 @@
         <v>29</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="39">
@@ -3737,7 +3737,7 @@
         <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>0.521593023406273</v>
+        <v>0.504954415136695</v>
       </c>
       <c r="P39" t="s">
         <v>121</v>
@@ -3749,7 +3749,7 @@
         <v>29</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="40">
@@ -3794,7 +3794,7 @@
         <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>0.526949977155659</v>
+        <v>0.51109914355566</v>
       </c>
       <c r="P40" t="s">
         <v>123</v>
@@ -3806,7 +3806,7 @@
         <v>29</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="41">
@@ -3851,7 +3851,7 @@
         <v>2</v>
       </c>
       <c r="O41" t="n">
-        <v>0.522890907035417</v>
+        <v>0.490889336124938</v>
       </c>
       <c r="P41" t="s">
         <v>125</v>
@@ -3863,7 +3863,7 @@
         <v>29</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="42">
@@ -3908,7 +3908,7 @@
         <v>2</v>
       </c>
       <c r="O42" t="n">
-        <v>0.478687484645012</v>
+        <v>0.476672648320491</v>
       </c>
       <c r="P42" t="s">
         <v>127</v>
@@ -3920,7 +3920,7 @@
         <v>29</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="43">
@@ -3965,7 +3965,7 @@
         <v>2</v>
       </c>
       <c r="O43" t="n">
-        <v>0.543090398340129</v>
+        <v>0.502219825966808</v>
       </c>
       <c r="P43" t="s">
         <v>129</v>
@@ -3977,7 +3977,7 @@
         <v>29</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="44">
@@ -4022,7 +4022,7 @@
         <v>2</v>
       </c>
       <c r="O44" t="n">
-        <v>0.511293669773988</v>
+        <v>0.508946690754538</v>
       </c>
       <c r="P44" t="s">
         <v>131</v>
@@ -4034,7 +4034,7 @@
         <v>29</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="45">
@@ -4079,7 +4079,7 @@
         <v>2</v>
       </c>
       <c r="O45" t="n">
-        <v>0.483331617135691</v>
+        <v>0.455471139324621</v>
       </c>
       <c r="P45" t="s">
         <v>133</v>
@@ -4091,7 +4091,7 @@
         <v>29</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="46">
@@ -4134,7 +4134,7 @@
         <v>2</v>
       </c>
       <c r="O46" t="n">
-        <v>0.507444726611883</v>
+        <v>0.497145147373121</v>
       </c>
       <c r="P46" t="s">
         <v>135</v>
@@ -4146,7 +4146,7 @@
         <v>29</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="47">
@@ -4189,7 +4189,7 @@
         <v>2</v>
       </c>
       <c r="O47" t="n">
-        <v>0.563609276514055</v>
+        <v>0.540457393035064</v>
       </c>
       <c r="P47" t="s">
         <v>137</v>
@@ -4201,7 +4201,7 @@
         <v>29</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="48">
@@ -4244,7 +4244,7 @@
         <v>2</v>
       </c>
       <c r="O48" t="n">
-        <v>0.683507688899183</v>
+        <v>0.68638071487657</v>
       </c>
       <c r="P48" t="s">
         <v>139</v>
@@ -4256,7 +4256,7 @@
         <v>29</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>45979.7078950131</v>
+        <v>45985.5105363216</v>
       </c>
     </row>
     <row r="49">
@@ -4299,7 +4299,7 @@
         <v>3</v>
       </c>
       <c r="O49" t="n">
-        <v>0.701935107467709</v>
+        <v>0.665479832339414</v>
       </c>
       <c r="P49" t="s">
         <v>141</v>
@@ -4311,7 +4311,7 @@
         <v>29</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="50">
@@ -4354,7 +4354,7 @@
         <v>3</v>
       </c>
       <c r="O50" t="n">
-        <v>0.493718387940162</v>
+        <v>0.469062449443769</v>
       </c>
       <c r="P50" t="s">
         <v>143</v>
@@ -4366,7 +4366,7 @@
         <v>29</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="51">
@@ -4409,7 +4409,7 @@
         <v>3</v>
       </c>
       <c r="O51" t="n">
-        <v>0.510439744803086</v>
+        <v>0.482630849379092</v>
       </c>
       <c r="P51" t="s">
         <v>145</v>
@@ -4421,7 +4421,7 @@
         <v>29</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="52">
@@ -4464,7 +4464,7 @@
         <v>3</v>
       </c>
       <c r="O52" t="n">
-        <v>0.679165758173977</v>
+        <v>0.702196414026584</v>
       </c>
       <c r="P52" t="s">
         <v>147</v>
@@ -4476,7 +4476,7 @@
         <v>29</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="53">
@@ -4519,7 +4519,7 @@
         <v>3</v>
       </c>
       <c r="O53" t="n">
-        <v>0.680644655708431</v>
+        <v>0.672602661428471</v>
       </c>
       <c r="P53" t="s">
         <v>149</v>
@@ -4531,7 +4531,7 @@
         <v>29</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="54">
@@ -4574,7 +4574,7 @@
         <v>3</v>
       </c>
       <c r="O54" t="n">
-        <v>0.71776529265536</v>
+        <v>0.689575431439226</v>
       </c>
       <c r="P54" t="s">
         <v>151</v>
@@ -4586,7 +4586,7 @@
         <v>29</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="55">
@@ -4629,7 +4629,7 @@
         <v>3</v>
       </c>
       <c r="O55" t="n">
-        <v>0.710882042317514</v>
+        <v>0.702149570308339</v>
       </c>
       <c r="P55" t="s">
         <v>153</v>
@@ -4641,7 +4641,7 @@
         <v>29</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="56">
@@ -4684,7 +4684,7 @@
         <v>3</v>
       </c>
       <c r="O56" t="n">
-        <v>0.627741037951984</v>
+        <v>0.605269079373673</v>
       </c>
       <c r="P56" t="s">
         <v>155</v>
@@ -4696,7 +4696,7 @@
         <v>29</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="57">
@@ -4739,7 +4739,7 @@
         <v>3</v>
       </c>
       <c r="O57" t="n">
-        <v>0.660388650182158</v>
+        <v>0.672449041632309</v>
       </c>
       <c r="P57" t="s">
         <v>157</v>
@@ -4751,7 +4751,7 @@
         <v>29</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="58">
@@ -4794,7 +4794,7 @@
         <v>3</v>
       </c>
       <c r="O58" t="n">
-        <v>0.526315474513124</v>
+        <v>0.494591412805748</v>
       </c>
       <c r="P58" t="s">
         <v>159</v>
@@ -4806,7 +4806,7 @@
         <v>29</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="59">
@@ -4849,7 +4849,7 @@
         <v>3</v>
       </c>
       <c r="O59" t="n">
-        <v>0.669514415671754</v>
+        <v>0.668699468136241</v>
       </c>
       <c r="P59" t="s">
         <v>161</v>
@@ -4861,7 +4861,7 @@
         <v>29</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="60">
@@ -4904,7 +4904,7 @@
         <v>3</v>
       </c>
       <c r="O60" t="n">
-        <v>0.761972345417703</v>
+        <v>0.784719421320485</v>
       </c>
       <c r="P60" t="s">
         <v>163</v>
@@ -4916,7 +4916,7 @@
         <v>29</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="61">
@@ -4957,7 +4957,7 @@
         <v>3</v>
       </c>
       <c r="O61" t="n">
-        <v>0.691030925216845</v>
+        <v>0.68375642501649</v>
       </c>
       <c r="P61" t="s">
         <v>165</v>
@@ -4969,7 +4969,7 @@
         <v>29</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="62">
@@ -5010,7 +5010,7 @@
         <v>3</v>
       </c>
       <c r="O62" t="n">
-        <v>0.693755700315078</v>
+        <v>0.714325858287172</v>
       </c>
       <c r="P62" t="s">
         <v>167</v>
@@ -5022,7 +5022,7 @@
         <v>29</v>
       </c>
       <c r="S62" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="63">
@@ -5067,7 +5067,7 @@
         <v>3</v>
       </c>
       <c r="O63" t="n">
-        <v>0.74484897726222</v>
+        <v>0.742429185277302</v>
       </c>
       <c r="P63" t="s">
         <v>169</v>
@@ -5079,7 +5079,7 @@
         <v>29</v>
       </c>
       <c r="S63" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="64">
@@ -5124,7 +5124,7 @@
         <v>3</v>
       </c>
       <c r="O64" t="n">
-        <v>0.697778646772689</v>
+        <v>0.726388782264767</v>
       </c>
       <c r="P64" t="s">
         <v>171</v>
@@ -5136,7 +5136,7 @@
         <v>29</v>
       </c>
       <c r="S64" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="65">
@@ -5181,7 +5181,7 @@
         <v>3</v>
       </c>
       <c r="O65" t="n">
-        <v>0.637541298160198</v>
+        <v>0.638006200086323</v>
       </c>
       <c r="P65" t="s">
         <v>173</v>
@@ -5193,7 +5193,7 @@
         <v>29</v>
       </c>
       <c r="S65" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="66">
@@ -5238,7 +5238,7 @@
         <v>3</v>
       </c>
       <c r="O66" t="n">
-        <v>0.714414977306449</v>
+        <v>0.736903858362285</v>
       </c>
       <c r="P66" t="s">
         <v>175</v>
@@ -5250,7 +5250,7 @@
         <v>29</v>
       </c>
       <c r="S66" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="67">
@@ -5295,7 +5295,7 @@
         <v>3</v>
       </c>
       <c r="O67" t="n">
-        <v>0.706403069030319</v>
+        <v>0.731197117322011</v>
       </c>
       <c r="P67" t="s">
         <v>177</v>
@@ -5307,7 +5307,7 @@
         <v>29</v>
       </c>
       <c r="S67" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="68">
@@ -5352,7 +5352,7 @@
         <v>3</v>
       </c>
       <c r="O68" t="n">
-        <v>0.627486493881337</v>
+        <v>0.641357381271678</v>
       </c>
       <c r="P68" t="s">
         <v>179</v>
@@ -5364,7 +5364,7 @@
         <v>29</v>
       </c>
       <c r="S68" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="69">
@@ -5407,7 +5407,7 @@
         <v>3</v>
       </c>
       <c r="O69" t="n">
-        <v>0.680093301182304</v>
+        <v>0.690526146141207</v>
       </c>
       <c r="P69" t="s">
         <v>181</v>
@@ -5419,7 +5419,7 @@
         <v>29</v>
       </c>
       <c r="S69" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="70">
@@ -5462,7 +5462,7 @@
         <v>3</v>
       </c>
       <c r="O70" t="n">
-        <v>0.518739574065344</v>
+        <v>0.495121242262195</v>
       </c>
       <c r="P70" t="s">
         <v>183</v>
@@ -5474,7 +5474,7 @@
         <v>29</v>
       </c>
       <c r="S70" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="71">
@@ -5517,7 +5517,7 @@
         <v>3</v>
       </c>
       <c r="O71" t="n">
-        <v>0.558187784501707</v>
+        <v>0.550516340114664</v>
       </c>
       <c r="P71" t="s">
         <v>185</v>
@@ -5529,7 +5529,7 @@
         <v>29</v>
       </c>
       <c r="S71" s="1" t="n">
-        <v>45979.8474067128</v>
+        <v>45985.64482983</v>
       </c>
     </row>
     <row r="72">
@@ -5572,7 +5572,7 @@
         <v>4</v>
       </c>
       <c r="O72" t="n">
-        <v>0.752643217556852</v>
+        <v>0.774405413107744</v>
       </c>
       <c r="P72" t="s">
         <v>187</v>
@@ -5584,7 +5584,7 @@
         <v>29</v>
       </c>
       <c r="S72" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="73">
@@ -5627,7 +5627,7 @@
         <v>4</v>
       </c>
       <c r="O73" t="n">
-        <v>0.539179719234225</v>
+        <v>0.523233763643102</v>
       </c>
       <c r="P73" t="s">
         <v>189</v>
@@ -5639,7 +5639,7 @@
         <v>29</v>
       </c>
       <c r="S73" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="74">
@@ -5682,7 +5682,7 @@
         <v>4</v>
       </c>
       <c r="O74" t="n">
-        <v>0.59926108386558</v>
+        <v>0.584303291814537</v>
       </c>
       <c r="P74" t="s">
         <v>191</v>
@@ -5694,7 +5694,7 @@
         <v>29</v>
       </c>
       <c r="S74" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="75">
@@ -5737,7 +5737,7 @@
         <v>4</v>
       </c>
       <c r="O75" t="n">
-        <v>0.75282478886986</v>
+        <v>0.766526981123731</v>
       </c>
       <c r="P75" t="s">
         <v>193</v>
@@ -5749,7 +5749,7 @@
         <v>29</v>
       </c>
       <c r="S75" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="76">
@@ -5792,7 +5792,7 @@
         <v>4</v>
       </c>
       <c r="O76" t="n">
-        <v>0.746552518885612</v>
+        <v>0.747544053021771</v>
       </c>
       <c r="P76" t="s">
         <v>195</v>
@@ -5804,7 +5804,7 @@
         <v>29</v>
       </c>
       <c r="S76" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="77">
@@ -5847,7 +5847,7 @@
         <v>4</v>
       </c>
       <c r="O77" t="n">
-        <v>0.792692150044183</v>
+        <v>0.754445646685511</v>
       </c>
       <c r="P77" t="s">
         <v>197</v>
@@ -5859,7 +5859,7 @@
         <v>29</v>
       </c>
       <c r="S77" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="78">
@@ -5902,7 +5902,7 @@
         <v>4</v>
       </c>
       <c r="O78" t="n">
-        <v>0.784252335610876</v>
+        <v>0.777751101181543</v>
       </c>
       <c r="P78" t="s">
         <v>199</v>
@@ -5914,7 +5914,7 @@
         <v>29</v>
       </c>
       <c r="S78" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="79">
@@ -5957,7 +5957,7 @@
         <v>4</v>
       </c>
       <c r="O79" t="n">
-        <v>0.710803754522177</v>
+        <v>0.726052192425031</v>
       </c>
       <c r="P79" t="s">
         <v>201</v>
@@ -5969,7 +5969,7 @@
         <v>29</v>
       </c>
       <c r="S79" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="80">
@@ -6012,7 +6012,7 @@
         <v>4</v>
       </c>
       <c r="O80" t="n">
-        <v>0.739506486992784</v>
+        <v>0.751783254033186</v>
       </c>
       <c r="P80" t="s">
         <v>203</v>
@@ -6024,7 +6024,7 @@
         <v>29</v>
       </c>
       <c r="S80" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="81">
@@ -6067,7 +6067,7 @@
         <v>4</v>
       </c>
       <c r="O81" t="n">
-        <v>0.652377288880286</v>
+        <v>0.628476600663248</v>
       </c>
       <c r="P81" t="s">
         <v>205</v>
@@ -6079,7 +6079,7 @@
         <v>29</v>
       </c>
       <c r="S81" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="82">
@@ -6122,7 +6122,7 @@
         <v>4</v>
       </c>
       <c r="O82" t="n">
-        <v>0.679139986522575</v>
+        <v>0.669578889098985</v>
       </c>
       <c r="P82" t="s">
         <v>207</v>
@@ -6134,7 +6134,7 @@
         <v>29</v>
       </c>
       <c r="S82" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="83">
@@ -6177,7 +6177,7 @@
         <v>4</v>
       </c>
       <c r="O83" t="n">
-        <v>0.682834230282628</v>
+        <v>0.694969961422175</v>
       </c>
       <c r="P83" t="s">
         <v>209</v>
@@ -6189,7 +6189,7 @@
         <v>29</v>
       </c>
       <c r="S83" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="84">
@@ -6230,7 +6230,7 @@
         <v>4</v>
       </c>
       <c r="O84" t="n">
-        <v>0.741793254548826</v>
+        <v>0.741707934777286</v>
       </c>
       <c r="P84" t="s">
         <v>211</v>
@@ -6242,7 +6242,7 @@
         <v>29</v>
       </c>
       <c r="S84" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="85">
@@ -6283,7 +6283,7 @@
         <v>4</v>
       </c>
       <c r="O85" t="n">
-        <v>0.703941551910402</v>
+        <v>0.710803004989786</v>
       </c>
       <c r="P85" t="s">
         <v>213</v>
@@ -6295,7 +6295,7 @@
         <v>29</v>
       </c>
       <c r="S85" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="86">
@@ -6340,7 +6340,7 @@
         <v>4</v>
       </c>
       <c r="O86" t="n">
-        <v>0.73001023567628</v>
+        <v>0.743066853726215</v>
       </c>
       <c r="P86" t="s">
         <v>215</v>
@@ -6352,7 +6352,7 @@
         <v>29</v>
       </c>
       <c r="S86" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="87">
@@ -6397,7 +6397,7 @@
         <v>4</v>
       </c>
       <c r="O87" t="n">
-        <v>0.746902930036739</v>
+        <v>0.771489497812191</v>
       </c>
       <c r="P87" t="s">
         <v>217</v>
@@ -6409,7 +6409,7 @@
         <v>29</v>
       </c>
       <c r="S87" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="88">
@@ -6454,7 +6454,7 @@
         <v>4</v>
       </c>
       <c r="O88" t="n">
-        <v>0.746552678311125</v>
+        <v>0.733620681670334</v>
       </c>
       <c r="P88" t="s">
         <v>219</v>
@@ -6466,7 +6466,7 @@
         <v>29</v>
       </c>
       <c r="S88" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="89">
@@ -6511,7 +6511,7 @@
         <v>4</v>
       </c>
       <c r="O89" t="n">
-        <v>0.738393073760685</v>
+        <v>0.752768015629217</v>
       </c>
       <c r="P89" t="s">
         <v>221</v>
@@ -6523,7 +6523,7 @@
         <v>29</v>
       </c>
       <c r="S89" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="90">
@@ -6568,7 +6568,7 @@
         <v>4</v>
       </c>
       <c r="O90" t="n">
-        <v>0.77470076458028</v>
+        <v>0.768176691957461</v>
       </c>
       <c r="P90" t="s">
         <v>223</v>
@@ -6580,7 +6580,7 @@
         <v>29</v>
       </c>
       <c r="S90" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="91">
@@ -6625,7 +6625,7 @@
         <v>4</v>
       </c>
       <c r="O91" t="n">
-        <v>0.740118928484404</v>
+        <v>0.76798518678142</v>
       </c>
       <c r="P91" t="s">
         <v>225</v>
@@ -6637,7 +6637,7 @@
         <v>29</v>
       </c>
       <c r="S91" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="92">
@@ -6680,7 +6680,7 @@
         <v>4</v>
       </c>
       <c r="O92" t="n">
-        <v>0.752538241062855</v>
+        <v>0.774223863257697</v>
       </c>
       <c r="P92" t="s">
         <v>227</v>
@@ -6692,7 +6692,7 @@
         <v>29</v>
       </c>
       <c r="S92" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="93">
@@ -6735,7 +6735,7 @@
         <v>4</v>
       </c>
       <c r="O93" t="n">
-        <v>0.514382915509546</v>
+        <v>0.506808111722981</v>
       </c>
       <c r="P93" t="s">
         <v>229</v>
@@ -6747,7 +6747,7 @@
         <v>29</v>
       </c>
       <c r="S93" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="94">
@@ -6790,7 +6790,7 @@
         <v>4</v>
       </c>
       <c r="O94" t="n">
-        <v>0.603491567534324</v>
+        <v>0.590236582846786</v>
       </c>
       <c r="P94" t="s">
         <v>231</v>
@@ -6802,7 +6802,7 @@
         <v>29</v>
       </c>
       <c r="S94" s="1" t="n">
-        <v>45979.9906462271</v>
+        <v>45985.8112113451</v>
       </c>
     </row>
     <row r="95">
@@ -6816,7 +6816,7 @@
         <v>20</v>
       </c>
       <c r="D95" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E95" t="s">
         <v>22</v>
@@ -6845,7 +6845,7 @@
         <v>5</v>
       </c>
       <c r="O95" t="n">
-        <v>0.799748002413642</v>
+        <v>0.766473975477897</v>
       </c>
       <c r="P95" t="s">
         <v>233</v>
@@ -6857,7 +6857,7 @@
         <v>29</v>
       </c>
       <c r="S95" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="96">
@@ -6871,7 +6871,7 @@
         <v>20</v>
       </c>
       <c r="D96" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E96" t="s">
         <v>22</v>
@@ -6900,7 +6900,7 @@
         <v>5</v>
       </c>
       <c r="O96" t="n">
-        <v>0.590355847849971</v>
+        <v>0.526787005532056</v>
       </c>
       <c r="P96" t="s">
         <v>235</v>
@@ -6912,7 +6912,7 @@
         <v>29</v>
       </c>
       <c r="S96" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="97">
@@ -6926,7 +6926,7 @@
         <v>20</v>
       </c>
       <c r="D97" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E97" t="s">
         <v>22</v>
@@ -6955,7 +6955,7 @@
         <v>5</v>
       </c>
       <c r="O97" t="n">
-        <v>0.71232433941424</v>
+        <v>0.631212621383368</v>
       </c>
       <c r="P97" t="s">
         <v>237</v>
@@ -6967,7 +6967,7 @@
         <v>29</v>
       </c>
       <c r="S97" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="98">
@@ -6981,7 +6981,7 @@
         <v>39</v>
       </c>
       <c r="D98" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E98" t="s">
         <v>22</v>
@@ -7010,7 +7010,7 @@
         <v>5</v>
       </c>
       <c r="O98" t="n">
-        <v>0.796692540210414</v>
+        <v>0.789275481161773</v>
       </c>
       <c r="P98" t="s">
         <v>239</v>
@@ -7022,7 +7022,7 @@
         <v>29</v>
       </c>
       <c r="S98" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="99">
@@ -7036,7 +7036,7 @@
         <v>42</v>
       </c>
       <c r="D99" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E99" t="s">
         <v>22</v>
@@ -7065,7 +7065,7 @@
         <v>5</v>
       </c>
       <c r="O99" t="n">
-        <v>0.807425983526882</v>
+        <v>0.749779048774627</v>
       </c>
       <c r="P99" t="s">
         <v>241</v>
@@ -7077,7 +7077,7 @@
         <v>29</v>
       </c>
       <c r="S99" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="100">
@@ -7091,7 +7091,7 @@
         <v>20</v>
       </c>
       <c r="D100" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E100" t="s">
         <v>22</v>
@@ -7120,7 +7120,7 @@
         <v>5</v>
       </c>
       <c r="O100" t="n">
-        <v>0.781128704665098</v>
+        <v>0.794444976938041</v>
       </c>
       <c r="P100" t="s">
         <v>243</v>
@@ -7132,7 +7132,7 @@
         <v>29</v>
       </c>
       <c r="S100" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="101">
@@ -7175,7 +7175,7 @@
         <v>5</v>
       </c>
       <c r="O101" t="n">
-        <v>0.760808644972891</v>
+        <v>0.772602067286886</v>
       </c>
       <c r="P101" t="s">
         <v>245</v>
@@ -7187,7 +7187,7 @@
         <v>29</v>
       </c>
       <c r="S101" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="102">
@@ -7201,7 +7201,7 @@
         <v>20</v>
       </c>
       <c r="D102" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E102" t="s">
         <v>51</v>
@@ -7230,7 +7230,7 @@
         <v>5</v>
       </c>
       <c r="O102" t="n">
-        <v>0.730052110596496</v>
+        <v>0.73620750245775</v>
       </c>
       <c r="P102" t="s">
         <v>247</v>
@@ -7242,7 +7242,7 @@
         <v>29</v>
       </c>
       <c r="S102" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="103">
@@ -7256,7 +7256,7 @@
         <v>20</v>
       </c>
       <c r="D103" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E103" t="s">
         <v>54</v>
@@ -7285,7 +7285,7 @@
         <v>5</v>
       </c>
       <c r="O103" t="n">
-        <v>0.782862847643522</v>
+        <v>0.754227666443598</v>
       </c>
       <c r="P103" t="s">
         <v>249</v>
@@ -7297,7 +7297,7 @@
         <v>29</v>
       </c>
       <c r="S103" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="104">
@@ -7311,7 +7311,7 @@
         <v>20</v>
       </c>
       <c r="D104" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E104" t="s">
         <v>22</v>
@@ -7340,7 +7340,7 @@
         <v>5</v>
       </c>
       <c r="O104" t="n">
-        <v>0.664055963742565</v>
+        <v>0.672631704810246</v>
       </c>
       <c r="P104" t="s">
         <v>251</v>
@@ -7352,7 +7352,7 @@
         <v>29</v>
       </c>
       <c r="S104" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="105">
@@ -7366,7 +7366,7 @@
         <v>20</v>
       </c>
       <c r="D105" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E105" t="s">
         <v>22</v>
@@ -7395,7 +7395,7 @@
         <v>5</v>
       </c>
       <c r="O105" t="n">
-        <v>0.693001540648652</v>
+        <v>0.679386117140094</v>
       </c>
       <c r="P105" t="s">
         <v>253</v>
@@ -7407,7 +7407,7 @@
         <v>29</v>
       </c>
       <c r="S105" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="106">
@@ -7421,7 +7421,7 @@
         <v>20</v>
       </c>
       <c r="D106" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E106" t="s">
         <v>22</v>
@@ -7450,7 +7450,7 @@
         <v>5</v>
       </c>
       <c r="O106" t="n">
-        <v>0.695814397424992</v>
+        <v>0.723836009696808</v>
       </c>
       <c r="P106" t="s">
         <v>255</v>
@@ -7462,7 +7462,7 @@
         <v>29</v>
       </c>
       <c r="S106" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="107">
@@ -7476,7 +7476,7 @@
         <v>20</v>
       </c>
       <c r="D107" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E107" t="s">
         <v>22</v>
@@ -7503,7 +7503,7 @@
         <v>5</v>
       </c>
       <c r="O107" t="n">
-        <v>0.746136825959536</v>
+        <v>0.72666136432647</v>
       </c>
       <c r="P107" t="s">
         <v>257</v>
@@ -7515,7 +7515,7 @@
         <v>29</v>
       </c>
       <c r="S107" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="108">
@@ -7529,7 +7529,7 @@
         <v>20</v>
       </c>
       <c r="D108" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E108" t="s">
         <v>22</v>
@@ -7556,7 +7556,7 @@
         <v>5</v>
       </c>
       <c r="O108" t="n">
-        <v>0.697503048877351</v>
+        <v>0.705494881775721</v>
       </c>
       <c r="P108" t="s">
         <v>259</v>
@@ -7568,7 +7568,7 @@
         <v>29</v>
       </c>
       <c r="S108" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="109">
@@ -7582,7 +7582,7 @@
         <v>20</v>
       </c>
       <c r="D109" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E109" t="s">
         <v>22</v>
@@ -7613,7 +7613,7 @@
         <v>5</v>
       </c>
       <c r="O109" t="n">
-        <v>0.767365565685528</v>
+        <v>0.753167173351403</v>
       </c>
       <c r="P109" t="s">
         <v>261</v>
@@ -7625,7 +7625,7 @@
         <v>29</v>
       </c>
       <c r="S109" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="110">
@@ -7639,7 +7639,7 @@
         <v>20</v>
       </c>
       <c r="D110" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E110" t="s">
         <v>22</v>
@@ -7670,7 +7670,7 @@
         <v>5</v>
       </c>
       <c r="O110" t="n">
-        <v>0.762820587263344</v>
+        <v>0.795561603120694</v>
       </c>
       <c r="P110" t="s">
         <v>263</v>
@@ -7682,7 +7682,7 @@
         <v>29</v>
       </c>
       <c r="S110" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="111">
@@ -7696,7 +7696,7 @@
         <v>20</v>
       </c>
       <c r="D111" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E111" t="s">
         <v>22</v>
@@ -7727,7 +7727,7 @@
         <v>5</v>
       </c>
       <c r="O111" t="n">
-        <v>0.790905620363658</v>
+        <v>0.765093795476825</v>
       </c>
       <c r="P111" t="s">
         <v>265</v>
@@ -7739,7 +7739,7 @@
         <v>29</v>
       </c>
       <c r="S111" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="112">
@@ -7753,7 +7753,7 @@
         <v>20</v>
       </c>
       <c r="D112" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E112" t="s">
         <v>22</v>
@@ -7784,7 +7784,7 @@
         <v>5</v>
       </c>
       <c r="O112" t="n">
-        <v>0.782258287010902</v>
+        <v>0.758498497146465</v>
       </c>
       <c r="P112" t="s">
         <v>267</v>
@@ -7796,7 +7796,7 @@
         <v>29</v>
       </c>
       <c r="S112" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="113">
@@ -7810,7 +7810,7 @@
         <v>20</v>
       </c>
       <c r="D113" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E113" t="s">
         <v>22</v>
@@ -7841,7 +7841,7 @@
         <v>5</v>
       </c>
       <c r="O113" t="n">
-        <v>0.766009029422941</v>
+        <v>0.795990258468379</v>
       </c>
       <c r="P113" t="s">
         <v>269</v>
@@ -7853,7 +7853,7 @@
         <v>29</v>
       </c>
       <c r="S113" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="114">
@@ -7867,7 +7867,7 @@
         <v>20</v>
       </c>
       <c r="D114" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E114" t="s">
         <v>22</v>
@@ -7898,7 +7898,7 @@
         <v>5</v>
       </c>
       <c r="O114" t="n">
-        <v>0.796317751579419</v>
+        <v>0.775910855516541</v>
       </c>
       <c r="P114" t="s">
         <v>271</v>
@@ -7910,7 +7910,7 @@
         <v>29</v>
       </c>
       <c r="S114" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="115">
@@ -7924,7 +7924,7 @@
         <v>20</v>
       </c>
       <c r="D115" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E115" t="s">
         <v>22</v>
@@ -7953,7 +7953,7 @@
         <v>5</v>
       </c>
       <c r="O115" t="n">
-        <v>0.796448258565066</v>
+        <v>0.766556660329898</v>
       </c>
       <c r="P115" t="s">
         <v>273</v>
@@ -7965,7 +7965,7 @@
         <v>29</v>
       </c>
       <c r="S115" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="116">
@@ -7979,7 +7979,7 @@
         <v>20</v>
       </c>
       <c r="D116" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E116" t="s">
         <v>22</v>
@@ -8008,7 +8008,7 @@
         <v>5</v>
       </c>
       <c r="O116" t="n">
-        <v>0.557419297405456</v>
+        <v>0.511004307225321</v>
       </c>
       <c r="P116" t="s">
         <v>275</v>
@@ -8020,7 +8020,7 @@
         <v>29</v>
       </c>
       <c r="S116" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="117">
@@ -8034,7 +8034,7 @@
         <v>20</v>
       </c>
       <c r="D117" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E117" t="s">
         <v>22</v>
@@ -8063,7 +8063,7 @@
         <v>5</v>
       </c>
       <c r="O117" t="n">
-        <v>0.617678216788099</v>
+        <v>0.606164938003935</v>
       </c>
       <c r="P117" t="s">
         <v>277</v>
@@ -8075,7 +8075,7 @@
         <v>29</v>
       </c>
       <c r="S117" s="1" t="n">
-        <v>45980.5760247243</v>
+        <v>45985.9427053083</v>
       </c>
     </row>
     <row r="118">
@@ -8086,10 +8086,10 @@
         <v>36</v>
       </c>
       <c r="C118" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D118" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E118" t="s">
         <v>22</v>
@@ -8101,13 +8101,15 @@
         <v>63</v>
       </c>
       <c r="H118" t="s">
-        <v>25</v>
-      </c>
-      <c r="I118"/>
-      <c r="J118" t="b">
-        <v>0</v>
-      </c>
-      <c r="K118"/>
+        <v>72</v>
+      </c>
+      <c r="I118" t="s">
+        <v>76</v>
+      </c>
+      <c r="J118"/>
+      <c r="K118" t="b">
+        <v>0</v>
+      </c>
       <c r="L118" t="s">
         <v>92</v>
       </c>
@@ -8118,7 +8120,7 @@
         <v>6</v>
       </c>
       <c r="O118" t="n">
-        <v>0.768620262103608</v>
+        <v>0.790647408094017</v>
       </c>
       <c r="P118" t="s">
         <v>279</v>
@@ -8130,7 +8132,7 @@
         <v>29</v>
       </c>
       <c r="S118" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="119">
@@ -8141,10 +8143,10 @@
         <v>19</v>
       </c>
       <c r="C119" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D119" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E119" t="s">
         <v>22</v>
@@ -8156,13 +8158,15 @@
         <v>63</v>
       </c>
       <c r="H119" t="s">
-        <v>25</v>
-      </c>
-      <c r="I119"/>
-      <c r="J119" t="b">
-        <v>0</v>
-      </c>
-      <c r="K119"/>
+        <v>72</v>
+      </c>
+      <c r="I119" t="s">
+        <v>76</v>
+      </c>
+      <c r="J119"/>
+      <c r="K119" t="b">
+        <v>0</v>
+      </c>
       <c r="L119" t="s">
         <v>92</v>
       </c>
@@ -8173,7 +8177,7 @@
         <v>6</v>
       </c>
       <c r="O119" t="n">
-        <v>0.605264940225356</v>
+        <v>0.443437644149889</v>
       </c>
       <c r="P119" t="s">
         <v>281</v>
@@ -8185,7 +8189,7 @@
         <v>29</v>
       </c>
       <c r="S119" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="120">
@@ -8196,10 +8200,10 @@
         <v>33</v>
       </c>
       <c r="C120" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D120" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E120" t="s">
         <v>22</v>
@@ -8211,13 +8215,15 @@
         <v>63</v>
       </c>
       <c r="H120" t="s">
-        <v>25</v>
-      </c>
-      <c r="I120"/>
-      <c r="J120" t="b">
-        <v>0</v>
-      </c>
-      <c r="K120"/>
+        <v>72</v>
+      </c>
+      <c r="I120" t="s">
+        <v>76</v>
+      </c>
+      <c r="J120"/>
+      <c r="K120" t="b">
+        <v>0</v>
+      </c>
       <c r="L120" t="s">
         <v>92</v>
       </c>
@@ -8228,7 +8234,7 @@
         <v>6</v>
       </c>
       <c r="O120" t="n">
-        <v>0.682685227139316</v>
+        <v>0.408656554666398</v>
       </c>
       <c r="P120" t="s">
         <v>283</v>
@@ -8240,7 +8246,7 @@
         <v>29</v>
       </c>
       <c r="S120" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="121">
@@ -8251,10 +8257,10 @@
         <v>36</v>
       </c>
       <c r="C121" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D121" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E121" t="s">
         <v>22</v>
@@ -8266,13 +8272,15 @@
         <v>63</v>
       </c>
       <c r="H121" t="s">
-        <v>25</v>
-      </c>
-      <c r="I121"/>
-      <c r="J121" t="b">
-        <v>0</v>
-      </c>
-      <c r="K121"/>
+        <v>72</v>
+      </c>
+      <c r="I121" t="s">
+        <v>76</v>
+      </c>
+      <c r="J121"/>
+      <c r="K121" t="b">
+        <v>0</v>
+      </c>
       <c r="L121" t="s">
         <v>92</v>
       </c>
@@ -8283,7 +8291,7 @@
         <v>6</v>
       </c>
       <c r="O121" t="n">
-        <v>0.791572764308803</v>
+        <v>0.780532183110085</v>
       </c>
       <c r="P121" t="s">
         <v>285</v>
@@ -8295,7 +8303,7 @@
         <v>29</v>
       </c>
       <c r="S121" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="122">
@@ -8306,10 +8314,10 @@
         <v>36</v>
       </c>
       <c r="C122" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D122" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E122" t="s">
         <v>22</v>
@@ -8321,13 +8329,15 @@
         <v>63</v>
       </c>
       <c r="H122" t="s">
-        <v>25</v>
-      </c>
-      <c r="I122"/>
-      <c r="J122" t="b">
-        <v>0</v>
-      </c>
-      <c r="K122"/>
+        <v>72</v>
+      </c>
+      <c r="I122" t="s">
+        <v>76</v>
+      </c>
+      <c r="J122"/>
+      <c r="K122" t="b">
+        <v>0</v>
+      </c>
       <c r="L122" t="s">
         <v>92</v>
       </c>
@@ -8338,7 +8348,7 @@
         <v>6</v>
       </c>
       <c r="O122" t="n">
-        <v>0.764567197040383</v>
+        <v>0.767899254552542</v>
       </c>
       <c r="P122" t="s">
         <v>287</v>
@@ -8350,7 +8360,7 @@
         <v>29</v>
       </c>
       <c r="S122" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="123">
@@ -8361,10 +8371,10 @@
         <v>36</v>
       </c>
       <c r="C123" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D123" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E123" t="s">
         <v>22</v>
@@ -8376,13 +8386,15 @@
         <v>63</v>
       </c>
       <c r="H123" t="s">
-        <v>25</v>
-      </c>
-      <c r="I123"/>
-      <c r="J123" t="b">
-        <v>0</v>
-      </c>
-      <c r="K123"/>
+        <v>72</v>
+      </c>
+      <c r="I123" t="s">
+        <v>76</v>
+      </c>
+      <c r="J123"/>
+      <c r="K123" t="b">
+        <v>0</v>
+      </c>
       <c r="L123" t="s">
         <v>92</v>
       </c>
@@ -8393,7 +8405,7 @@
         <v>6</v>
       </c>
       <c r="O123" t="n">
-        <v>0.758035437427941</v>
+        <v>0.790304948149864</v>
       </c>
       <c r="P123" t="s">
         <v>289</v>
@@ -8405,7 +8417,7 @@
         <v>29</v>
       </c>
       <c r="S123" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="124">
@@ -8416,7 +8428,7 @@
         <v>36</v>
       </c>
       <c r="C124" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D124" t="s">
         <v>21</v>
@@ -8431,13 +8443,15 @@
         <v>63</v>
       </c>
       <c r="H124" t="s">
-        <v>25</v>
-      </c>
-      <c r="I124"/>
-      <c r="J124" t="b">
-        <v>0</v>
-      </c>
-      <c r="K124"/>
+        <v>72</v>
+      </c>
+      <c r="I124" t="s">
+        <v>76</v>
+      </c>
+      <c r="J124"/>
+      <c r="K124" t="b">
+        <v>0</v>
+      </c>
       <c r="L124" t="s">
         <v>92</v>
       </c>
@@ -8448,7 +8462,7 @@
         <v>6</v>
       </c>
       <c r="O124" t="n">
-        <v>0.763896584738946</v>
+        <v>0.754360059398616</v>
       </c>
       <c r="P124" t="s">
         <v>291</v>
@@ -8460,7 +8474,7 @@
         <v>29</v>
       </c>
       <c r="S124" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="125">
@@ -8471,10 +8485,10 @@
         <v>36</v>
       </c>
       <c r="C125" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D125" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E125" t="s">
         <v>51</v>
@@ -8486,13 +8500,15 @@
         <v>63</v>
       </c>
       <c r="H125" t="s">
-        <v>25</v>
-      </c>
-      <c r="I125"/>
-      <c r="J125" t="b">
-        <v>0</v>
-      </c>
-      <c r="K125"/>
+        <v>72</v>
+      </c>
+      <c r="I125" t="s">
+        <v>76</v>
+      </c>
+      <c r="J125"/>
+      <c r="K125" t="b">
+        <v>0</v>
+      </c>
       <c r="L125" t="s">
         <v>92</v>
       </c>
@@ -8503,7 +8519,7 @@
         <v>6</v>
       </c>
       <c r="O125" t="n">
-        <v>0.74308316616365</v>
+        <v>0.723783603787461</v>
       </c>
       <c r="P125" t="s">
         <v>293</v>
@@ -8515,7 +8531,7 @@
         <v>29</v>
       </c>
       <c r="S125" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="126">
@@ -8526,10 +8542,10 @@
         <v>36</v>
       </c>
       <c r="C126" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D126" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E126" t="s">
         <v>54</v>
@@ -8541,13 +8557,15 @@
         <v>63</v>
       </c>
       <c r="H126" t="s">
-        <v>25</v>
-      </c>
-      <c r="I126"/>
-      <c r="J126" t="b">
-        <v>0</v>
-      </c>
-      <c r="K126"/>
+        <v>72</v>
+      </c>
+      <c r="I126" t="s">
+        <v>76</v>
+      </c>
+      <c r="J126"/>
+      <c r="K126" t="b">
+        <v>0</v>
+      </c>
       <c r="L126" t="s">
         <v>92</v>
       </c>
@@ -8558,7 +8576,7 @@
         <v>6</v>
       </c>
       <c r="O126" t="n">
-        <v>0.7778526994675</v>
+        <v>0.789725364210528</v>
       </c>
       <c r="P126" t="s">
         <v>295</v>
@@ -8570,7 +8588,7 @@
         <v>29</v>
       </c>
       <c r="S126" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="127">
@@ -8581,10 +8599,10 @@
         <v>36</v>
       </c>
       <c r="C127" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D127" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E127" t="s">
         <v>22</v>
@@ -8596,13 +8614,15 @@
         <v>63</v>
       </c>
       <c r="H127" t="s">
-        <v>25</v>
-      </c>
-      <c r="I127"/>
-      <c r="J127" t="b">
-        <v>0</v>
-      </c>
-      <c r="K127"/>
+        <v>72</v>
+      </c>
+      <c r="I127" t="s">
+        <v>76</v>
+      </c>
+      <c r="J127"/>
+      <c r="K127" t="b">
+        <v>0</v>
+      </c>
       <c r="L127" t="s">
         <v>92</v>
       </c>
@@ -8613,7 +8633,7 @@
         <v>6</v>
       </c>
       <c r="O127" t="n">
-        <v>0.676667931774276</v>
+        <v>0.683851921157813</v>
       </c>
       <c r="P127" t="s">
         <v>297</v>
@@ -8625,7 +8645,7 @@
         <v>29</v>
       </c>
       <c r="S127" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="128">
@@ -8636,10 +8656,10 @@
         <v>36</v>
       </c>
       <c r="C128" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D128" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E128" t="s">
         <v>22</v>
@@ -8651,13 +8671,15 @@
         <v>60</v>
       </c>
       <c r="H128" t="s">
-        <v>25</v>
-      </c>
-      <c r="I128"/>
-      <c r="J128" t="b">
-        <v>0</v>
-      </c>
-      <c r="K128"/>
+        <v>72</v>
+      </c>
+      <c r="I128" t="s">
+        <v>76</v>
+      </c>
+      <c r="J128"/>
+      <c r="K128" t="b">
+        <v>0</v>
+      </c>
       <c r="L128" t="s">
         <v>92</v>
       </c>
@@ -8668,7 +8690,7 @@
         <v>6</v>
       </c>
       <c r="O128" t="n">
-        <v>0.727973041043722</v>
+        <v>0.733220718188771</v>
       </c>
       <c r="P128" t="s">
         <v>299</v>
@@ -8680,7 +8702,7 @@
         <v>29</v>
       </c>
       <c r="S128" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="129">
@@ -8691,10 +8713,10 @@
         <v>36</v>
       </c>
       <c r="C129" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D129" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E129" t="s">
         <v>22</v>
@@ -8706,13 +8728,15 @@
         <v>24</v>
       </c>
       <c r="H129" t="s">
-        <v>25</v>
-      </c>
-      <c r="I129"/>
-      <c r="J129" t="b">
-        <v>0</v>
-      </c>
-      <c r="K129"/>
+        <v>72</v>
+      </c>
+      <c r="I129" t="s">
+        <v>76</v>
+      </c>
+      <c r="J129"/>
+      <c r="K129" t="b">
+        <v>0</v>
+      </c>
       <c r="L129" t="s">
         <v>92</v>
       </c>
@@ -8723,7 +8747,7 @@
         <v>6</v>
       </c>
       <c r="O129" t="n">
-        <v>0.737137703410927</v>
+        <v>0.751594577513047</v>
       </c>
       <c r="P129" t="s">
         <v>301</v>
@@ -8735,7 +8759,7 @@
         <v>29</v>
       </c>
       <c r="S129" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="130">
@@ -8746,10 +8770,10 @@
         <v>36</v>
       </c>
       <c r="C130" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D130" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E130" t="s">
         <v>22</v>
@@ -8776,7 +8800,7 @@
         <v>6</v>
       </c>
       <c r="O130" t="n">
-        <v>0.735664038709585</v>
+        <v>0.774509790877583</v>
       </c>
       <c r="P130" t="s">
         <v>303</v>
@@ -8788,7 +8812,7 @@
         <v>29</v>
       </c>
       <c r="S130" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="131">
@@ -8799,10 +8823,10 @@
         <v>36</v>
       </c>
       <c r="C131" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D131" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E131" t="s">
         <v>22</v>
@@ -8829,7 +8853,7 @@
         <v>6</v>
       </c>
       <c r="O131" t="n">
-        <v>0.740389189859266</v>
+        <v>0.710971146803312</v>
       </c>
       <c r="P131" t="s">
         <v>305</v>
@@ -8841,7 +8865,7 @@
         <v>29</v>
       </c>
       <c r="S131" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="132">
@@ -8852,10 +8876,10 @@
         <v>36</v>
       </c>
       <c r="C132" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D132" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E132" t="s">
         <v>22</v>
@@ -8886,7 +8910,7 @@
         <v>6</v>
       </c>
       <c r="O132" t="n">
-        <v>0.771056015027519</v>
+        <v>0.762193469143312</v>
       </c>
       <c r="P132" t="s">
         <v>307</v>
@@ -8898,7 +8922,7 @@
         <v>29</v>
       </c>
       <c r="S132" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="133">
@@ -8909,10 +8933,10 @@
         <v>36</v>
       </c>
       <c r="C133" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D133" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E133" t="s">
         <v>22</v>
@@ -8943,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="O133" t="n">
-        <v>0.786459404144767</v>
+        <v>0.790324525642624</v>
       </c>
       <c r="P133" t="s">
         <v>309</v>
@@ -8955,7 +8979,7 @@
         <v>29</v>
       </c>
       <c r="S133" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="134">
@@ -8966,10 +8990,10 @@
         <v>36</v>
       </c>
       <c r="C134" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D134" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E134" t="s">
         <v>22</v>
@@ -9000,7 +9024,7 @@
         <v>6</v>
       </c>
       <c r="O134" t="n">
-        <v>0.799498086823464</v>
+        <v>0.765299276592701</v>
       </c>
       <c r="P134" t="s">
         <v>311</v>
@@ -9012,7 +9036,7 @@
         <v>29</v>
       </c>
       <c r="S134" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="135">
@@ -9023,10 +9047,10 @@
         <v>36</v>
       </c>
       <c r="C135" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D135" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E135" t="s">
         <v>22</v>
@@ -9057,7 +9081,7 @@
         <v>6</v>
       </c>
       <c r="O135" t="n">
-        <v>0.787283261689388</v>
+        <v>0.802213119159612</v>
       </c>
       <c r="P135" t="s">
         <v>313</v>
@@ -9069,7 +9093,7 @@
         <v>29</v>
       </c>
       <c r="S135" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="136">
@@ -9080,10 +9104,10 @@
         <v>36</v>
       </c>
       <c r="C136" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D136" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E136" t="s">
         <v>22</v>
@@ -9098,7 +9122,7 @@
         <v>72</v>
       </c>
       <c r="I136" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="J136"/>
       <c r="K136" t="b">
@@ -9114,7 +9138,7 @@
         <v>6</v>
       </c>
       <c r="O136" t="n">
-        <v>0.814736846760874</v>
+        <v>0.756551594553502</v>
       </c>
       <c r="P136" t="s">
         <v>315</v>
@@ -9126,7 +9150,7 @@
         <v>29</v>
       </c>
       <c r="S136" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="137">
@@ -9137,10 +9161,10 @@
         <v>36</v>
       </c>
       <c r="C137" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D137" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E137" t="s">
         <v>22</v>
@@ -9152,15 +9176,13 @@
         <v>63</v>
       </c>
       <c r="H137" t="s">
-        <v>72</v>
-      </c>
-      <c r="I137" t="s">
-        <v>57</v>
-      </c>
-      <c r="J137"/>
-      <c r="K137" t="b">
-        <v>0</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I137"/>
+      <c r="J137" t="b">
+        <v>1</v>
+      </c>
+      <c r="K137"/>
       <c r="L137" t="s">
         <v>92</v>
       </c>
@@ -9171,7 +9193,7 @@
         <v>6</v>
       </c>
       <c r="O137" t="n">
-        <v>0.791127626098254</v>
+        <v>0.769231282774353</v>
       </c>
       <c r="P137" t="s">
         <v>317</v>
@@ -9183,7 +9205,7 @@
         <v>29</v>
       </c>
       <c r="S137" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="138">
@@ -9194,10 +9216,10 @@
         <v>36</v>
       </c>
       <c r="C138" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D138" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E138" t="s">
         <v>22</v>
@@ -9213,7 +9235,7 @@
       </c>
       <c r="I138"/>
       <c r="J138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K138"/>
       <c r="L138" t="s">
@@ -9226,7 +9248,7 @@
         <v>6</v>
       </c>
       <c r="O138" t="n">
-        <v>0.797898903766713</v>
+        <v>0.798764191568195</v>
       </c>
       <c r="P138" t="s">
         <v>319</v>
@@ -9238,7 +9260,7 @@
         <v>29</v>
       </c>
       <c r="S138" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="139">
@@ -9249,10 +9271,10 @@
         <v>36</v>
       </c>
       <c r="C139" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D139" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E139" t="s">
         <v>22</v>
@@ -9264,13 +9286,15 @@
         <v>63</v>
       </c>
       <c r="H139" t="s">
-        <v>25</v>
-      </c>
-      <c r="I139"/>
-      <c r="J139" t="b">
-        <v>0</v>
-      </c>
-      <c r="K139"/>
+        <v>72</v>
+      </c>
+      <c r="I139" t="s">
+        <v>76</v>
+      </c>
+      <c r="J139"/>
+      <c r="K139" t="b">
+        <v>0</v>
+      </c>
       <c r="L139" t="s">
         <v>26</v>
       </c>
@@ -9281,7 +9305,7 @@
         <v>6</v>
       </c>
       <c r="O139" t="n">
-        <v>0.546044131116332</v>
+        <v>0.538874697377346</v>
       </c>
       <c r="P139" t="s">
         <v>321</v>
@@ -9293,7 +9317,7 @@
         <v>29</v>
       </c>
       <c r="S139" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="140">
@@ -9304,10 +9328,10 @@
         <v>36</v>
       </c>
       <c r="C140" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D140" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E140" t="s">
         <v>22</v>
@@ -9319,13 +9343,15 @@
         <v>63</v>
       </c>
       <c r="H140" t="s">
-        <v>25</v>
-      </c>
-      <c r="I140"/>
-      <c r="J140" t="b">
-        <v>0</v>
-      </c>
-      <c r="K140"/>
+        <v>72</v>
+      </c>
+      <c r="I140" t="s">
+        <v>76</v>
+      </c>
+      <c r="J140"/>
+      <c r="K140" t="b">
+        <v>0</v>
+      </c>
       <c r="L140" t="s">
         <v>89</v>
       </c>
@@ -9336,7 +9362,7 @@
         <v>6</v>
       </c>
       <c r="O140" t="n">
-        <v>0.572683608300044</v>
+        <v>0.589406516416519</v>
       </c>
       <c r="P140" t="s">
         <v>323</v>
@@ -9348,7 +9374,7 @@
         <v>29</v>
       </c>
       <c r="S140" s="1" t="n">
-        <v>45980.8282684512</v>
+        <v>45986.077743706</v>
       </c>
     </row>
     <row r="141">
@@ -9359,10 +9385,10 @@
         <v>36</v>
       </c>
       <c r="C141" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D141" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E141" t="s">
         <v>22</v>
@@ -9377,7 +9403,7 @@
         <v>72</v>
       </c>
       <c r="I141" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J141"/>
       <c r="K141" t="b">
@@ -9393,7 +9419,7 @@
         <v>7</v>
       </c>
       <c r="O141" t="n">
-        <v>0.794187087250339</v>
+        <v>0.725536022711769</v>
       </c>
       <c r="P141" t="s">
         <v>325</v>
@@ -9405,7 +9431,7 @@
         <v>29</v>
       </c>
       <c r="S141" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="142">
@@ -9416,10 +9442,10 @@
         <v>19</v>
       </c>
       <c r="C142" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D142" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E142" t="s">
         <v>22</v>
@@ -9434,7 +9460,7 @@
         <v>72</v>
       </c>
       <c r="I142" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J142"/>
       <c r="K142" t="b">
@@ -9450,7 +9476,7 @@
         <v>7</v>
       </c>
       <c r="O142" t="n">
-        <v>0.461407928064613</v>
+        <v>0.589804686496215</v>
       </c>
       <c r="P142" t="s">
         <v>327</v>
@@ -9462,7 +9488,7 @@
         <v>29</v>
       </c>
       <c r="S142" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="143">
@@ -9473,10 +9499,10 @@
         <v>33</v>
       </c>
       <c r="C143" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D143" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E143" t="s">
         <v>22</v>
@@ -9491,7 +9517,7 @@
         <v>72</v>
       </c>
       <c r="I143" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J143"/>
       <c r="K143" t="b">
@@ -9507,7 +9533,7 @@
         <v>7</v>
       </c>
       <c r="O143" t="n">
-        <v>0.456184351491249</v>
+        <v>0.687073363992035</v>
       </c>
       <c r="P143" t="s">
         <v>329</v>
@@ -9519,7 +9545,7 @@
         <v>29</v>
       </c>
       <c r="S143" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="144">
@@ -9530,10 +9556,10 @@
         <v>36</v>
       </c>
       <c r="C144" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D144" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E144" t="s">
         <v>22</v>
@@ -9548,7 +9574,7 @@
         <v>72</v>
       </c>
       <c r="I144" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J144"/>
       <c r="K144" t="b">
@@ -9564,7 +9590,7 @@
         <v>7</v>
       </c>
       <c r="O144" t="n">
-        <v>0.807138104855077</v>
+        <v>0.766894734864184</v>
       </c>
       <c r="P144" t="s">
         <v>331</v>
@@ -9576,7 +9602,7 @@
         <v>29</v>
       </c>
       <c r="S144" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="145">
@@ -9587,10 +9613,10 @@
         <v>36</v>
       </c>
       <c r="C145" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D145" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E145" t="s">
         <v>22</v>
@@ -9605,7 +9631,7 @@
         <v>72</v>
       </c>
       <c r="I145" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J145"/>
       <c r="K145" t="b">
@@ -9621,7 +9647,7 @@
         <v>7</v>
       </c>
       <c r="O145" t="n">
-        <v>0.804807141539247</v>
+        <v>0.753697348443084</v>
       </c>
       <c r="P145" t="s">
         <v>333</v>
@@ -9633,7 +9659,7 @@
         <v>29</v>
       </c>
       <c r="S145" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="146">
@@ -9644,10 +9670,10 @@
         <v>36</v>
       </c>
       <c r="C146" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D146" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E146" t="s">
         <v>22</v>
@@ -9662,7 +9688,7 @@
         <v>72</v>
       </c>
       <c r="I146" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J146"/>
       <c r="K146" t="b">
@@ -9678,7 +9704,7 @@
         <v>7</v>
       </c>
       <c r="O146" t="n">
-        <v>0.770615319150445</v>
+        <v>0.816058484524809</v>
       </c>
       <c r="P146" t="s">
         <v>335</v>
@@ -9690,7 +9716,7 @@
         <v>29</v>
       </c>
       <c r="S146" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="147">
@@ -9701,7 +9727,7 @@
         <v>36</v>
       </c>
       <c r="C147" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D147" t="s">
         <v>21</v>
@@ -9719,7 +9745,7 @@
         <v>72</v>
       </c>
       <c r="I147" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J147"/>
       <c r="K147" t="b">
@@ -9735,7 +9761,7 @@
         <v>7</v>
       </c>
       <c r="O147" t="n">
-        <v>0.753565707530913</v>
+        <v>0.760405224173438</v>
       </c>
       <c r="P147" t="s">
         <v>337</v>
@@ -9747,7 +9773,7 @@
         <v>29</v>
       </c>
       <c r="S147" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="148">
@@ -9758,10 +9784,10 @@
         <v>36</v>
       </c>
       <c r="C148" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D148" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E148" t="s">
         <v>51</v>
@@ -9776,7 +9802,7 @@
         <v>72</v>
       </c>
       <c r="I148" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J148"/>
       <c r="K148" t="b">
@@ -9792,7 +9818,7 @@
         <v>7</v>
       </c>
       <c r="O148" t="n">
-        <v>0.744390001675322</v>
+        <v>0.744627875420513</v>
       </c>
       <c r="P148" t="s">
         <v>339</v>
@@ -9804,7 +9830,7 @@
         <v>29</v>
       </c>
       <c r="S148" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="149">
@@ -9815,10 +9841,10 @@
         <v>36</v>
       </c>
       <c r="C149" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D149" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E149" t="s">
         <v>54</v>
@@ -9833,7 +9859,7 @@
         <v>72</v>
       </c>
       <c r="I149" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J149"/>
       <c r="K149" t="b">
@@ -9849,7 +9875,7 @@
         <v>7</v>
       </c>
       <c r="O149" t="n">
-        <v>0.782431650199784</v>
+        <v>0.76173991706907</v>
       </c>
       <c r="P149" t="s">
         <v>341</v>
@@ -9861,7 +9887,7 @@
         <v>29</v>
       </c>
       <c r="S149" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="150">
@@ -9872,10 +9898,10 @@
         <v>36</v>
       </c>
       <c r="C150" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D150" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E150" t="s">
         <v>22</v>
@@ -9890,7 +9916,7 @@
         <v>72</v>
       </c>
       <c r="I150" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J150"/>
       <c r="K150" t="b">
@@ -9906,7 +9932,7 @@
         <v>7</v>
       </c>
       <c r="O150" t="n">
-        <v>0.660625656953074</v>
+        <v>0.67543772731925</v>
       </c>
       <c r="P150" t="s">
         <v>343</v>
@@ -9918,7 +9944,7 @@
         <v>29</v>
       </c>
       <c r="S150" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="151">
@@ -9929,10 +9955,10 @@
         <v>36</v>
       </c>
       <c r="C151" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D151" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E151" t="s">
         <v>22</v>
@@ -9947,7 +9973,7 @@
         <v>72</v>
       </c>
       <c r="I151" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J151"/>
       <c r="K151" t="b">
@@ -9963,7 +9989,7 @@
         <v>7</v>
       </c>
       <c r="O151" t="n">
-        <v>0.736981756175838</v>
+        <v>0.73669998247347</v>
       </c>
       <c r="P151" t="s">
         <v>345</v>
@@ -9975,7 +10001,7 @@
         <v>29</v>
       </c>
       <c r="S151" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="152">
@@ -9986,10 +10012,10 @@
         <v>36</v>
       </c>
       <c r="C152" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D152" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E152" t="s">
         <v>22</v>
@@ -10004,7 +10030,7 @@
         <v>72</v>
       </c>
       <c r="I152" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J152"/>
       <c r="K152" t="b">
@@ -10020,7 +10046,7 @@
         <v>7</v>
       </c>
       <c r="O152" t="n">
-        <v>0.743002070337238</v>
+        <v>0.758628951172652</v>
       </c>
       <c r="P152" t="s">
         <v>347</v>
@@ -10032,7 +10058,7 @@
         <v>29</v>
       </c>
       <c r="S152" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="153">
@@ -10043,10 +10069,10 @@
         <v>36</v>
       </c>
       <c r="C153" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D153" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E153" t="s">
         <v>22</v>
@@ -10073,7 +10099,7 @@
         <v>7</v>
       </c>
       <c r="O153" t="n">
-        <v>0.754249251196263</v>
+        <v>0.744392389344282</v>
       </c>
       <c r="P153" t="s">
         <v>349</v>
@@ -10085,7 +10111,7 @@
         <v>29</v>
       </c>
       <c r="S153" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="154">
@@ -10096,10 +10122,10 @@
         <v>36</v>
       </c>
       <c r="C154" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D154" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E154" t="s">
         <v>22</v>
@@ -10126,7 +10152,7 @@
         <v>7</v>
       </c>
       <c r="O154" t="n">
-        <v>0.721325313415</v>
+        <v>0.711644667835707</v>
       </c>
       <c r="P154" t="s">
         <v>351</v>
@@ -10138,7 +10164,7 @@
         <v>29</v>
       </c>
       <c r="S154" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="155">
@@ -10149,10 +10175,10 @@
         <v>36</v>
       </c>
       <c r="C155" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D155" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E155" t="s">
         <v>22</v>
@@ -10183,7 +10209,7 @@
         <v>7</v>
       </c>
       <c r="O155" t="n">
-        <v>0.775965572706729</v>
+        <v>0.754973838687159</v>
       </c>
       <c r="P155" t="s">
         <v>353</v>
@@ -10195,7 +10221,7 @@
         <v>29</v>
       </c>
       <c r="S155" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="156">
@@ -10206,10 +10232,10 @@
         <v>36</v>
       </c>
       <c r="C156" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D156" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E156" t="s">
         <v>22</v>
@@ -10240,7 +10266,7 @@
         <v>7</v>
       </c>
       <c r="O156" t="n">
-        <v>0.789454390740741</v>
+        <v>0.80065750598257</v>
       </c>
       <c r="P156" t="s">
         <v>355</v>
@@ -10252,7 +10278,7 @@
         <v>29</v>
       </c>
       <c r="S156" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="157">
@@ -10263,10 +10289,10 @@
         <v>36</v>
       </c>
       <c r="C157" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D157" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E157" t="s">
         <v>22</v>
@@ -10297,7 +10323,7 @@
         <v>7</v>
       </c>
       <c r="O157" t="n">
-        <v>0.782212596845362</v>
+        <v>0.766278099744902</v>
       </c>
       <c r="P157" t="s">
         <v>357</v>
@@ -10309,7 +10335,7 @@
         <v>29</v>
       </c>
       <c r="S157" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="158">
@@ -10320,10 +10346,10 @@
         <v>36</v>
       </c>
       <c r="C158" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D158" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E158" t="s">
         <v>22</v>
@@ -10338,7 +10364,7 @@
         <v>72</v>
       </c>
       <c r="I158" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J158"/>
       <c r="K158" t="b">
@@ -10354,7 +10380,7 @@
         <v>7</v>
       </c>
       <c r="O158" t="n">
-        <v>0.772454638092987</v>
+        <v>0.777716008537284</v>
       </c>
       <c r="P158" t="s">
         <v>359</v>
@@ -10366,7 +10392,7 @@
         <v>29</v>
       </c>
       <c r="S158" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="159">
@@ -10377,10 +10403,10 @@
         <v>36</v>
       </c>
       <c r="C159" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D159" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E159" t="s">
         <v>22</v>
@@ -10411,7 +10437,7 @@
         <v>7</v>
       </c>
       <c r="O159" t="n">
-        <v>0.786437783229199</v>
+        <v>0.769744937018355</v>
       </c>
       <c r="P159" t="s">
         <v>361</v>
@@ -10423,7 +10449,7 @@
         <v>29</v>
       </c>
       <c r="S159" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="160">
@@ -10434,10 +10460,10 @@
         <v>36</v>
       </c>
       <c r="C160" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D160" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E160" t="s">
         <v>22</v>
@@ -10466,7 +10492,7 @@
         <v>7</v>
       </c>
       <c r="O160" t="n">
-        <v>0.791948723514708</v>
+        <v>0.796084342122296</v>
       </c>
       <c r="P160" t="s">
         <v>363</v>
@@ -10478,7 +10504,7 @@
         <v>29</v>
       </c>
       <c r="S160" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="161">
@@ -10489,10 +10515,10 @@
         <v>36</v>
       </c>
       <c r="C161" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D161" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E161" t="s">
         <v>22</v>
@@ -10521,7 +10547,7 @@
         <v>7</v>
       </c>
       <c r="O161" t="n">
-        <v>0.76786452637005</v>
+        <v>0.752978712820874</v>
       </c>
       <c r="P161" t="s">
         <v>365</v>
@@ -10533,7 +10559,7 @@
         <v>29</v>
       </c>
       <c r="S161" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="162">
@@ -10544,10 +10570,10 @@
         <v>36</v>
       </c>
       <c r="C162" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D162" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E162" t="s">
         <v>22</v>
@@ -10562,7 +10588,7 @@
         <v>72</v>
       </c>
       <c r="I162" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J162"/>
       <c r="K162" t="b">
@@ -10578,7 +10604,7 @@
         <v>7</v>
       </c>
       <c r="O162" t="n">
-        <v>0.553667897092794</v>
+        <v>0.558780161906256</v>
       </c>
       <c r="P162" t="s">
         <v>367</v>
@@ -10590,7 +10616,7 @@
         <v>29</v>
       </c>
       <c r="S162" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="163">
@@ -10601,10 +10627,10 @@
         <v>36</v>
       </c>
       <c r="C163" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D163" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E163" t="s">
         <v>22</v>
@@ -10619,7 +10645,7 @@
         <v>72</v>
       </c>
       <c r="I163" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J163"/>
       <c r="K163" t="b">
@@ -10635,7 +10661,7 @@
         <v>7</v>
       </c>
       <c r="O163" t="n">
-        <v>0.600036021035383</v>
+        <v>0.60067200780807</v>
       </c>
       <c r="P163" t="s">
         <v>369</v>
@@ -10647,7 +10673,7 @@
         <v>29</v>
       </c>
       <c r="S163" s="1" t="n">
-        <v>45981.0006877183</v>
+        <v>45986.2083710114</v>
       </c>
     </row>
     <row r="164">
@@ -10676,7 +10702,7 @@
         <v>72</v>
       </c>
       <c r="I164" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J164"/>
       <c r="K164" t="b">
@@ -10692,7 +10718,7 @@
         <v>8</v>
       </c>
       <c r="O164" t="n">
-        <v>0.800080318622455</v>
+        <v>0.796004794452947</v>
       </c>
       <c r="P164" t="s">
         <v>371</v>
@@ -10704,7 +10730,7 @@
         <v>29</v>
       </c>
       <c r="S164" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="165">
@@ -10733,7 +10759,7 @@
         <v>72</v>
       </c>
       <c r="I165" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J165"/>
       <c r="K165" t="b">
@@ -10749,7 +10775,7 @@
         <v>8</v>
       </c>
       <c r="O165" t="n">
-        <v>0.491272442736593</v>
+        <v>0.599697634459861</v>
       </c>
       <c r="P165" t="s">
         <v>373</v>
@@ -10761,7 +10787,7 @@
         <v>29</v>
       </c>
       <c r="S165" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="166">
@@ -10790,7 +10816,7 @@
         <v>72</v>
       </c>
       <c r="I166" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J166"/>
       <c r="K166" t="b">
@@ -10806,7 +10832,7 @@
         <v>8</v>
       </c>
       <c r="O166" t="n">
-        <v>0.498703905851745</v>
+        <v>0.740102332467928</v>
       </c>
       <c r="P166" t="s">
         <v>375</v>
@@ -10818,7 +10844,7 @@
         <v>29</v>
       </c>
       <c r="S166" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="167">
@@ -10847,7 +10873,7 @@
         <v>72</v>
       </c>
       <c r="I167" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J167"/>
       <c r="K167" t="b">
@@ -10863,7 +10889,7 @@
         <v>8</v>
       </c>
       <c r="O167" t="n">
-        <v>0.806657120503187</v>
+        <v>0.773510667602135</v>
       </c>
       <c r="P167" t="s">
         <v>377</v>
@@ -10875,7 +10901,7 @@
         <v>29</v>
       </c>
       <c r="S167" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="168">
@@ -10904,7 +10930,7 @@
         <v>72</v>
       </c>
       <c r="I168" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J168"/>
       <c r="K168" t="b">
@@ -10920,7 +10946,7 @@
         <v>8</v>
       </c>
       <c r="O168" t="n">
-        <v>0.783893723640845</v>
+        <v>0.755550867542508</v>
       </c>
       <c r="P168" t="s">
         <v>379</v>
@@ -10932,7 +10958,7 @@
         <v>29</v>
       </c>
       <c r="S168" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="169">
@@ -10961,7 +10987,7 @@
         <v>72</v>
       </c>
       <c r="I169" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J169"/>
       <c r="K169" t="b">
@@ -10977,7 +11003,7 @@
         <v>8</v>
       </c>
       <c r="O169" t="n">
-        <v>0.775237913859624</v>
+        <v>0.77545840445014</v>
       </c>
       <c r="P169" t="s">
         <v>381</v>
@@ -10989,7 +11015,7 @@
         <v>29</v>
       </c>
       <c r="S169" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="170">
@@ -11018,7 +11044,7 @@
         <v>72</v>
       </c>
       <c r="I170" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J170"/>
       <c r="K170" t="b">
@@ -11034,7 +11060,7 @@
         <v>8</v>
       </c>
       <c r="O170" t="n">
-        <v>0.770895880771547</v>
+        <v>0.762712252914671</v>
       </c>
       <c r="P170" t="s">
         <v>383</v>
@@ -11046,7 +11072,7 @@
         <v>29</v>
       </c>
       <c r="S170" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="171">
@@ -11075,7 +11101,7 @@
         <v>72</v>
       </c>
       <c r="I171" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J171"/>
       <c r="K171" t="b">
@@ -11091,7 +11117,7 @@
         <v>8</v>
       </c>
       <c r="O171" t="n">
-        <v>0.744224467066541</v>
+        <v>0.736789892891865</v>
       </c>
       <c r="P171" t="s">
         <v>385</v>
@@ -11103,7 +11129,7 @@
         <v>29</v>
       </c>
       <c r="S171" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="172">
@@ -11132,7 +11158,7 @@
         <v>72</v>
       </c>
       <c r="I172" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J172"/>
       <c r="K172" t="b">
@@ -11148,7 +11174,7 @@
         <v>8</v>
       </c>
       <c r="O172" t="n">
-        <v>0.79650922846296</v>
+        <v>0.789915137221887</v>
       </c>
       <c r="P172" t="s">
         <v>387</v>
@@ -11160,7 +11186,7 @@
         <v>29</v>
       </c>
       <c r="S172" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="173">
@@ -11189,7 +11215,7 @@
         <v>72</v>
       </c>
       <c r="I173" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J173"/>
       <c r="K173" t="b">
@@ -11205,7 +11231,7 @@
         <v>8</v>
       </c>
       <c r="O173" t="n">
-        <v>0.664375971584809</v>
+        <v>0.664762253868193</v>
       </c>
       <c r="P173" t="s">
         <v>389</v>
@@ -11217,7 +11243,7 @@
         <v>29</v>
       </c>
       <c r="S173" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="174">
@@ -11246,7 +11272,7 @@
         <v>72</v>
       </c>
       <c r="I174" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J174"/>
       <c r="K174" t="b">
@@ -11262,7 +11288,7 @@
         <v>8</v>
       </c>
       <c r="O174" t="n">
-        <v>0.706941593524464</v>
+        <v>0.737875720168341</v>
       </c>
       <c r="P174" t="s">
         <v>391</v>
@@ -11274,7 +11300,7 @@
         <v>29</v>
       </c>
       <c r="S174" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="175">
@@ -11303,7 +11329,7 @@
         <v>72</v>
       </c>
       <c r="I175" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J175"/>
       <c r="K175" t="b">
@@ -11319,7 +11345,7 @@
         <v>8</v>
       </c>
       <c r="O175" t="n">
-        <v>0.725591757296998</v>
+        <v>0.767395426926775</v>
       </c>
       <c r="P175" t="s">
         <v>393</v>
@@ -11331,7 +11357,7 @@
         <v>29</v>
       </c>
       <c r="S175" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="176">
@@ -11372,7 +11398,7 @@
         <v>8</v>
       </c>
       <c r="O176" t="n">
-        <v>0.748857216202434</v>
+        <v>0.746303681328701</v>
       </c>
       <c r="P176" t="s">
         <v>395</v>
@@ -11384,7 +11410,7 @@
         <v>29</v>
       </c>
       <c r="S176" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="177">
@@ -11425,7 +11451,7 @@
         <v>8</v>
       </c>
       <c r="O177" t="n">
-        <v>0.7196862085481</v>
+        <v>0.69158088070664</v>
       </c>
       <c r="P177" t="s">
         <v>397</v>
@@ -11437,7 +11463,7 @@
         <v>29</v>
       </c>
       <c r="S177" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="178">
@@ -11482,7 +11508,7 @@
         <v>8</v>
       </c>
       <c r="O178" t="n">
-        <v>0.742982817768369</v>
+        <v>0.735296623783203</v>
       </c>
       <c r="P178" t="s">
         <v>399</v>
@@ -11494,7 +11520,7 @@
         <v>29</v>
       </c>
       <c r="S178" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="179">
@@ -11539,7 +11565,7 @@
         <v>8</v>
       </c>
       <c r="O179" t="n">
-        <v>0.76940340166381</v>
+        <v>0.77374991514296</v>
       </c>
       <c r="P179" t="s">
         <v>401</v>
@@ -11551,7 +11577,7 @@
         <v>29</v>
       </c>
       <c r="S179" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="180">
@@ -11596,7 +11622,7 @@
         <v>8</v>
       </c>
       <c r="O180" t="n">
-        <v>0.782067191292587</v>
+        <v>0.800587057163055</v>
       </c>
       <c r="P180" t="s">
         <v>403</v>
@@ -11608,7 +11634,7 @@
         <v>29</v>
       </c>
       <c r="S180" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="181">
@@ -11637,7 +11663,7 @@
         <v>72</v>
       </c>
       <c r="I181" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J181"/>
       <c r="K181" t="b">
@@ -11653,7 +11679,7 @@
         <v>8</v>
       </c>
       <c r="O181" t="n">
-        <v>0.748048806027708</v>
+        <v>0.766608588360766</v>
       </c>
       <c r="P181" t="s">
         <v>405</v>
@@ -11665,7 +11691,7 @@
         <v>29</v>
       </c>
       <c r="S181" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="182">
@@ -11710,7 +11736,7 @@
         <v>8</v>
       </c>
       <c r="O182" t="n">
-        <v>0.784075021097856</v>
+        <v>0.800205045502848</v>
       </c>
       <c r="P182" t="s">
         <v>407</v>
@@ -11722,7 +11748,7 @@
         <v>29</v>
       </c>
       <c r="S182" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="183">
@@ -11765,7 +11791,7 @@
         <v>8</v>
       </c>
       <c r="O183" t="n">
-        <v>0.759064202416129</v>
+        <v>0.77954607123974</v>
       </c>
       <c r="P183" t="s">
         <v>409</v>
@@ -11777,7 +11803,7 @@
         <v>29</v>
       </c>
       <c r="S183" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="184">
@@ -11820,7 +11846,7 @@
         <v>8</v>
       </c>
       <c r="O184" t="n">
-        <v>0.737772401063844</v>
+        <v>0.775726366949028</v>
       </c>
       <c r="P184" t="s">
         <v>411</v>
@@ -11832,7 +11858,7 @@
         <v>29</v>
       </c>
       <c r="S184" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="185">
@@ -11861,7 +11887,7 @@
         <v>72</v>
       </c>
       <c r="I185" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J185"/>
       <c r="K185" t="b">
@@ -11877,7 +11903,7 @@
         <v>8</v>
       </c>
       <c r="O185" t="n">
-        <v>0.551154386999105</v>
+        <v>0.547305027192479</v>
       </c>
       <c r="P185" t="s">
         <v>413</v>
@@ -11889,7 +11915,7 @@
         <v>29</v>
       </c>
       <c r="S185" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
     <row r="186">
@@ -11918,7 +11944,7 @@
         <v>72</v>
       </c>
       <c r="I186" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J186"/>
       <c r="K186" t="b">
@@ -11934,7 +11960,7 @@
         <v>8</v>
       </c>
       <c r="O186" t="n">
-        <v>0.591241112869344</v>
+        <v>0.60075435043347</v>
       </c>
       <c r="P186" t="s">
         <v>415</v>
@@ -11946,7 +11972,7 @@
         <v>29</v>
       </c>
       <c r="S186" s="1" t="n">
-        <v>45981.2558347482</v>
+        <v>45986.3301753141</v>
       </c>
     </row>
   </sheetData>
